--- a/data.xlsx
+++ b/data.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Towns" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -418,4 +419,30 @@
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:B1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Town ID</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Town Name</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data.xlsx
+++ b/data.xlsx
@@ -8,7 +8,7 @@
   </bookViews>
   <sheets>
     <sheet name="Sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Towns" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Locations" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,18 +427,788 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B1"/>
+  <dimension ref="A1:C52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Town ID</t>
+          <t>Location ID</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>Town Name</t>
+          <t>Location Name</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Location Type</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Meadowbrook</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Sproutwood Trail</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Maple City</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Timberline Trail</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Thornwood Forest</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Ironvale</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Cragpass Trail</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Lunarpeak Cavern</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Moonshadow Trail</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Azuremere City</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Brightwater Bridge</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tidecrest Trail</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Fernway Trail</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Hollowpass Tunnel</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Sunreach Trail</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Scarletide City</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>The Gilded Voyager</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Portside Trail</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Molehill Depths</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Stonewind Trail</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Cindercross Trail</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Shadowrock Tunnel</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Voltspire Station</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Ashen Trail</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Duskpass Tunnel</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Willowshade Trail</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Jadespire City</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Greenridge Trail</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>The Red Line</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Windrush Trail</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Rosemire City</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Wildmere Reserve</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Marshlight Trail</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Reedhollow Trail</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Driftgrass Trail</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Slumberreed Trail</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Duskthistle Town</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Spire of Echoes</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Amberspire City</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Helion Tower</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Coralbreeze Trail</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Saltspray Trail</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Frostcoral Isles</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Ember Town</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Town</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>The Cinderkeep Manor</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Driftwave Trail</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>Bramblecrest Trail</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Stonegate Trail</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>Ascension Pass</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Trail</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>The Summit</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Destination</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Champion's Cave</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Destination</t>
         </is>
       </c>
     </row>

--- a/data.xlsx
+++ b/data.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Cragpass Trail</t>
+          <t>Ashland Trail</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -558,7 +558,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Lunarpeak Cavern</t>
+          <t>Lake Ashland Cavern</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -588,7 +588,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Azuremere City</t>
+          <t>Sendai City</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">

--- a/data.xlsx
+++ b/data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="63">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
   <si>
     <t>Location ID</t>
   </si>
@@ -47,10 +47,10 @@
     <t>Trail</t>
   </si>
   <si>
-    <t xml:space="preserve">You wake up, full of excitement. You are still a little tired because you barely got any sleep last night, but that doesn't matter any more because today is the day that you get to </t>
+    <t>Maple City</t>
   </si>
   <si>
-    <t>Maple City</t>
+    <t>You wake up, full of excitement. You are still a little tired because you barely got any sleep last night, but that doesn't matter any more because today is the day that you get your first Morimon! You quickly get dressed and grab the backpack you packed last night before heading downstairs to join your parents for breakfast. Your mom has prepared a big meal but you're too excited to eat more than a few bites. "You've grown up so fast!" your mother exclaims. "Make sure you keep in touch, and be safe!" she tells you. Your father pats you on the shoulder, reminding you that you had better hurry to the Morimon center or else you'll be late. Taking his advice, you throw your backpack over your shoulder and head out of the house.</t>
   </si>
   <si>
     <t>Catcher</t>
@@ -63,6 +63,9 @@
   </si>
   <si>
     <t>Destination</t>
+  </si>
+  <si>
+    <t>You feel someone gently shaking you awake; still a bit groggy from the night before. As you awaken you hear the familiar voice of your father. "Come on [Player_Name], it's time to wake up. You don't want to be late for your first day as a Morimon catcher." Your lack of energy becomes completely replaced with a surge of excitement. That's right! Today is the day you've been dreaming of. It's the chance for you to venture out on your own as a Morimon catcher. You quickly check the time and realize your father wasn't kidding. If you don't hurry you will be late. You quickly throw on some clothes and grab the bag you packed the night before, then head out the front door.</t>
   </si>
   <si>
     <t>Ironvale</t>
@@ -239,14 +242,23 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="7">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment shrinkToFit="0" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -583,7 +595,7 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="C4" s="1" t="s">
         <v>8</v>
@@ -685,7 +697,7 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>8</v>
@@ -719,7 +731,7 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>10</v>
@@ -753,7 +765,7 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>16</v>
@@ -787,7 +799,7 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" s="1" t="s">
         <v>10</v>
@@ -821,7 +833,7 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" s="1" t="s">
         <v>8</v>
@@ -855,7 +867,7 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>10</v>
@@ -889,7 +901,7 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>10</v>
@@ -923,7 +935,7 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>10</v>
@@ -957,7 +969,7 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>10</v>
@@ -991,7 +1003,7 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>10</v>
@@ -1025,7 +1037,7 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>8</v>
@@ -1059,7 +1071,7 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C18" s="1" t="s">
         <v>16</v>
@@ -1093,7 +1105,7 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="C19" s="1" t="s">
         <v>10</v>
@@ -1127,7 +1139,7 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="C20" s="1" t="s">
         <v>16</v>
@@ -1161,7 +1173,7 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="C21" s="1" t="s">
         <v>10</v>
@@ -1195,7 +1207,7 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>10</v>
@@ -1229,7 +1241,7 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>16</v>
@@ -1263,7 +1275,7 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>16</v>
@@ -1297,7 +1309,7 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>10</v>
@@ -1331,7 +1343,7 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="C26" s="1" t="s">
         <v>10</v>
@@ -1365,7 +1377,7 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>10</v>
@@ -1399,7 +1411,7 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>8</v>
@@ -1433,7 +1445,7 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1" t="s">
         <v>10</v>
@@ -1467,7 +1479,7 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>10</v>
@@ -1501,7 +1513,7 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>10</v>
@@ -1535,7 +1547,7 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C32" s="1" t="s">
         <v>8</v>
@@ -1569,7 +1581,7 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C33" s="1" t="s">
         <v>16</v>
@@ -1603,7 +1615,7 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C34" s="1" t="s">
         <v>10</v>
@@ -1637,7 +1649,7 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C35" s="1" t="s">
         <v>10</v>
@@ -1671,7 +1683,7 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C36" s="1" t="s">
         <v>10</v>
@@ -1705,7 +1717,7 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C37" s="1" t="s">
         <v>10</v>
@@ -1739,7 +1751,7 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C38" s="1" t="s">
         <v>8</v>
@@ -1773,7 +1785,7 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C39" s="1" t="s">
         <v>16</v>
@@ -1807,7 +1819,7 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C40" s="1" t="s">
         <v>8</v>
@@ -1841,7 +1853,7 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C41" s="1" t="s">
         <v>16</v>
@@ -1875,7 +1887,7 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C42" s="1" t="s">
         <v>10</v>
@@ -1909,7 +1921,7 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C43" s="1" t="s">
         <v>10</v>
@@ -1943,7 +1955,7 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C44" s="1" t="s">
         <v>16</v>
@@ -1977,7 +1989,7 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C45" s="1" t="s">
         <v>8</v>
@@ -2011,7 +2023,7 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C46" s="1" t="s">
         <v>16</v>
@@ -2045,7 +2057,7 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C47" s="1" t="s">
         <v>10</v>
@@ -2079,7 +2091,7 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C48" s="1" t="s">
         <v>10</v>
@@ -2113,7 +2125,7 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="C49" s="1" t="s">
         <v>10</v>
@@ -2147,7 +2159,7 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C50" s="1" t="s">
         <v>10</v>
@@ -2181,7 +2193,7 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C51" s="1" t="s">
         <v>16</v>
@@ -2215,7 +2227,7 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C52" s="1" t="s">
         <v>16</v>
@@ -28815,7 +28827,7 @@
       <c r="A1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="2" t="s">
         <v>4</v>
       </c>
       <c r="C1" s="1" t="s">
@@ -28847,11 +28859,11 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="2">
+      <c r="A2" s="3">
         <v>1.0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>11</v>
+      <c r="B2" s="4" t="s">
+        <v>12</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
@@ -28883,9 +28895,18 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
+      <c r="A3" s="5">
+        <v>2.0</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="C3" s="6">
+        <v>1.0</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>13</v>
+      </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
       <c r="G3" s="1"/>
@@ -28910,7 +28931,7 @@
       <c r="Z3" s="1"/>
     </row>
     <row r="4" ht="12.75" customHeight="1">
-      <c r="B4" s="1"/>
+      <c r="B4" s="2"/>
       <c r="C4" s="1"/>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -28938,7 +28959,7 @@
     </row>
     <row r="5" ht="12.75" customHeight="1">
       <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
+      <c r="B5" s="2"/>
       <c r="C5" s="1"/>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -28966,7 +28987,7 @@
     </row>
     <row r="6" ht="12.75" customHeight="1">
       <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
+      <c r="B6" s="2"/>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -28994,7 +29015,7 @@
     </row>
     <row r="7" ht="12.75" customHeight="1">
       <c r="A7" s="1"/>
-      <c r="B7" s="1"/>
+      <c r="B7" s="2"/>
       <c r="C7" s="1"/>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -29022,7 +29043,7 @@
     </row>
     <row r="8" ht="12.75" customHeight="1">
       <c r="A8" s="1"/>
-      <c r="B8" s="1"/>
+      <c r="B8" s="2"/>
       <c r="C8" s="1"/>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -29050,7 +29071,7 @@
     </row>
     <row r="9" ht="12.75" customHeight="1">
       <c r="A9" s="1"/>
-      <c r="B9" s="1"/>
+      <c r="B9" s="2"/>
       <c r="C9" s="1"/>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -29078,7 +29099,7 @@
     </row>
     <row r="10" ht="12.75" customHeight="1">
       <c r="A10" s="1"/>
-      <c r="B10" s="1"/>
+      <c r="B10" s="2"/>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -29106,7 +29127,7 @@
     </row>
     <row r="11" ht="12.75" customHeight="1">
       <c r="A11" s="1"/>
-      <c r="B11" s="1"/>
+      <c r="B11" s="2"/>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -29134,7 +29155,7 @@
     </row>
     <row r="12" ht="12.75" customHeight="1">
       <c r="A12" s="1"/>
-      <c r="B12" s="1"/>
+      <c r="B12" s="2"/>
       <c r="C12" s="1"/>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -29162,7 +29183,7 @@
     </row>
     <row r="13" ht="12.75" customHeight="1">
       <c r="A13" s="1"/>
-      <c r="B13" s="1"/>
+      <c r="B13" s="2"/>
       <c r="C13" s="1"/>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -29190,7 +29211,7 @@
     </row>
     <row r="14" ht="12.75" customHeight="1">
       <c r="A14" s="1"/>
-      <c r="B14" s="1"/>
+      <c r="B14" s="2"/>
       <c r="C14" s="1"/>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -29218,7 +29239,7 @@
     </row>
     <row r="15" ht="12.75" customHeight="1">
       <c r="A15" s="1"/>
-      <c r="B15" s="1"/>
+      <c r="B15" s="2"/>
       <c r="C15" s="1"/>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -29246,7 +29267,7 @@
     </row>
     <row r="16" ht="12.75" customHeight="1">
       <c r="A16" s="1"/>
-      <c r="B16" s="1"/>
+      <c r="B16" s="2"/>
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -29274,7 +29295,7 @@
     </row>
     <row r="17" ht="12.75" customHeight="1">
       <c r="A17" s="1"/>
-      <c r="B17" s="1"/>
+      <c r="B17" s="2"/>
       <c r="C17" s="1"/>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -29302,7 +29323,7 @@
     </row>
     <row r="18" ht="12.75" customHeight="1">
       <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
+      <c r="B18" s="2"/>
       <c r="C18" s="1"/>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -29330,7 +29351,7 @@
     </row>
     <row r="19" ht="12.75" customHeight="1">
       <c r="A19" s="1"/>
-      <c r="B19" s="1"/>
+      <c r="B19" s="2"/>
       <c r="C19" s="1"/>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -29358,7 +29379,7 @@
     </row>
     <row r="20" ht="12.75" customHeight="1">
       <c r="A20" s="1"/>
-      <c r="B20" s="1"/>
+      <c r="B20" s="2"/>
       <c r="C20" s="1"/>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -29386,7 +29407,7 @@
     </row>
     <row r="21" ht="12.75" customHeight="1">
       <c r="A21" s="1"/>
-      <c r="B21" s="1"/>
+      <c r="B21" s="2"/>
       <c r="C21" s="1"/>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -29414,7 +29435,7 @@
     </row>
     <row r="22" ht="12.75" customHeight="1">
       <c r="A22" s="1"/>
-      <c r="B22" s="1"/>
+      <c r="B22" s="2"/>
       <c r="C22" s="1"/>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -29442,7 +29463,7 @@
     </row>
     <row r="23" ht="12.75" customHeight="1">
       <c r="A23" s="1"/>
-      <c r="B23" s="1"/>
+      <c r="B23" s="2"/>
       <c r="C23" s="1"/>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -29470,7 +29491,7 @@
     </row>
     <row r="24" ht="12.75" customHeight="1">
       <c r="A24" s="1"/>
-      <c r="B24" s="1"/>
+      <c r="B24" s="2"/>
       <c r="C24" s="1"/>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -29498,7 +29519,7 @@
     </row>
     <row r="25" ht="12.75" customHeight="1">
       <c r="A25" s="1"/>
-      <c r="B25" s="1"/>
+      <c r="B25" s="2"/>
       <c r="C25" s="1"/>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -29526,7 +29547,7 @@
     </row>
     <row r="26" ht="12.75" customHeight="1">
       <c r="A26" s="1"/>
-      <c r="B26" s="1"/>
+      <c r="B26" s="2"/>
       <c r="C26" s="1"/>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -29554,7 +29575,7 @@
     </row>
     <row r="27" ht="12.75" customHeight="1">
       <c r="A27" s="1"/>
-      <c r="B27" s="1"/>
+      <c r="B27" s="2"/>
       <c r="C27" s="1"/>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -29582,7 +29603,7 @@
     </row>
     <row r="28" ht="12.75" customHeight="1">
       <c r="A28" s="1"/>
-      <c r="B28" s="1"/>
+      <c r="B28" s="2"/>
       <c r="C28" s="1"/>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -29610,7 +29631,7 @@
     </row>
     <row r="29" ht="12.75" customHeight="1">
       <c r="A29" s="1"/>
-      <c r="B29" s="1"/>
+      <c r="B29" s="2"/>
       <c r="C29" s="1"/>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -29638,7 +29659,7 @@
     </row>
     <row r="30" ht="12.75" customHeight="1">
       <c r="A30" s="1"/>
-      <c r="B30" s="1"/>
+      <c r="B30" s="2"/>
       <c r="C30" s="1"/>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -29666,7 +29687,7 @@
     </row>
     <row r="31" ht="12.75" customHeight="1">
       <c r="A31" s="1"/>
-      <c r="B31" s="1"/>
+      <c r="B31" s="2"/>
       <c r="C31" s="1"/>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -29694,7 +29715,7 @@
     </row>
     <row r="32" ht="12.75" customHeight="1">
       <c r="A32" s="1"/>
-      <c r="B32" s="1"/>
+      <c r="B32" s="2"/>
       <c r="C32" s="1"/>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -29722,7 +29743,7 @@
     </row>
     <row r="33" ht="12.75" customHeight="1">
       <c r="A33" s="1"/>
-      <c r="B33" s="1"/>
+      <c r="B33" s="2"/>
       <c r="C33" s="1"/>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -29750,7 +29771,7 @@
     </row>
     <row r="34" ht="12.75" customHeight="1">
       <c r="A34" s="1"/>
-      <c r="B34" s="1"/>
+      <c r="B34" s="2"/>
       <c r="C34" s="1"/>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -29778,7 +29799,7 @@
     </row>
     <row r="35" ht="12.75" customHeight="1">
       <c r="A35" s="1"/>
-      <c r="B35" s="1"/>
+      <c r="B35" s="2"/>
       <c r="C35" s="1"/>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -29806,7 +29827,7 @@
     </row>
     <row r="36" ht="12.75" customHeight="1">
       <c r="A36" s="1"/>
-      <c r="B36" s="1"/>
+      <c r="B36" s="2"/>
       <c r="C36" s="1"/>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -29834,7 +29855,7 @@
     </row>
     <row r="37" ht="12.75" customHeight="1">
       <c r="A37" s="1"/>
-      <c r="B37" s="1"/>
+      <c r="B37" s="2"/>
       <c r="C37" s="1"/>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -29862,7 +29883,7 @@
     </row>
     <row r="38" ht="12.75" customHeight="1">
       <c r="A38" s="1"/>
-      <c r="B38" s="1"/>
+      <c r="B38" s="2"/>
       <c r="C38" s="1"/>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -29890,7 +29911,7 @@
     </row>
     <row r="39" ht="12.75" customHeight="1">
       <c r="A39" s="1"/>
-      <c r="B39" s="1"/>
+      <c r="B39" s="2"/>
       <c r="C39" s="1"/>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -29918,7 +29939,7 @@
     </row>
     <row r="40" ht="12.75" customHeight="1">
       <c r="A40" s="1"/>
-      <c r="B40" s="1"/>
+      <c r="B40" s="2"/>
       <c r="C40" s="1"/>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -29946,7 +29967,7 @@
     </row>
     <row r="41" ht="12.75" customHeight="1">
       <c r="A41" s="1"/>
-      <c r="B41" s="1"/>
+      <c r="B41" s="2"/>
       <c r="C41" s="1"/>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -29974,7 +29995,7 @@
     </row>
     <row r="42" ht="12.75" customHeight="1">
       <c r="A42" s="1"/>
-      <c r="B42" s="1"/>
+      <c r="B42" s="2"/>
       <c r="C42" s="1"/>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -30002,7 +30023,7 @@
     </row>
     <row r="43" ht="12.75" customHeight="1">
       <c r="A43" s="1"/>
-      <c r="B43" s="1"/>
+      <c r="B43" s="2"/>
       <c r="C43" s="1"/>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -30030,7 +30051,7 @@
     </row>
     <row r="44" ht="12.75" customHeight="1">
       <c r="A44" s="1"/>
-      <c r="B44" s="1"/>
+      <c r="B44" s="2"/>
       <c r="C44" s="1"/>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -30058,7 +30079,7 @@
     </row>
     <row r="45" ht="12.75" customHeight="1">
       <c r="A45" s="1"/>
-      <c r="B45" s="1"/>
+      <c r="B45" s="2"/>
       <c r="C45" s="1"/>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -30086,7 +30107,7 @@
     </row>
     <row r="46" ht="12.75" customHeight="1">
       <c r="A46" s="1"/>
-      <c r="B46" s="1"/>
+      <c r="B46" s="2"/>
       <c r="C46" s="1"/>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -30114,7 +30135,7 @@
     </row>
     <row r="47" ht="12.75" customHeight="1">
       <c r="A47" s="1"/>
-      <c r="B47" s="1"/>
+      <c r="B47" s="2"/>
       <c r="C47" s="1"/>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -30142,7 +30163,7 @@
     </row>
     <row r="48" ht="12.75" customHeight="1">
       <c r="A48" s="1"/>
-      <c r="B48" s="1"/>
+      <c r="B48" s="2"/>
       <c r="C48" s="1"/>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -30170,7 +30191,7 @@
     </row>
     <row r="49" ht="12.75" customHeight="1">
       <c r="A49" s="1"/>
-      <c r="B49" s="1"/>
+      <c r="B49" s="2"/>
       <c r="C49" s="1"/>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -30198,7 +30219,7 @@
     </row>
     <row r="50" ht="12.75" customHeight="1">
       <c r="A50" s="1"/>
-      <c r="B50" s="1"/>
+      <c r="B50" s="2"/>
       <c r="C50" s="1"/>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -30226,7 +30247,7 @@
     </row>
     <row r="51" ht="12.75" customHeight="1">
       <c r="A51" s="1"/>
-      <c r="B51" s="1"/>
+      <c r="B51" s="2"/>
       <c r="C51" s="1"/>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -30254,7 +30275,7 @@
     </row>
     <row r="52" ht="12.75" customHeight="1">
       <c r="A52" s="1"/>
-      <c r="B52" s="1"/>
+      <c r="B52" s="2"/>
       <c r="C52" s="1"/>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -30282,7 +30303,7 @@
     </row>
     <row r="53" ht="12.75" customHeight="1">
       <c r="A53" s="1"/>
-      <c r="B53" s="1"/>
+      <c r="B53" s="2"/>
       <c r="C53" s="1"/>
       <c r="D53" s="1"/>
       <c r="E53" s="1"/>
@@ -30310,7 +30331,7 @@
     </row>
     <row r="54" ht="12.75" customHeight="1">
       <c r="A54" s="1"/>
-      <c r="B54" s="1"/>
+      <c r="B54" s="2"/>
       <c r="C54" s="1"/>
       <c r="D54" s="1"/>
       <c r="E54" s="1"/>
@@ -30338,7 +30359,7 @@
     </row>
     <row r="55" ht="12.75" customHeight="1">
       <c r="A55" s="1"/>
-      <c r="B55" s="1"/>
+      <c r="B55" s="2"/>
       <c r="C55" s="1"/>
       <c r="D55" s="1"/>
       <c r="E55" s="1"/>
@@ -30366,7 +30387,7 @@
     </row>
     <row r="56" ht="12.75" customHeight="1">
       <c r="A56" s="1"/>
-      <c r="B56" s="1"/>
+      <c r="B56" s="2"/>
       <c r="C56" s="1"/>
       <c r="D56" s="1"/>
       <c r="E56" s="1"/>
@@ -30394,7 +30415,7 @@
     </row>
     <row r="57" ht="12.75" customHeight="1">
       <c r="A57" s="1"/>
-      <c r="B57" s="1"/>
+      <c r="B57" s="2"/>
       <c r="C57" s="1"/>
       <c r="D57" s="1"/>
       <c r="E57" s="1"/>
@@ -30422,7 +30443,7 @@
     </row>
     <row r="58" ht="12.75" customHeight="1">
       <c r="A58" s="1"/>
-      <c r="B58" s="1"/>
+      <c r="B58" s="2"/>
       <c r="C58" s="1"/>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -30450,7 +30471,7 @@
     </row>
     <row r="59" ht="12.75" customHeight="1">
       <c r="A59" s="1"/>
-      <c r="B59" s="1"/>
+      <c r="B59" s="2"/>
       <c r="C59" s="1"/>
       <c r="D59" s="1"/>
       <c r="E59" s="1"/>
@@ -30478,7 +30499,7 @@
     </row>
     <row r="60" ht="12.75" customHeight="1">
       <c r="A60" s="1"/>
-      <c r="B60" s="1"/>
+      <c r="B60" s="2"/>
       <c r="C60" s="1"/>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -30506,7 +30527,7 @@
     </row>
     <row r="61" ht="12.75" customHeight="1">
       <c r="A61" s="1"/>
-      <c r="B61" s="1"/>
+      <c r="B61" s="2"/>
       <c r="C61" s="1"/>
       <c r="D61" s="1"/>
       <c r="E61" s="1"/>
@@ -30534,7 +30555,7 @@
     </row>
     <row r="62" ht="12.75" customHeight="1">
       <c r="A62" s="1"/>
-      <c r="B62" s="1"/>
+      <c r="B62" s="2"/>
       <c r="C62" s="1"/>
       <c r="D62" s="1"/>
       <c r="E62" s="1"/>
@@ -30562,7 +30583,7 @@
     </row>
     <row r="63" ht="12.75" customHeight="1">
       <c r="A63" s="1"/>
-      <c r="B63" s="1"/>
+      <c r="B63" s="2"/>
       <c r="C63" s="1"/>
       <c r="D63" s="1"/>
       <c r="E63" s="1"/>
@@ -30590,7 +30611,7 @@
     </row>
     <row r="64" ht="12.75" customHeight="1">
       <c r="A64" s="1"/>
-      <c r="B64" s="1"/>
+      <c r="B64" s="2"/>
       <c r="C64" s="1"/>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -30618,7 +30639,7 @@
     </row>
     <row r="65" ht="12.75" customHeight="1">
       <c r="A65" s="1"/>
-      <c r="B65" s="1"/>
+      <c r="B65" s="2"/>
       <c r="C65" s="1"/>
       <c r="D65" s="1"/>
       <c r="E65" s="1"/>
@@ -30646,7 +30667,7 @@
     </row>
     <row r="66" ht="12.75" customHeight="1">
       <c r="A66" s="1"/>
-      <c r="B66" s="1"/>
+      <c r="B66" s="2"/>
       <c r="C66" s="1"/>
       <c r="D66" s="1"/>
       <c r="E66" s="1"/>
@@ -30674,7 +30695,7 @@
     </row>
     <row r="67" ht="12.75" customHeight="1">
       <c r="A67" s="1"/>
-      <c r="B67" s="1"/>
+      <c r="B67" s="2"/>
       <c r="C67" s="1"/>
       <c r="D67" s="1"/>
       <c r="E67" s="1"/>
@@ -30702,7 +30723,7 @@
     </row>
     <row r="68" ht="12.75" customHeight="1">
       <c r="A68" s="1"/>
-      <c r="B68" s="1"/>
+      <c r="B68" s="2"/>
       <c r="C68" s="1"/>
       <c r="D68" s="1"/>
       <c r="E68" s="1"/>
@@ -30730,7 +30751,7 @@
     </row>
     <row r="69" ht="12.75" customHeight="1">
       <c r="A69" s="1"/>
-      <c r="B69" s="1"/>
+      <c r="B69" s="2"/>
       <c r="C69" s="1"/>
       <c r="D69" s="1"/>
       <c r="E69" s="1"/>
@@ -30758,7 +30779,7 @@
     </row>
     <row r="70" ht="12.75" customHeight="1">
       <c r="A70" s="1"/>
-      <c r="B70" s="1"/>
+      <c r="B70" s="2"/>
       <c r="C70" s="1"/>
       <c r="D70" s="1"/>
       <c r="E70" s="1"/>
@@ -30786,7 +30807,7 @@
     </row>
     <row r="71" ht="12.75" customHeight="1">
       <c r="A71" s="1"/>
-      <c r="B71" s="1"/>
+      <c r="B71" s="2"/>
       <c r="C71" s="1"/>
       <c r="D71" s="1"/>
       <c r="E71" s="1"/>
@@ -30814,7 +30835,7 @@
     </row>
     <row r="72" ht="12.75" customHeight="1">
       <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
+      <c r="B72" s="2"/>
       <c r="C72" s="1"/>
       <c r="D72" s="1"/>
       <c r="E72" s="1"/>
@@ -30842,7 +30863,7 @@
     </row>
     <row r="73" ht="12.75" customHeight="1">
       <c r="A73" s="1"/>
-      <c r="B73" s="1"/>
+      <c r="B73" s="2"/>
       <c r="C73" s="1"/>
       <c r="D73" s="1"/>
       <c r="E73" s="1"/>
@@ -30870,7 +30891,7 @@
     </row>
     <row r="74" ht="12.75" customHeight="1">
       <c r="A74" s="1"/>
-      <c r="B74" s="1"/>
+      <c r="B74" s="2"/>
       <c r="C74" s="1"/>
       <c r="D74" s="1"/>
       <c r="E74" s="1"/>
@@ -30898,7 +30919,7 @@
     </row>
     <row r="75" ht="12.75" customHeight="1">
       <c r="A75" s="1"/>
-      <c r="B75" s="1"/>
+      <c r="B75" s="2"/>
       <c r="C75" s="1"/>
       <c r="D75" s="1"/>
       <c r="E75" s="1"/>
@@ -30926,7 +30947,7 @@
     </row>
     <row r="76" ht="12.75" customHeight="1">
       <c r="A76" s="1"/>
-      <c r="B76" s="1"/>
+      <c r="B76" s="2"/>
       <c r="C76" s="1"/>
       <c r="D76" s="1"/>
       <c r="E76" s="1"/>
@@ -30954,7 +30975,7 @@
     </row>
     <row r="77" ht="12.75" customHeight="1">
       <c r="A77" s="1"/>
-      <c r="B77" s="1"/>
+      <c r="B77" s="2"/>
       <c r="C77" s="1"/>
       <c r="D77" s="1"/>
       <c r="E77" s="1"/>
@@ -30982,7 +31003,7 @@
     </row>
     <row r="78" ht="12.75" customHeight="1">
       <c r="A78" s="1"/>
-      <c r="B78" s="1"/>
+      <c r="B78" s="2"/>
       <c r="C78" s="1"/>
       <c r="D78" s="1"/>
       <c r="E78" s="1"/>
@@ -31010,7 +31031,7 @@
     </row>
     <row r="79" ht="12.75" customHeight="1">
       <c r="A79" s="1"/>
-      <c r="B79" s="1"/>
+      <c r="B79" s="2"/>
       <c r="C79" s="1"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1"/>
@@ -31038,7 +31059,7 @@
     </row>
     <row r="80" ht="12.75" customHeight="1">
       <c r="A80" s="1"/>
-      <c r="B80" s="1"/>
+      <c r="B80" s="2"/>
       <c r="C80" s="1"/>
       <c r="D80" s="1"/>
       <c r="E80" s="1"/>
@@ -31066,7 +31087,7 @@
     </row>
     <row r="81" ht="12.75" customHeight="1">
       <c r="A81" s="1"/>
-      <c r="B81" s="1"/>
+      <c r="B81" s="2"/>
       <c r="C81" s="1"/>
       <c r="D81" s="1"/>
       <c r="E81" s="1"/>
@@ -31094,7 +31115,7 @@
     </row>
     <row r="82" ht="12.75" customHeight="1">
       <c r="A82" s="1"/>
-      <c r="B82" s="1"/>
+      <c r="B82" s="2"/>
       <c r="C82" s="1"/>
       <c r="D82" s="1"/>
       <c r="E82" s="1"/>
@@ -31122,7 +31143,7 @@
     </row>
     <row r="83" ht="12.75" customHeight="1">
       <c r="A83" s="1"/>
-      <c r="B83" s="1"/>
+      <c r="B83" s="2"/>
       <c r="C83" s="1"/>
       <c r="D83" s="1"/>
       <c r="E83" s="1"/>
@@ -31150,7 +31171,7 @@
     </row>
     <row r="84" ht="12.75" customHeight="1">
       <c r="A84" s="1"/>
-      <c r="B84" s="1"/>
+      <c r="B84" s="2"/>
       <c r="C84" s="1"/>
       <c r="D84" s="1"/>
       <c r="E84" s="1"/>
@@ -31178,7 +31199,7 @@
     </row>
     <row r="85" ht="12.75" customHeight="1">
       <c r="A85" s="1"/>
-      <c r="B85" s="1"/>
+      <c r="B85" s="2"/>
       <c r="C85" s="1"/>
       <c r="D85" s="1"/>
       <c r="E85" s="1"/>
@@ -31206,7 +31227,7 @@
     </row>
     <row r="86" ht="12.75" customHeight="1">
       <c r="A86" s="1"/>
-      <c r="B86" s="1"/>
+      <c r="B86" s="2"/>
       <c r="C86" s="1"/>
       <c r="D86" s="1"/>
       <c r="E86" s="1"/>
@@ -31234,7 +31255,7 @@
     </row>
     <row r="87" ht="12.75" customHeight="1">
       <c r="A87" s="1"/>
-      <c r="B87" s="1"/>
+      <c r="B87" s="2"/>
       <c r="C87" s="1"/>
       <c r="D87" s="1"/>
       <c r="E87" s="1"/>
@@ -31262,7 +31283,7 @@
     </row>
     <row r="88" ht="12.75" customHeight="1">
       <c r="A88" s="1"/>
-      <c r="B88" s="1"/>
+      <c r="B88" s="2"/>
       <c r="C88" s="1"/>
       <c r="D88" s="1"/>
       <c r="E88" s="1"/>
@@ -31290,7 +31311,7 @@
     </row>
     <row r="89" ht="12.75" customHeight="1">
       <c r="A89" s="1"/>
-      <c r="B89" s="1"/>
+      <c r="B89" s="2"/>
       <c r="C89" s="1"/>
       <c r="D89" s="1"/>
       <c r="E89" s="1"/>
@@ -31318,7 +31339,7 @@
     </row>
     <row r="90" ht="12.75" customHeight="1">
       <c r="A90" s="1"/>
-      <c r="B90" s="1"/>
+      <c r="B90" s="2"/>
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1"/>
@@ -31346,7 +31367,7 @@
     </row>
     <row r="91" ht="12.75" customHeight="1">
       <c r="A91" s="1"/>
-      <c r="B91" s="1"/>
+      <c r="B91" s="2"/>
       <c r="C91" s="1"/>
       <c r="D91" s="1"/>
       <c r="E91" s="1"/>
@@ -31374,7 +31395,7 @@
     </row>
     <row r="92" ht="12.75" customHeight="1">
       <c r="A92" s="1"/>
-      <c r="B92" s="1"/>
+      <c r="B92" s="2"/>
       <c r="C92" s="1"/>
       <c r="D92" s="1"/>
       <c r="E92" s="1"/>
@@ -31402,7 +31423,7 @@
     </row>
     <row r="93" ht="12.75" customHeight="1">
       <c r="A93" s="1"/>
-      <c r="B93" s="1"/>
+      <c r="B93" s="2"/>
       <c r="C93" s="1"/>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -31430,7 +31451,7 @@
     </row>
     <row r="94" ht="12.75" customHeight="1">
       <c r="A94" s="1"/>
-      <c r="B94" s="1"/>
+      <c r="B94" s="2"/>
       <c r="C94" s="1"/>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -31458,7 +31479,7 @@
     </row>
     <row r="95" ht="12.75" customHeight="1">
       <c r="A95" s="1"/>
-      <c r="B95" s="1"/>
+      <c r="B95" s="2"/>
       <c r="C95" s="1"/>
       <c r="D95" s="1"/>
       <c r="E95" s="1"/>
@@ -31486,7 +31507,7 @@
     </row>
     <row r="96" ht="12.75" customHeight="1">
       <c r="A96" s="1"/>
-      <c r="B96" s="1"/>
+      <c r="B96" s="2"/>
       <c r="C96" s="1"/>
       <c r="D96" s="1"/>
       <c r="E96" s="1"/>
@@ -31514,7 +31535,7 @@
     </row>
     <row r="97" ht="12.75" customHeight="1">
       <c r="A97" s="1"/>
-      <c r="B97" s="1"/>
+      <c r="B97" s="2"/>
       <c r="C97" s="1"/>
       <c r="D97" s="1"/>
       <c r="E97" s="1"/>
@@ -31542,7 +31563,7 @@
     </row>
     <row r="98" ht="12.75" customHeight="1">
       <c r="A98" s="1"/>
-      <c r="B98" s="1"/>
+      <c r="B98" s="2"/>
       <c r="C98" s="1"/>
       <c r="D98" s="1"/>
       <c r="E98" s="1"/>
@@ -31570,7 +31591,7 @@
     </row>
     <row r="99" ht="12.75" customHeight="1">
       <c r="A99" s="1"/>
-      <c r="B99" s="1"/>
+      <c r="B99" s="2"/>
       <c r="C99" s="1"/>
       <c r="D99" s="1"/>
       <c r="E99" s="1"/>
@@ -31598,7 +31619,7 @@
     </row>
     <row r="100" ht="12.75" customHeight="1">
       <c r="A100" s="1"/>
-      <c r="B100" s="1"/>
+      <c r="B100" s="2"/>
       <c r="C100" s="1"/>
       <c r="D100" s="1"/>
       <c r="E100" s="1"/>
@@ -31626,7 +31647,7 @@
     </row>
     <row r="101" ht="12.75" customHeight="1">
       <c r="A101" s="1"/>
-      <c r="B101" s="1"/>
+      <c r="B101" s="2"/>
       <c r="C101" s="1"/>
       <c r="D101" s="1"/>
       <c r="E101" s="1"/>
@@ -31654,7 +31675,7 @@
     </row>
     <row r="102" ht="12.75" customHeight="1">
       <c r="A102" s="1"/>
-      <c r="B102" s="1"/>
+      <c r="B102" s="2"/>
       <c r="C102" s="1"/>
       <c r="D102" s="1"/>
       <c r="E102" s="1"/>
@@ -31682,7 +31703,7 @@
     </row>
     <row r="103" ht="12.75" customHeight="1">
       <c r="A103" s="1"/>
-      <c r="B103" s="1"/>
+      <c r="B103" s="2"/>
       <c r="C103" s="1"/>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -31710,7 +31731,7 @@
     </row>
     <row r="104" ht="12.75" customHeight="1">
       <c r="A104" s="1"/>
-      <c r="B104" s="1"/>
+      <c r="B104" s="2"/>
       <c r="C104" s="1"/>
       <c r="D104" s="1"/>
       <c r="E104" s="1"/>
@@ -31738,7 +31759,7 @@
     </row>
     <row r="105" ht="12.75" customHeight="1">
       <c r="A105" s="1"/>
-      <c r="B105" s="1"/>
+      <c r="B105" s="2"/>
       <c r="C105" s="1"/>
       <c r="D105" s="1"/>
       <c r="E105" s="1"/>
@@ -31766,7 +31787,7 @@
     </row>
     <row r="106" ht="12.75" customHeight="1">
       <c r="A106" s="1"/>
-      <c r="B106" s="1"/>
+      <c r="B106" s="2"/>
       <c r="C106" s="1"/>
       <c r="D106" s="1"/>
       <c r="E106" s="1"/>
@@ -31794,7 +31815,7 @@
     </row>
     <row r="107" ht="12.75" customHeight="1">
       <c r="A107" s="1"/>
-      <c r="B107" s="1"/>
+      <c r="B107" s="2"/>
       <c r="C107" s="1"/>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -31822,7 +31843,7 @@
     </row>
     <row r="108" ht="12.75" customHeight="1">
       <c r="A108" s="1"/>
-      <c r="B108" s="1"/>
+      <c r="B108" s="2"/>
       <c r="C108" s="1"/>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
@@ -31850,7 +31871,7 @@
     </row>
     <row r="109" ht="12.75" customHeight="1">
       <c r="A109" s="1"/>
-      <c r="B109" s="1"/>
+      <c r="B109" s="2"/>
       <c r="C109" s="1"/>
       <c r="D109" s="1"/>
       <c r="E109" s="1"/>
@@ -31878,7 +31899,7 @@
     </row>
     <row r="110" ht="12.75" customHeight="1">
       <c r="A110" s="1"/>
-      <c r="B110" s="1"/>
+      <c r="B110" s="2"/>
       <c r="C110" s="1"/>
       <c r="D110" s="1"/>
       <c r="E110" s="1"/>
@@ -31906,7 +31927,7 @@
     </row>
     <row r="111" ht="12.75" customHeight="1">
       <c r="A111" s="1"/>
-      <c r="B111" s="1"/>
+      <c r="B111" s="2"/>
       <c r="C111" s="1"/>
       <c r="D111" s="1"/>
       <c r="E111" s="1"/>
@@ -31934,7 +31955,7 @@
     </row>
     <row r="112" ht="12.75" customHeight="1">
       <c r="A112" s="1"/>
-      <c r="B112" s="1"/>
+      <c r="B112" s="2"/>
       <c r="C112" s="1"/>
       <c r="D112" s="1"/>
       <c r="E112" s="1"/>
@@ -31962,7 +31983,7 @@
     </row>
     <row r="113" ht="12.75" customHeight="1">
       <c r="A113" s="1"/>
-      <c r="B113" s="1"/>
+      <c r="B113" s="2"/>
       <c r="C113" s="1"/>
       <c r="D113" s="1"/>
       <c r="E113" s="1"/>
@@ -31990,7 +32011,7 @@
     </row>
     <row r="114" ht="12.75" customHeight="1">
       <c r="A114" s="1"/>
-      <c r="B114" s="1"/>
+      <c r="B114" s="2"/>
       <c r="C114" s="1"/>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -32018,7 +32039,7 @@
     </row>
     <row r="115" ht="12.75" customHeight="1">
       <c r="A115" s="1"/>
-      <c r="B115" s="1"/>
+      <c r="B115" s="2"/>
       <c r="C115" s="1"/>
       <c r="D115" s="1"/>
       <c r="E115" s="1"/>
@@ -32046,7 +32067,7 @@
     </row>
     <row r="116" ht="12.75" customHeight="1">
       <c r="A116" s="1"/>
-      <c r="B116" s="1"/>
+      <c r="B116" s="2"/>
       <c r="C116" s="1"/>
       <c r="D116" s="1"/>
       <c r="E116" s="1"/>
@@ -32074,7 +32095,7 @@
     </row>
     <row r="117" ht="12.75" customHeight="1">
       <c r="A117" s="1"/>
-      <c r="B117" s="1"/>
+      <c r="B117" s="2"/>
       <c r="C117" s="1"/>
       <c r="D117" s="1"/>
       <c r="E117" s="1"/>
@@ -32102,7 +32123,7 @@
     </row>
     <row r="118" ht="12.75" customHeight="1">
       <c r="A118" s="1"/>
-      <c r="B118" s="1"/>
+      <c r="B118" s="2"/>
       <c r="C118" s="1"/>
       <c r="D118" s="1"/>
       <c r="E118" s="1"/>
@@ -32130,7 +32151,7 @@
     </row>
     <row r="119" ht="12.75" customHeight="1">
       <c r="A119" s="1"/>
-      <c r="B119" s="1"/>
+      <c r="B119" s="2"/>
       <c r="C119" s="1"/>
       <c r="D119" s="1"/>
       <c r="E119" s="1"/>
@@ -32158,7 +32179,7 @@
     </row>
     <row r="120" ht="12.75" customHeight="1">
       <c r="A120" s="1"/>
-      <c r="B120" s="1"/>
+      <c r="B120" s="2"/>
       <c r="C120" s="1"/>
       <c r="D120" s="1"/>
       <c r="E120" s="1"/>
@@ -32186,7 +32207,7 @@
     </row>
     <row r="121" ht="12.75" customHeight="1">
       <c r="A121" s="1"/>
-      <c r="B121" s="1"/>
+      <c r="B121" s="2"/>
       <c r="C121" s="1"/>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -32214,7 +32235,7 @@
     </row>
     <row r="122" ht="12.75" customHeight="1">
       <c r="A122" s="1"/>
-      <c r="B122" s="1"/>
+      <c r="B122" s="2"/>
       <c r="C122" s="1"/>
       <c r="D122" s="1"/>
       <c r="E122" s="1"/>
@@ -32242,7 +32263,7 @@
     </row>
     <row r="123" ht="12.75" customHeight="1">
       <c r="A123" s="1"/>
-      <c r="B123" s="1"/>
+      <c r="B123" s="2"/>
       <c r="C123" s="1"/>
       <c r="D123" s="1"/>
       <c r="E123" s="1"/>
@@ -32270,7 +32291,7 @@
     </row>
     <row r="124" ht="12.75" customHeight="1">
       <c r="A124" s="1"/>
-      <c r="B124" s="1"/>
+      <c r="B124" s="2"/>
       <c r="C124" s="1"/>
       <c r="D124" s="1"/>
       <c r="E124" s="1"/>
@@ -32298,7 +32319,7 @@
     </row>
     <row r="125" ht="12.75" customHeight="1">
       <c r="A125" s="1"/>
-      <c r="B125" s="1"/>
+      <c r="B125" s="2"/>
       <c r="C125" s="1"/>
       <c r="D125" s="1"/>
       <c r="E125" s="1"/>
@@ -32326,7 +32347,7 @@
     </row>
     <row r="126" ht="12.75" customHeight="1">
       <c r="A126" s="1"/>
-      <c r="B126" s="1"/>
+      <c r="B126" s="2"/>
       <c r="C126" s="1"/>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -32354,7 +32375,7 @@
     </row>
     <row r="127" ht="12.75" customHeight="1">
       <c r="A127" s="1"/>
-      <c r="B127" s="1"/>
+      <c r="B127" s="2"/>
       <c r="C127" s="1"/>
       <c r="D127" s="1"/>
       <c r="E127" s="1"/>
@@ -32382,7 +32403,7 @@
     </row>
     <row r="128" ht="12.75" customHeight="1">
       <c r="A128" s="1"/>
-      <c r="B128" s="1"/>
+      <c r="B128" s="2"/>
       <c r="C128" s="1"/>
       <c r="D128" s="1"/>
       <c r="E128" s="1"/>
@@ -32410,7 +32431,7 @@
     </row>
     <row r="129" ht="12.75" customHeight="1">
       <c r="A129" s="1"/>
-      <c r="B129" s="1"/>
+      <c r="B129" s="2"/>
       <c r="C129" s="1"/>
       <c r="D129" s="1"/>
       <c r="E129" s="1"/>
@@ -32438,7 +32459,7 @@
     </row>
     <row r="130" ht="12.75" customHeight="1">
       <c r="A130" s="1"/>
-      <c r="B130" s="1"/>
+      <c r="B130" s="2"/>
       <c r="C130" s="1"/>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -32466,7 +32487,7 @@
     </row>
     <row r="131" ht="12.75" customHeight="1">
       <c r="A131" s="1"/>
-      <c r="B131" s="1"/>
+      <c r="B131" s="2"/>
       <c r="C131" s="1"/>
       <c r="D131" s="1"/>
       <c r="E131" s="1"/>
@@ -32494,7 +32515,7 @@
     </row>
     <row r="132" ht="12.75" customHeight="1">
       <c r="A132" s="1"/>
-      <c r="B132" s="1"/>
+      <c r="B132" s="2"/>
       <c r="C132" s="1"/>
       <c r="D132" s="1"/>
       <c r="E132" s="1"/>
@@ -32522,7 +32543,7 @@
     </row>
     <row r="133" ht="12.75" customHeight="1">
       <c r="A133" s="1"/>
-      <c r="B133" s="1"/>
+      <c r="B133" s="2"/>
       <c r="C133" s="1"/>
       <c r="D133" s="1"/>
       <c r="E133" s="1"/>
@@ -32550,7 +32571,7 @@
     </row>
     <row r="134" ht="12.75" customHeight="1">
       <c r="A134" s="1"/>
-      <c r="B134" s="1"/>
+      <c r="B134" s="2"/>
       <c r="C134" s="1"/>
       <c r="D134" s="1"/>
       <c r="E134" s="1"/>
@@ -32578,7 +32599,7 @@
     </row>
     <row r="135" ht="12.75" customHeight="1">
       <c r="A135" s="1"/>
-      <c r="B135" s="1"/>
+      <c r="B135" s="2"/>
       <c r="C135" s="1"/>
       <c r="D135" s="1"/>
       <c r="E135" s="1"/>
@@ -32606,7 +32627,7 @@
     </row>
     <row r="136" ht="12.75" customHeight="1">
       <c r="A136" s="1"/>
-      <c r="B136" s="1"/>
+      <c r="B136" s="2"/>
       <c r="C136" s="1"/>
       <c r="D136" s="1"/>
       <c r="E136" s="1"/>
@@ -32634,7 +32655,7 @@
     </row>
     <row r="137" ht="12.75" customHeight="1">
       <c r="A137" s="1"/>
-      <c r="B137" s="1"/>
+      <c r="B137" s="2"/>
       <c r="C137" s="1"/>
       <c r="D137" s="1"/>
       <c r="E137" s="1"/>
@@ -32662,7 +32683,7 @@
     </row>
     <row r="138" ht="12.75" customHeight="1">
       <c r="A138" s="1"/>
-      <c r="B138" s="1"/>
+      <c r="B138" s="2"/>
       <c r="C138" s="1"/>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -32690,7 +32711,7 @@
     </row>
     <row r="139" ht="12.75" customHeight="1">
       <c r="A139" s="1"/>
-      <c r="B139" s="1"/>
+      <c r="B139" s="2"/>
       <c r="C139" s="1"/>
       <c r="D139" s="1"/>
       <c r="E139" s="1"/>
@@ -32718,7 +32739,7 @@
     </row>
     <row r="140" ht="12.75" customHeight="1">
       <c r="A140" s="1"/>
-      <c r="B140" s="1"/>
+      <c r="B140" s="2"/>
       <c r="C140" s="1"/>
       <c r="D140" s="1"/>
       <c r="E140" s="1"/>
@@ -32746,7 +32767,7 @@
     </row>
     <row r="141" ht="12.75" customHeight="1">
       <c r="A141" s="1"/>
-      <c r="B141" s="1"/>
+      <c r="B141" s="2"/>
       <c r="C141" s="1"/>
       <c r="D141" s="1"/>
       <c r="E141" s="1"/>
@@ -32774,7 +32795,7 @@
     </row>
     <row r="142" ht="12.75" customHeight="1">
       <c r="A142" s="1"/>
-      <c r="B142" s="1"/>
+      <c r="B142" s="2"/>
       <c r="C142" s="1"/>
       <c r="D142" s="1"/>
       <c r="E142" s="1"/>
@@ -32802,7 +32823,7 @@
     </row>
     <row r="143" ht="12.75" customHeight="1">
       <c r="A143" s="1"/>
-      <c r="B143" s="1"/>
+      <c r="B143" s="2"/>
       <c r="C143" s="1"/>
       <c r="D143" s="1"/>
       <c r="E143" s="1"/>
@@ -32830,7 +32851,7 @@
     </row>
     <row r="144" ht="12.75" customHeight="1">
       <c r="A144" s="1"/>
-      <c r="B144" s="1"/>
+      <c r="B144" s="2"/>
       <c r="C144" s="1"/>
       <c r="D144" s="1"/>
       <c r="E144" s="1"/>
@@ -32858,7 +32879,7 @@
     </row>
     <row r="145" ht="12.75" customHeight="1">
       <c r="A145" s="1"/>
-      <c r="B145" s="1"/>
+      <c r="B145" s="2"/>
       <c r="C145" s="1"/>
       <c r="D145" s="1"/>
       <c r="E145" s="1"/>
@@ -32886,7 +32907,7 @@
     </row>
     <row r="146" ht="12.75" customHeight="1">
       <c r="A146" s="1"/>
-      <c r="B146" s="1"/>
+      <c r="B146" s="2"/>
       <c r="C146" s="1"/>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -32914,7 +32935,7 @@
     </row>
     <row r="147" ht="12.75" customHeight="1">
       <c r="A147" s="1"/>
-      <c r="B147" s="1"/>
+      <c r="B147" s="2"/>
       <c r="C147" s="1"/>
       <c r="D147" s="1"/>
       <c r="E147" s="1"/>
@@ -32942,7 +32963,7 @@
     </row>
     <row r="148" ht="12.75" customHeight="1">
       <c r="A148" s="1"/>
-      <c r="B148" s="1"/>
+      <c r="B148" s="2"/>
       <c r="C148" s="1"/>
       <c r="D148" s="1"/>
       <c r="E148" s="1"/>
@@ -32970,7 +32991,7 @@
     </row>
     <row r="149" ht="12.75" customHeight="1">
       <c r="A149" s="1"/>
-      <c r="B149" s="1"/>
+      <c r="B149" s="2"/>
       <c r="C149" s="1"/>
       <c r="D149" s="1"/>
       <c r="E149" s="1"/>
@@ -32998,7 +33019,7 @@
     </row>
     <row r="150" ht="12.75" customHeight="1">
       <c r="A150" s="1"/>
-      <c r="B150" s="1"/>
+      <c r="B150" s="2"/>
       <c r="C150" s="1"/>
       <c r="D150" s="1"/>
       <c r="E150" s="1"/>
@@ -33026,7 +33047,7 @@
     </row>
     <row r="151" ht="12.75" customHeight="1">
       <c r="A151" s="1"/>
-      <c r="B151" s="1"/>
+      <c r="B151" s="2"/>
       <c r="C151" s="1"/>
       <c r="D151" s="1"/>
       <c r="E151" s="1"/>
@@ -33054,7 +33075,7 @@
     </row>
     <row r="152" ht="12.75" customHeight="1">
       <c r="A152" s="1"/>
-      <c r="B152" s="1"/>
+      <c r="B152" s="2"/>
       <c r="C152" s="1"/>
       <c r="D152" s="1"/>
       <c r="E152" s="1"/>
@@ -33082,7 +33103,7 @@
     </row>
     <row r="153" ht="12.75" customHeight="1">
       <c r="A153" s="1"/>
-      <c r="B153" s="1"/>
+      <c r="B153" s="2"/>
       <c r="C153" s="1"/>
       <c r="D153" s="1"/>
       <c r="E153" s="1"/>
@@ -33110,7 +33131,7 @@
     </row>
     <row r="154" ht="12.75" customHeight="1">
       <c r="A154" s="1"/>
-      <c r="B154" s="1"/>
+      <c r="B154" s="2"/>
       <c r="C154" s="1"/>
       <c r="D154" s="1"/>
       <c r="E154" s="1"/>
@@ -33138,7 +33159,7 @@
     </row>
     <row r="155" ht="12.75" customHeight="1">
       <c r="A155" s="1"/>
-      <c r="B155" s="1"/>
+      <c r="B155" s="2"/>
       <c r="C155" s="1"/>
       <c r="D155" s="1"/>
       <c r="E155" s="1"/>
@@ -33166,7 +33187,7 @@
     </row>
     <row r="156" ht="12.75" customHeight="1">
       <c r="A156" s="1"/>
-      <c r="B156" s="1"/>
+      <c r="B156" s="2"/>
       <c r="C156" s="1"/>
       <c r="D156" s="1"/>
       <c r="E156" s="1"/>
@@ -33194,7 +33215,7 @@
     </row>
     <row r="157" ht="12.75" customHeight="1">
       <c r="A157" s="1"/>
-      <c r="B157" s="1"/>
+      <c r="B157" s="2"/>
       <c r="C157" s="1"/>
       <c r="D157" s="1"/>
       <c r="E157" s="1"/>
@@ -33222,7 +33243,7 @@
     </row>
     <row r="158" ht="12.75" customHeight="1">
       <c r="A158" s="1"/>
-      <c r="B158" s="1"/>
+      <c r="B158" s="2"/>
       <c r="C158" s="1"/>
       <c r="D158" s="1"/>
       <c r="E158" s="1"/>
@@ -33250,7 +33271,7 @@
     </row>
     <row r="159" ht="12.75" customHeight="1">
       <c r="A159" s="1"/>
-      <c r="B159" s="1"/>
+      <c r="B159" s="2"/>
       <c r="C159" s="1"/>
       <c r="D159" s="1"/>
       <c r="E159" s="1"/>
@@ -33278,7 +33299,7 @@
     </row>
     <row r="160" ht="12.75" customHeight="1">
       <c r="A160" s="1"/>
-      <c r="B160" s="1"/>
+      <c r="B160" s="2"/>
       <c r="C160" s="1"/>
       <c r="D160" s="1"/>
       <c r="E160" s="1"/>
@@ -33306,7 +33327,7 @@
     </row>
     <row r="161" ht="12.75" customHeight="1">
       <c r="A161" s="1"/>
-      <c r="B161" s="1"/>
+      <c r="B161" s="2"/>
       <c r="C161" s="1"/>
       <c r="D161" s="1"/>
       <c r="E161" s="1"/>
@@ -33334,7 +33355,7 @@
     </row>
     <row r="162" ht="12.75" customHeight="1">
       <c r="A162" s="1"/>
-      <c r="B162" s="1"/>
+      <c r="B162" s="2"/>
       <c r="C162" s="1"/>
       <c r="D162" s="1"/>
       <c r="E162" s="1"/>
@@ -33362,7 +33383,7 @@
     </row>
     <row r="163" ht="12.75" customHeight="1">
       <c r="A163" s="1"/>
-      <c r="B163" s="1"/>
+      <c r="B163" s="2"/>
       <c r="C163" s="1"/>
       <c r="D163" s="1"/>
       <c r="E163" s="1"/>
@@ -33390,7 +33411,7 @@
     </row>
     <row r="164" ht="12.75" customHeight="1">
       <c r="A164" s="1"/>
-      <c r="B164" s="1"/>
+      <c r="B164" s="2"/>
       <c r="C164" s="1"/>
       <c r="D164" s="1"/>
       <c r="E164" s="1"/>
@@ -33418,7 +33439,7 @@
     </row>
     <row r="165" ht="12.75" customHeight="1">
       <c r="A165" s="1"/>
-      <c r="B165" s="1"/>
+      <c r="B165" s="2"/>
       <c r="C165" s="1"/>
       <c r="D165" s="1"/>
       <c r="E165" s="1"/>
@@ -33446,7 +33467,7 @@
     </row>
     <row r="166" ht="12.75" customHeight="1">
       <c r="A166" s="1"/>
-      <c r="B166" s="1"/>
+      <c r="B166" s="2"/>
       <c r="C166" s="1"/>
       <c r="D166" s="1"/>
       <c r="E166" s="1"/>
@@ -33474,7 +33495,7 @@
     </row>
     <row r="167" ht="12.75" customHeight="1">
       <c r="A167" s="1"/>
-      <c r="B167" s="1"/>
+      <c r="B167" s="2"/>
       <c r="C167" s="1"/>
       <c r="D167" s="1"/>
       <c r="E167" s="1"/>
@@ -33502,7 +33523,7 @@
     </row>
     <row r="168" ht="12.75" customHeight="1">
       <c r="A168" s="1"/>
-      <c r="B168" s="1"/>
+      <c r="B168" s="2"/>
       <c r="C168" s="1"/>
       <c r="D168" s="1"/>
       <c r="E168" s="1"/>
@@ -33530,7 +33551,7 @@
     </row>
     <row r="169" ht="12.75" customHeight="1">
       <c r="A169" s="1"/>
-      <c r="B169" s="1"/>
+      <c r="B169" s="2"/>
       <c r="C169" s="1"/>
       <c r="D169" s="1"/>
       <c r="E169" s="1"/>
@@ -33558,7 +33579,7 @@
     </row>
     <row r="170" ht="12.75" customHeight="1">
       <c r="A170" s="1"/>
-      <c r="B170" s="1"/>
+      <c r="B170" s="2"/>
       <c r="C170" s="1"/>
       <c r="D170" s="1"/>
       <c r="E170" s="1"/>
@@ -33586,7 +33607,7 @@
     </row>
     <row r="171" ht="12.75" customHeight="1">
       <c r="A171" s="1"/>
-      <c r="B171" s="1"/>
+      <c r="B171" s="2"/>
       <c r="C171" s="1"/>
       <c r="D171" s="1"/>
       <c r="E171" s="1"/>
@@ -33614,7 +33635,7 @@
     </row>
     <row r="172" ht="12.75" customHeight="1">
       <c r="A172" s="1"/>
-      <c r="B172" s="1"/>
+      <c r="B172" s="2"/>
       <c r="C172" s="1"/>
       <c r="D172" s="1"/>
       <c r="E172" s="1"/>
@@ -33642,7 +33663,7 @@
     </row>
     <row r="173" ht="12.75" customHeight="1">
       <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
+      <c r="B173" s="2"/>
       <c r="C173" s="1"/>
       <c r="D173" s="1"/>
       <c r="E173" s="1"/>
@@ -33670,7 +33691,7 @@
     </row>
     <row r="174" ht="12.75" customHeight="1">
       <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
+      <c r="B174" s="2"/>
       <c r="C174" s="1"/>
       <c r="D174" s="1"/>
       <c r="E174" s="1"/>
@@ -33698,7 +33719,7 @@
     </row>
     <row r="175" ht="12.75" customHeight="1">
       <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
+      <c r="B175" s="2"/>
       <c r="C175" s="1"/>
       <c r="D175" s="1"/>
       <c r="E175" s="1"/>
@@ -33726,7 +33747,7 @@
     </row>
     <row r="176" ht="12.75" customHeight="1">
       <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
+      <c r="B176" s="2"/>
       <c r="C176" s="1"/>
       <c r="D176" s="1"/>
       <c r="E176" s="1"/>
@@ -33754,7 +33775,7 @@
     </row>
     <row r="177" ht="12.75" customHeight="1">
       <c r="A177" s="1"/>
-      <c r="B177" s="1"/>
+      <c r="B177" s="2"/>
       <c r="C177" s="1"/>
       <c r="D177" s="1"/>
       <c r="E177" s="1"/>
@@ -33782,7 +33803,7 @@
     </row>
     <row r="178" ht="12.75" customHeight="1">
       <c r="A178" s="1"/>
-      <c r="B178" s="1"/>
+      <c r="B178" s="2"/>
       <c r="C178" s="1"/>
       <c r="D178" s="1"/>
       <c r="E178" s="1"/>
@@ -33810,7 +33831,7 @@
     </row>
     <row r="179" ht="12.75" customHeight="1">
       <c r="A179" s="1"/>
-      <c r="B179" s="1"/>
+      <c r="B179" s="2"/>
       <c r="C179" s="1"/>
       <c r="D179" s="1"/>
       <c r="E179" s="1"/>
@@ -33838,7 +33859,7 @@
     </row>
     <row r="180" ht="12.75" customHeight="1">
       <c r="A180" s="1"/>
-      <c r="B180" s="1"/>
+      <c r="B180" s="2"/>
       <c r="C180" s="1"/>
       <c r="D180" s="1"/>
       <c r="E180" s="1"/>
@@ -33866,7 +33887,7 @@
     </row>
     <row r="181" ht="12.75" customHeight="1">
       <c r="A181" s="1"/>
-      <c r="B181" s="1"/>
+      <c r="B181" s="2"/>
       <c r="C181" s="1"/>
       <c r="D181" s="1"/>
       <c r="E181" s="1"/>
@@ -33894,7 +33915,7 @@
     </row>
     <row r="182" ht="12.75" customHeight="1">
       <c r="A182" s="1"/>
-      <c r="B182" s="1"/>
+      <c r="B182" s="2"/>
       <c r="C182" s="1"/>
       <c r="D182" s="1"/>
       <c r="E182" s="1"/>
@@ -33922,7 +33943,7 @@
     </row>
     <row r="183" ht="12.75" customHeight="1">
       <c r="A183" s="1"/>
-      <c r="B183" s="1"/>
+      <c r="B183" s="2"/>
       <c r="C183" s="1"/>
       <c r="D183" s="1"/>
       <c r="E183" s="1"/>
@@ -33950,7 +33971,7 @@
     </row>
     <row r="184" ht="12.75" customHeight="1">
       <c r="A184" s="1"/>
-      <c r="B184" s="1"/>
+      <c r="B184" s="2"/>
       <c r="C184" s="1"/>
       <c r="D184" s="1"/>
       <c r="E184" s="1"/>
@@ -33978,7 +33999,7 @@
     </row>
     <row r="185" ht="12.75" customHeight="1">
       <c r="A185" s="1"/>
-      <c r="B185" s="1"/>
+      <c r="B185" s="2"/>
       <c r="C185" s="1"/>
       <c r="D185" s="1"/>
       <c r="E185" s="1"/>
@@ -34006,7 +34027,7 @@
     </row>
     <row r="186" ht="12.75" customHeight="1">
       <c r="A186" s="1"/>
-      <c r="B186" s="1"/>
+      <c r="B186" s="2"/>
       <c r="C186" s="1"/>
       <c r="D186" s="1"/>
       <c r="E186" s="1"/>
@@ -34034,7 +34055,7 @@
     </row>
     <row r="187" ht="12.75" customHeight="1">
       <c r="A187" s="1"/>
-      <c r="B187" s="1"/>
+      <c r="B187" s="2"/>
       <c r="C187" s="1"/>
       <c r="D187" s="1"/>
       <c r="E187" s="1"/>
@@ -34062,7 +34083,7 @@
     </row>
     <row r="188" ht="12.75" customHeight="1">
       <c r="A188" s="1"/>
-      <c r="B188" s="1"/>
+      <c r="B188" s="2"/>
       <c r="C188" s="1"/>
       <c r="D188" s="1"/>
       <c r="E188" s="1"/>
@@ -34090,7 +34111,7 @@
     </row>
     <row r="189" ht="12.75" customHeight="1">
       <c r="A189" s="1"/>
-      <c r="B189" s="1"/>
+      <c r="B189" s="2"/>
       <c r="C189" s="1"/>
       <c r="D189" s="1"/>
       <c r="E189" s="1"/>
@@ -34118,7 +34139,7 @@
     </row>
     <row r="190" ht="12.75" customHeight="1">
       <c r="A190" s="1"/>
-      <c r="B190" s="1"/>
+      <c r="B190" s="2"/>
       <c r="C190" s="1"/>
       <c r="D190" s="1"/>
       <c r="E190" s="1"/>
@@ -34146,7 +34167,7 @@
     </row>
     <row r="191" ht="12.75" customHeight="1">
       <c r="A191" s="1"/>
-      <c r="B191" s="1"/>
+      <c r="B191" s="2"/>
       <c r="C191" s="1"/>
       <c r="D191" s="1"/>
       <c r="E191" s="1"/>
@@ -34174,7 +34195,7 @@
     </row>
     <row r="192" ht="12.75" customHeight="1">
       <c r="A192" s="1"/>
-      <c r="B192" s="1"/>
+      <c r="B192" s="2"/>
       <c r="C192" s="1"/>
       <c r="D192" s="1"/>
       <c r="E192" s="1"/>
@@ -34202,7 +34223,7 @@
     </row>
     <row r="193" ht="12.75" customHeight="1">
       <c r="A193" s="1"/>
-      <c r="B193" s="1"/>
+      <c r="B193" s="2"/>
       <c r="C193" s="1"/>
       <c r="D193" s="1"/>
       <c r="E193" s="1"/>
@@ -34230,7 +34251,7 @@
     </row>
     <row r="194" ht="12.75" customHeight="1">
       <c r="A194" s="1"/>
-      <c r="B194" s="1"/>
+      <c r="B194" s="2"/>
       <c r="C194" s="1"/>
       <c r="D194" s="1"/>
       <c r="E194" s="1"/>
@@ -34258,7 +34279,7 @@
     </row>
     <row r="195" ht="12.75" customHeight="1">
       <c r="A195" s="1"/>
-      <c r="B195" s="1"/>
+      <c r="B195" s="2"/>
       <c r="C195" s="1"/>
       <c r="D195" s="1"/>
       <c r="E195" s="1"/>
@@ -34286,7 +34307,7 @@
     </row>
     <row r="196" ht="12.75" customHeight="1">
       <c r="A196" s="1"/>
-      <c r="B196" s="1"/>
+      <c r="B196" s="2"/>
       <c r="C196" s="1"/>
       <c r="D196" s="1"/>
       <c r="E196" s="1"/>
@@ -34314,7 +34335,7 @@
     </row>
     <row r="197" ht="12.75" customHeight="1">
       <c r="A197" s="1"/>
-      <c r="B197" s="1"/>
+      <c r="B197" s="2"/>
       <c r="C197" s="1"/>
       <c r="D197" s="1"/>
       <c r="E197" s="1"/>
@@ -34342,7 +34363,7 @@
     </row>
     <row r="198" ht="12.75" customHeight="1">
       <c r="A198" s="1"/>
-      <c r="B198" s="1"/>
+      <c r="B198" s="2"/>
       <c r="C198" s="1"/>
       <c r="D198" s="1"/>
       <c r="E198" s="1"/>
@@ -34370,7 +34391,7 @@
     </row>
     <row r="199" ht="12.75" customHeight="1">
       <c r="A199" s="1"/>
-      <c r="B199" s="1"/>
+      <c r="B199" s="2"/>
       <c r="C199" s="1"/>
       <c r="D199" s="1"/>
       <c r="E199" s="1"/>
@@ -34398,7 +34419,7 @@
     </row>
     <row r="200" ht="12.75" customHeight="1">
       <c r="A200" s="1"/>
-      <c r="B200" s="1"/>
+      <c r="B200" s="2"/>
       <c r="C200" s="1"/>
       <c r="D200" s="1"/>
       <c r="E200" s="1"/>
@@ -34426,7 +34447,7 @@
     </row>
     <row r="201" ht="12.75" customHeight="1">
       <c r="A201" s="1"/>
-      <c r="B201" s="1"/>
+      <c r="B201" s="2"/>
       <c r="C201" s="1"/>
       <c r="D201" s="1"/>
       <c r="E201" s="1"/>
@@ -34454,7 +34475,7 @@
     </row>
     <row r="202" ht="12.75" customHeight="1">
       <c r="A202" s="1"/>
-      <c r="B202" s="1"/>
+      <c r="B202" s="2"/>
       <c r="C202" s="1"/>
       <c r="D202" s="1"/>
       <c r="E202" s="1"/>
@@ -34482,7 +34503,7 @@
     </row>
     <row r="203" ht="12.75" customHeight="1">
       <c r="A203" s="1"/>
-      <c r="B203" s="1"/>
+      <c r="B203" s="2"/>
       <c r="C203" s="1"/>
       <c r="D203" s="1"/>
       <c r="E203" s="1"/>
@@ -34510,7 +34531,7 @@
     </row>
     <row r="204" ht="12.75" customHeight="1">
       <c r="A204" s="1"/>
-      <c r="B204" s="1"/>
+      <c r="B204" s="2"/>
       <c r="C204" s="1"/>
       <c r="D204" s="1"/>
       <c r="E204" s="1"/>
@@ -34538,7 +34559,7 @@
     </row>
     <row r="205" ht="12.75" customHeight="1">
       <c r="A205" s="1"/>
-      <c r="B205" s="1"/>
+      <c r="B205" s="2"/>
       <c r="C205" s="1"/>
       <c r="D205" s="1"/>
       <c r="E205" s="1"/>
@@ -34566,7 +34587,7 @@
     </row>
     <row r="206" ht="12.75" customHeight="1">
       <c r="A206" s="1"/>
-      <c r="B206" s="1"/>
+      <c r="B206" s="2"/>
       <c r="C206" s="1"/>
       <c r="D206" s="1"/>
       <c r="E206" s="1"/>
@@ -34594,7 +34615,7 @@
     </row>
     <row r="207" ht="12.75" customHeight="1">
       <c r="A207" s="1"/>
-      <c r="B207" s="1"/>
+      <c r="B207" s="2"/>
       <c r="C207" s="1"/>
       <c r="D207" s="1"/>
       <c r="E207" s="1"/>
@@ -34622,7 +34643,7 @@
     </row>
     <row r="208" ht="12.75" customHeight="1">
       <c r="A208" s="1"/>
-      <c r="B208" s="1"/>
+      <c r="B208" s="2"/>
       <c r="C208" s="1"/>
       <c r="D208" s="1"/>
       <c r="E208" s="1"/>
@@ -34650,7 +34671,7 @@
     </row>
     <row r="209" ht="12.75" customHeight="1">
       <c r="A209" s="1"/>
-      <c r="B209" s="1"/>
+      <c r="B209" s="2"/>
       <c r="C209" s="1"/>
       <c r="D209" s="1"/>
       <c r="E209" s="1"/>
@@ -34678,7 +34699,7 @@
     </row>
     <row r="210" ht="12.75" customHeight="1">
       <c r="A210" s="1"/>
-      <c r="B210" s="1"/>
+      <c r="B210" s="2"/>
       <c r="C210" s="1"/>
       <c r="D210" s="1"/>
       <c r="E210" s="1"/>
@@ -34706,7 +34727,7 @@
     </row>
     <row r="211" ht="12.75" customHeight="1">
       <c r="A211" s="1"/>
-      <c r="B211" s="1"/>
+      <c r="B211" s="2"/>
       <c r="C211" s="1"/>
       <c r="D211" s="1"/>
       <c r="E211" s="1"/>
@@ -34734,7 +34755,7 @@
     </row>
     <row r="212" ht="12.75" customHeight="1">
       <c r="A212" s="1"/>
-      <c r="B212" s="1"/>
+      <c r="B212" s="2"/>
       <c r="C212" s="1"/>
       <c r="D212" s="1"/>
       <c r="E212" s="1"/>
@@ -34762,7 +34783,7 @@
     </row>
     <row r="213" ht="12.75" customHeight="1">
       <c r="A213" s="1"/>
-      <c r="B213" s="1"/>
+      <c r="B213" s="2"/>
       <c r="C213" s="1"/>
       <c r="D213" s="1"/>
       <c r="E213" s="1"/>
@@ -34790,7 +34811,7 @@
     </row>
     <row r="214" ht="12.75" customHeight="1">
       <c r="A214" s="1"/>
-      <c r="B214" s="1"/>
+      <c r="B214" s="2"/>
       <c r="C214" s="1"/>
       <c r="D214" s="1"/>
       <c r="E214" s="1"/>
@@ -34818,7 +34839,7 @@
     </row>
     <row r="215" ht="12.75" customHeight="1">
       <c r="A215" s="1"/>
-      <c r="B215" s="1"/>
+      <c r="B215" s="2"/>
       <c r="C215" s="1"/>
       <c r="D215" s="1"/>
       <c r="E215" s="1"/>
@@ -34846,7 +34867,7 @@
     </row>
     <row r="216" ht="12.75" customHeight="1">
       <c r="A216" s="1"/>
-      <c r="B216" s="1"/>
+      <c r="B216" s="2"/>
       <c r="C216" s="1"/>
       <c r="D216" s="1"/>
       <c r="E216" s="1"/>
@@ -34874,7 +34895,7 @@
     </row>
     <row r="217" ht="12.75" customHeight="1">
       <c r="A217" s="1"/>
-      <c r="B217" s="1"/>
+      <c r="B217" s="2"/>
       <c r="C217" s="1"/>
       <c r="D217" s="1"/>
       <c r="E217" s="1"/>
@@ -34902,7 +34923,7 @@
     </row>
     <row r="218" ht="12.75" customHeight="1">
       <c r="A218" s="1"/>
-      <c r="B218" s="1"/>
+      <c r="B218" s="2"/>
       <c r="C218" s="1"/>
       <c r="D218" s="1"/>
       <c r="E218" s="1"/>
@@ -34930,7 +34951,7 @@
     </row>
     <row r="219" ht="12.75" customHeight="1">
       <c r="A219" s="1"/>
-      <c r="B219" s="1"/>
+      <c r="B219" s="2"/>
       <c r="C219" s="1"/>
       <c r="D219" s="1"/>
       <c r="E219" s="1"/>
@@ -34958,7 +34979,7 @@
     </row>
     <row r="220" ht="12.75" customHeight="1">
       <c r="A220" s="1"/>
-      <c r="B220" s="1"/>
+      <c r="B220" s="2"/>
       <c r="C220" s="1"/>
       <c r="D220" s="1"/>
       <c r="E220" s="1"/>
@@ -34986,7 +35007,7 @@
     </row>
     <row r="221" ht="12.75" customHeight="1">
       <c r="A221" s="1"/>
-      <c r="B221" s="1"/>
+      <c r="B221" s="2"/>
       <c r="C221" s="1"/>
       <c r="D221" s="1"/>
       <c r="E221" s="1"/>
@@ -35014,7 +35035,7 @@
     </row>
     <row r="222" ht="12.75" customHeight="1">
       <c r="A222" s="1"/>
-      <c r="B222" s="1"/>
+      <c r="B222" s="2"/>
       <c r="C222" s="1"/>
       <c r="D222" s="1"/>
       <c r="E222" s="1"/>
@@ -35042,7 +35063,7 @@
     </row>
     <row r="223" ht="12.75" customHeight="1">
       <c r="A223" s="1"/>
-      <c r="B223" s="1"/>
+      <c r="B223" s="2"/>
       <c r="C223" s="1"/>
       <c r="D223" s="1"/>
       <c r="E223" s="1"/>
@@ -35070,7 +35091,7 @@
     </row>
     <row r="224" ht="12.75" customHeight="1">
       <c r="A224" s="1"/>
-      <c r="B224" s="1"/>
+      <c r="B224" s="2"/>
       <c r="C224" s="1"/>
       <c r="D224" s="1"/>
       <c r="E224" s="1"/>
@@ -35098,7 +35119,7 @@
     </row>
     <row r="225" ht="12.75" customHeight="1">
       <c r="A225" s="1"/>
-      <c r="B225" s="1"/>
+      <c r="B225" s="2"/>
       <c r="C225" s="1"/>
       <c r="D225" s="1"/>
       <c r="E225" s="1"/>
@@ -35126,7 +35147,7 @@
     </row>
     <row r="226" ht="12.75" customHeight="1">
       <c r="A226" s="1"/>
-      <c r="B226" s="1"/>
+      <c r="B226" s="2"/>
       <c r="C226" s="1"/>
       <c r="D226" s="1"/>
       <c r="E226" s="1"/>
@@ -35154,7 +35175,7 @@
     </row>
     <row r="227" ht="12.75" customHeight="1">
       <c r="A227" s="1"/>
-      <c r="B227" s="1"/>
+      <c r="B227" s="2"/>
       <c r="C227" s="1"/>
       <c r="D227" s="1"/>
       <c r="E227" s="1"/>
@@ -35182,7 +35203,7 @@
     </row>
     <row r="228" ht="12.75" customHeight="1">
       <c r="A228" s="1"/>
-      <c r="B228" s="1"/>
+      <c r="B228" s="2"/>
       <c r="C228" s="1"/>
       <c r="D228" s="1"/>
       <c r="E228" s="1"/>
@@ -35210,7 +35231,7 @@
     </row>
     <row r="229" ht="12.75" customHeight="1">
       <c r="A229" s="1"/>
-      <c r="B229" s="1"/>
+      <c r="B229" s="2"/>
       <c r="C229" s="1"/>
       <c r="D229" s="1"/>
       <c r="E229" s="1"/>
@@ -35238,7 +35259,7 @@
     </row>
     <row r="230" ht="12.75" customHeight="1">
       <c r="A230" s="1"/>
-      <c r="B230" s="1"/>
+      <c r="B230" s="2"/>
       <c r="C230" s="1"/>
       <c r="D230" s="1"/>
       <c r="E230" s="1"/>
@@ -35266,7 +35287,7 @@
     </row>
     <row r="231" ht="12.75" customHeight="1">
       <c r="A231" s="1"/>
-      <c r="B231" s="1"/>
+      <c r="B231" s="2"/>
       <c r="C231" s="1"/>
       <c r="D231" s="1"/>
       <c r="E231" s="1"/>
@@ -35294,7 +35315,7 @@
     </row>
     <row r="232" ht="12.75" customHeight="1">
       <c r="A232" s="1"/>
-      <c r="B232" s="1"/>
+      <c r="B232" s="2"/>
       <c r="C232" s="1"/>
       <c r="D232" s="1"/>
       <c r="E232" s="1"/>
@@ -35322,7 +35343,7 @@
     </row>
     <row r="233" ht="12.75" customHeight="1">
       <c r="A233" s="1"/>
-      <c r="B233" s="1"/>
+      <c r="B233" s="2"/>
       <c r="C233" s="1"/>
       <c r="D233" s="1"/>
       <c r="E233" s="1"/>
@@ -35350,7 +35371,7 @@
     </row>
     <row r="234" ht="12.75" customHeight="1">
       <c r="A234" s="1"/>
-      <c r="B234" s="1"/>
+      <c r="B234" s="2"/>
       <c r="C234" s="1"/>
       <c r="D234" s="1"/>
       <c r="E234" s="1"/>
@@ -35378,7 +35399,7 @@
     </row>
     <row r="235" ht="12.75" customHeight="1">
       <c r="A235" s="1"/>
-      <c r="B235" s="1"/>
+      <c r="B235" s="2"/>
       <c r="C235" s="1"/>
       <c r="D235" s="1"/>
       <c r="E235" s="1"/>
@@ -35406,7 +35427,7 @@
     </row>
     <row r="236" ht="12.75" customHeight="1">
       <c r="A236" s="1"/>
-      <c r="B236" s="1"/>
+      <c r="B236" s="2"/>
       <c r="C236" s="1"/>
       <c r="D236" s="1"/>
       <c r="E236" s="1"/>
@@ -35434,7 +35455,7 @@
     </row>
     <row r="237" ht="12.75" customHeight="1">
       <c r="A237" s="1"/>
-      <c r="B237" s="1"/>
+      <c r="B237" s="2"/>
       <c r="C237" s="1"/>
       <c r="D237" s="1"/>
       <c r="E237" s="1"/>
@@ -35462,7 +35483,7 @@
     </row>
     <row r="238" ht="12.75" customHeight="1">
       <c r="A238" s="1"/>
-      <c r="B238" s="1"/>
+      <c r="B238" s="2"/>
       <c r="C238" s="1"/>
       <c r="D238" s="1"/>
       <c r="E238" s="1"/>
@@ -35490,7 +35511,7 @@
     </row>
     <row r="239" ht="12.75" customHeight="1">
       <c r="A239" s="1"/>
-      <c r="B239" s="1"/>
+      <c r="B239" s="2"/>
       <c r="C239" s="1"/>
       <c r="D239" s="1"/>
       <c r="E239" s="1"/>
@@ -35518,7 +35539,7 @@
     </row>
     <row r="240" ht="12.75" customHeight="1">
       <c r="A240" s="1"/>
-      <c r="B240" s="1"/>
+      <c r="B240" s="2"/>
       <c r="C240" s="1"/>
       <c r="D240" s="1"/>
       <c r="E240" s="1"/>
@@ -35546,7 +35567,7 @@
     </row>
     <row r="241" ht="12.75" customHeight="1">
       <c r="A241" s="1"/>
-      <c r="B241" s="1"/>
+      <c r="B241" s="2"/>
       <c r="C241" s="1"/>
       <c r="D241" s="1"/>
       <c r="E241" s="1"/>
@@ -35574,7 +35595,7 @@
     </row>
     <row r="242" ht="12.75" customHeight="1">
       <c r="A242" s="1"/>
-      <c r="B242" s="1"/>
+      <c r="B242" s="2"/>
       <c r="C242" s="1"/>
       <c r="D242" s="1"/>
       <c r="E242" s="1"/>
@@ -35602,7 +35623,7 @@
     </row>
     <row r="243" ht="12.75" customHeight="1">
       <c r="A243" s="1"/>
-      <c r="B243" s="1"/>
+      <c r="B243" s="2"/>
       <c r="C243" s="1"/>
       <c r="D243" s="1"/>
       <c r="E243" s="1"/>
@@ -35630,7 +35651,7 @@
     </row>
     <row r="244" ht="12.75" customHeight="1">
       <c r="A244" s="1"/>
-      <c r="B244" s="1"/>
+      <c r="B244" s="2"/>
       <c r="C244" s="1"/>
       <c r="D244" s="1"/>
       <c r="E244" s="1"/>
@@ -35658,7 +35679,7 @@
     </row>
     <row r="245" ht="12.75" customHeight="1">
       <c r="A245" s="1"/>
-      <c r="B245" s="1"/>
+      <c r="B245" s="2"/>
       <c r="C245" s="1"/>
       <c r="D245" s="1"/>
       <c r="E245" s="1"/>
@@ -35686,7 +35707,7 @@
     </row>
     <row r="246" ht="12.75" customHeight="1">
       <c r="A246" s="1"/>
-      <c r="B246" s="1"/>
+      <c r="B246" s="2"/>
       <c r="C246" s="1"/>
       <c r="D246" s="1"/>
       <c r="E246" s="1"/>
@@ -35714,7 +35735,7 @@
     </row>
     <row r="247" ht="12.75" customHeight="1">
       <c r="A247" s="1"/>
-      <c r="B247" s="1"/>
+      <c r="B247" s="2"/>
       <c r="C247" s="1"/>
       <c r="D247" s="1"/>
       <c r="E247" s="1"/>
@@ -35742,7 +35763,7 @@
     </row>
     <row r="248" ht="12.75" customHeight="1">
       <c r="A248" s="1"/>
-      <c r="B248" s="1"/>
+      <c r="B248" s="2"/>
       <c r="C248" s="1"/>
       <c r="D248" s="1"/>
       <c r="E248" s="1"/>
@@ -35770,7 +35791,7 @@
     </row>
     <row r="249" ht="12.75" customHeight="1">
       <c r="A249" s="1"/>
-      <c r="B249" s="1"/>
+      <c r="B249" s="2"/>
       <c r="C249" s="1"/>
       <c r="D249" s="1"/>
       <c r="E249" s="1"/>
@@ -35798,7 +35819,7 @@
     </row>
     <row r="250" ht="12.75" customHeight="1">
       <c r="A250" s="1"/>
-      <c r="B250" s="1"/>
+      <c r="B250" s="2"/>
       <c r="C250" s="1"/>
       <c r="D250" s="1"/>
       <c r="E250" s="1"/>
@@ -35826,7 +35847,7 @@
     </row>
     <row r="251" ht="12.75" customHeight="1">
       <c r="A251" s="1"/>
-      <c r="B251" s="1"/>
+      <c r="B251" s="2"/>
       <c r="C251" s="1"/>
       <c r="D251" s="1"/>
       <c r="E251" s="1"/>
@@ -35854,7 +35875,7 @@
     </row>
     <row r="252" ht="12.75" customHeight="1">
       <c r="A252" s="1"/>
-      <c r="B252" s="1"/>
+      <c r="B252" s="2"/>
       <c r="C252" s="1"/>
       <c r="D252" s="1"/>
       <c r="E252" s="1"/>
@@ -35882,7 +35903,7 @@
     </row>
     <row r="253" ht="12.75" customHeight="1">
       <c r="A253" s="1"/>
-      <c r="B253" s="1"/>
+      <c r="B253" s="2"/>
       <c r="C253" s="1"/>
       <c r="D253" s="1"/>
       <c r="E253" s="1"/>
@@ -35910,7 +35931,7 @@
     </row>
     <row r="254" ht="12.75" customHeight="1">
       <c r="A254" s="1"/>
-      <c r="B254" s="1"/>
+      <c r="B254" s="2"/>
       <c r="C254" s="1"/>
       <c r="D254" s="1"/>
       <c r="E254" s="1"/>
@@ -35938,7 +35959,7 @@
     </row>
     <row r="255" ht="12.75" customHeight="1">
       <c r="A255" s="1"/>
-      <c r="B255" s="1"/>
+      <c r="B255" s="2"/>
       <c r="C255" s="1"/>
       <c r="D255" s="1"/>
       <c r="E255" s="1"/>
@@ -35966,7 +35987,7 @@
     </row>
     <row r="256" ht="12.75" customHeight="1">
       <c r="A256" s="1"/>
-      <c r="B256" s="1"/>
+      <c r="B256" s="2"/>
       <c r="C256" s="1"/>
       <c r="D256" s="1"/>
       <c r="E256" s="1"/>
@@ -35994,7 +36015,7 @@
     </row>
     <row r="257" ht="12.75" customHeight="1">
       <c r="A257" s="1"/>
-      <c r="B257" s="1"/>
+      <c r="B257" s="2"/>
       <c r="C257" s="1"/>
       <c r="D257" s="1"/>
       <c r="E257" s="1"/>
@@ -36022,7 +36043,7 @@
     </row>
     <row r="258" ht="12.75" customHeight="1">
       <c r="A258" s="1"/>
-      <c r="B258" s="1"/>
+      <c r="B258" s="2"/>
       <c r="C258" s="1"/>
       <c r="D258" s="1"/>
       <c r="E258" s="1"/>
@@ -36050,7 +36071,7 @@
     </row>
     <row r="259" ht="12.75" customHeight="1">
       <c r="A259" s="1"/>
-      <c r="B259" s="1"/>
+      <c r="B259" s="2"/>
       <c r="C259" s="1"/>
       <c r="D259" s="1"/>
       <c r="E259" s="1"/>
@@ -36078,7 +36099,7 @@
     </row>
     <row r="260" ht="12.75" customHeight="1">
       <c r="A260" s="1"/>
-      <c r="B260" s="1"/>
+      <c r="B260" s="2"/>
       <c r="C260" s="1"/>
       <c r="D260" s="1"/>
       <c r="E260" s="1"/>
@@ -36106,7 +36127,7 @@
     </row>
     <row r="261" ht="12.75" customHeight="1">
       <c r="A261" s="1"/>
-      <c r="B261" s="1"/>
+      <c r="B261" s="2"/>
       <c r="C261" s="1"/>
       <c r="D261" s="1"/>
       <c r="E261" s="1"/>
@@ -36134,7 +36155,7 @@
     </row>
     <row r="262" ht="12.75" customHeight="1">
       <c r="A262" s="1"/>
-      <c r="B262" s="1"/>
+      <c r="B262" s="2"/>
       <c r="C262" s="1"/>
       <c r="D262" s="1"/>
       <c r="E262" s="1"/>
@@ -36162,7 +36183,7 @@
     </row>
     <row r="263" ht="12.75" customHeight="1">
       <c r="A263" s="1"/>
-      <c r="B263" s="1"/>
+      <c r="B263" s="2"/>
       <c r="C263" s="1"/>
       <c r="D263" s="1"/>
       <c r="E263" s="1"/>
@@ -36190,7 +36211,7 @@
     </row>
     <row r="264" ht="12.75" customHeight="1">
       <c r="A264" s="1"/>
-      <c r="B264" s="1"/>
+      <c r="B264" s="2"/>
       <c r="C264" s="1"/>
       <c r="D264" s="1"/>
       <c r="E264" s="1"/>
@@ -36218,7 +36239,7 @@
     </row>
     <row r="265" ht="12.75" customHeight="1">
       <c r="A265" s="1"/>
-      <c r="B265" s="1"/>
+      <c r="B265" s="2"/>
       <c r="C265" s="1"/>
       <c r="D265" s="1"/>
       <c r="E265" s="1"/>
@@ -36246,7 +36267,7 @@
     </row>
     <row r="266" ht="12.75" customHeight="1">
       <c r="A266" s="1"/>
-      <c r="B266" s="1"/>
+      <c r="B266" s="2"/>
       <c r="C266" s="1"/>
       <c r="D266" s="1"/>
       <c r="E266" s="1"/>
@@ -36274,7 +36295,7 @@
     </row>
     <row r="267" ht="12.75" customHeight="1">
       <c r="A267" s="1"/>
-      <c r="B267" s="1"/>
+      <c r="B267" s="2"/>
       <c r="C267" s="1"/>
       <c r="D267" s="1"/>
       <c r="E267" s="1"/>
@@ -36302,7 +36323,7 @@
     </row>
     <row r="268" ht="12.75" customHeight="1">
       <c r="A268" s="1"/>
-      <c r="B268" s="1"/>
+      <c r="B268" s="2"/>
       <c r="C268" s="1"/>
       <c r="D268" s="1"/>
       <c r="E268" s="1"/>
@@ -36330,7 +36351,7 @@
     </row>
     <row r="269" ht="12.75" customHeight="1">
       <c r="A269" s="1"/>
-      <c r="B269" s="1"/>
+      <c r="B269" s="2"/>
       <c r="C269" s="1"/>
       <c r="D269" s="1"/>
       <c r="E269" s="1"/>
@@ -36358,7 +36379,7 @@
     </row>
     <row r="270" ht="12.75" customHeight="1">
       <c r="A270" s="1"/>
-      <c r="B270" s="1"/>
+      <c r="B270" s="2"/>
       <c r="C270" s="1"/>
       <c r="D270" s="1"/>
       <c r="E270" s="1"/>
@@ -36386,7 +36407,7 @@
     </row>
     <row r="271" ht="12.75" customHeight="1">
       <c r="A271" s="1"/>
-      <c r="B271" s="1"/>
+      <c r="B271" s="2"/>
       <c r="C271" s="1"/>
       <c r="D271" s="1"/>
       <c r="E271" s="1"/>
@@ -36414,7 +36435,7 @@
     </row>
     <row r="272" ht="12.75" customHeight="1">
       <c r="A272" s="1"/>
-      <c r="B272" s="1"/>
+      <c r="B272" s="2"/>
       <c r="C272" s="1"/>
       <c r="D272" s="1"/>
       <c r="E272" s="1"/>
@@ -36442,7 +36463,7 @@
     </row>
     <row r="273" ht="12.75" customHeight="1">
       <c r="A273" s="1"/>
-      <c r="B273" s="1"/>
+      <c r="B273" s="2"/>
       <c r="C273" s="1"/>
       <c r="D273" s="1"/>
       <c r="E273" s="1"/>
@@ -36470,7 +36491,7 @@
     </row>
     <row r="274" ht="12.75" customHeight="1">
       <c r="A274" s="1"/>
-      <c r="B274" s="1"/>
+      <c r="B274" s="2"/>
       <c r="C274" s="1"/>
       <c r="D274" s="1"/>
       <c r="E274" s="1"/>
@@ -36498,7 +36519,7 @@
     </row>
     <row r="275" ht="12.75" customHeight="1">
       <c r="A275" s="1"/>
-      <c r="B275" s="1"/>
+      <c r="B275" s="2"/>
       <c r="C275" s="1"/>
       <c r="D275" s="1"/>
       <c r="E275" s="1"/>
@@ -36526,7 +36547,7 @@
     </row>
     <row r="276" ht="12.75" customHeight="1">
       <c r="A276" s="1"/>
-      <c r="B276" s="1"/>
+      <c r="B276" s="2"/>
       <c r="C276" s="1"/>
       <c r="D276" s="1"/>
       <c r="E276" s="1"/>
@@ -36554,7 +36575,7 @@
     </row>
     <row r="277" ht="12.75" customHeight="1">
       <c r="A277" s="1"/>
-      <c r="B277" s="1"/>
+      <c r="B277" s="2"/>
       <c r="C277" s="1"/>
       <c r="D277" s="1"/>
       <c r="E277" s="1"/>
@@ -36582,7 +36603,7 @@
     </row>
     <row r="278" ht="12.75" customHeight="1">
       <c r="A278" s="1"/>
-      <c r="B278" s="1"/>
+      <c r="B278" s="2"/>
       <c r="C278" s="1"/>
       <c r="D278" s="1"/>
       <c r="E278" s="1"/>
@@ -36610,7 +36631,7 @@
     </row>
     <row r="279" ht="12.75" customHeight="1">
       <c r="A279" s="1"/>
-      <c r="B279" s="1"/>
+      <c r="B279" s="2"/>
       <c r="C279" s="1"/>
       <c r="D279" s="1"/>
       <c r="E279" s="1"/>
@@ -36638,7 +36659,7 @@
     </row>
     <row r="280" ht="12.75" customHeight="1">
       <c r="A280" s="1"/>
-      <c r="B280" s="1"/>
+      <c r="B280" s="2"/>
       <c r="C280" s="1"/>
       <c r="D280" s="1"/>
       <c r="E280" s="1"/>
@@ -36666,7 +36687,7 @@
     </row>
     <row r="281" ht="12.75" customHeight="1">
       <c r="A281" s="1"/>
-      <c r="B281" s="1"/>
+      <c r="B281" s="2"/>
       <c r="C281" s="1"/>
       <c r="D281" s="1"/>
       <c r="E281" s="1"/>
@@ -36694,7 +36715,7 @@
     </row>
     <row r="282" ht="12.75" customHeight="1">
       <c r="A282" s="1"/>
-      <c r="B282" s="1"/>
+      <c r="B282" s="2"/>
       <c r="C282" s="1"/>
       <c r="D282" s="1"/>
       <c r="E282" s="1"/>
@@ -36722,7 +36743,7 @@
     </row>
     <row r="283" ht="12.75" customHeight="1">
       <c r="A283" s="1"/>
-      <c r="B283" s="1"/>
+      <c r="B283" s="2"/>
       <c r="C283" s="1"/>
       <c r="D283" s="1"/>
       <c r="E283" s="1"/>
@@ -36750,7 +36771,7 @@
     </row>
     <row r="284" ht="12.75" customHeight="1">
       <c r="A284" s="1"/>
-      <c r="B284" s="1"/>
+      <c r="B284" s="2"/>
       <c r="C284" s="1"/>
       <c r="D284" s="1"/>
       <c r="E284" s="1"/>
@@ -36778,7 +36799,7 @@
     </row>
     <row r="285" ht="12.75" customHeight="1">
       <c r="A285" s="1"/>
-      <c r="B285" s="1"/>
+      <c r="B285" s="2"/>
       <c r="C285" s="1"/>
       <c r="D285" s="1"/>
       <c r="E285" s="1"/>
@@ -36806,7 +36827,7 @@
     </row>
     <row r="286" ht="12.75" customHeight="1">
       <c r="A286" s="1"/>
-      <c r="B286" s="1"/>
+      <c r="B286" s="2"/>
       <c r="C286" s="1"/>
       <c r="D286" s="1"/>
       <c r="E286" s="1"/>
@@ -36834,7 +36855,7 @@
     </row>
     <row r="287" ht="12.75" customHeight="1">
       <c r="A287" s="1"/>
-      <c r="B287" s="1"/>
+      <c r="B287" s="2"/>
       <c r="C287" s="1"/>
       <c r="D287" s="1"/>
       <c r="E287" s="1"/>
@@ -36862,7 +36883,7 @@
     </row>
     <row r="288" ht="12.75" customHeight="1">
       <c r="A288" s="1"/>
-      <c r="B288" s="1"/>
+      <c r="B288" s="2"/>
       <c r="C288" s="1"/>
       <c r="D288" s="1"/>
       <c r="E288" s="1"/>
@@ -36890,7 +36911,7 @@
     </row>
     <row r="289" ht="12.75" customHeight="1">
       <c r="A289" s="1"/>
-      <c r="B289" s="1"/>
+      <c r="B289" s="2"/>
       <c r="C289" s="1"/>
       <c r="D289" s="1"/>
       <c r="E289" s="1"/>
@@ -36918,7 +36939,7 @@
     </row>
     <row r="290" ht="12.75" customHeight="1">
       <c r="A290" s="1"/>
-      <c r="B290" s="1"/>
+      <c r="B290" s="2"/>
       <c r="C290" s="1"/>
       <c r="D290" s="1"/>
       <c r="E290" s="1"/>
@@ -36946,7 +36967,7 @@
     </row>
     <row r="291" ht="12.75" customHeight="1">
       <c r="A291" s="1"/>
-      <c r="B291" s="1"/>
+      <c r="B291" s="2"/>
       <c r="C291" s="1"/>
       <c r="D291" s="1"/>
       <c r="E291" s="1"/>
@@ -36974,7 +36995,7 @@
     </row>
     <row r="292" ht="12.75" customHeight="1">
       <c r="A292" s="1"/>
-      <c r="B292" s="1"/>
+      <c r="B292" s="2"/>
       <c r="C292" s="1"/>
       <c r="D292" s="1"/>
       <c r="E292" s="1"/>
@@ -37002,7 +37023,7 @@
     </row>
     <row r="293" ht="12.75" customHeight="1">
       <c r="A293" s="1"/>
-      <c r="B293" s="1"/>
+      <c r="B293" s="2"/>
       <c r="C293" s="1"/>
       <c r="D293" s="1"/>
       <c r="E293" s="1"/>
@@ -37030,7 +37051,7 @@
     </row>
     <row r="294" ht="12.75" customHeight="1">
       <c r="A294" s="1"/>
-      <c r="B294" s="1"/>
+      <c r="B294" s="2"/>
       <c r="C294" s="1"/>
       <c r="D294" s="1"/>
       <c r="E294" s="1"/>
@@ -37058,7 +37079,7 @@
     </row>
     <row r="295" ht="12.75" customHeight="1">
       <c r="A295" s="1"/>
-      <c r="B295" s="1"/>
+      <c r="B295" s="2"/>
       <c r="C295" s="1"/>
       <c r="D295" s="1"/>
       <c r="E295" s="1"/>
@@ -37086,7 +37107,7 @@
     </row>
     <row r="296" ht="12.75" customHeight="1">
       <c r="A296" s="1"/>
-      <c r="B296" s="1"/>
+      <c r="B296" s="2"/>
       <c r="C296" s="1"/>
       <c r="D296" s="1"/>
       <c r="E296" s="1"/>
@@ -37114,7 +37135,7 @@
     </row>
     <row r="297" ht="12.75" customHeight="1">
       <c r="A297" s="1"/>
-      <c r="B297" s="1"/>
+      <c r="B297" s="2"/>
       <c r="C297" s="1"/>
       <c r="D297" s="1"/>
       <c r="E297" s="1"/>
@@ -37142,7 +37163,7 @@
     </row>
     <row r="298" ht="12.75" customHeight="1">
       <c r="A298" s="1"/>
-      <c r="B298" s="1"/>
+      <c r="B298" s="2"/>
       <c r="C298" s="1"/>
       <c r="D298" s="1"/>
       <c r="E298" s="1"/>
@@ -37170,7 +37191,7 @@
     </row>
     <row r="299" ht="12.75" customHeight="1">
       <c r="A299" s="1"/>
-      <c r="B299" s="1"/>
+      <c r="B299" s="2"/>
       <c r="C299" s="1"/>
       <c r="D299" s="1"/>
       <c r="E299" s="1"/>
@@ -37198,7 +37219,7 @@
     </row>
     <row r="300" ht="12.75" customHeight="1">
       <c r="A300" s="1"/>
-      <c r="B300" s="1"/>
+      <c r="B300" s="2"/>
       <c r="C300" s="1"/>
       <c r="D300" s="1"/>
       <c r="E300" s="1"/>
@@ -37226,7 +37247,7 @@
     </row>
     <row r="301" ht="12.75" customHeight="1">
       <c r="A301" s="1"/>
-      <c r="B301" s="1"/>
+      <c r="B301" s="2"/>
       <c r="C301" s="1"/>
       <c r="D301" s="1"/>
       <c r="E301" s="1"/>
@@ -37254,7 +37275,7 @@
     </row>
     <row r="302" ht="12.75" customHeight="1">
       <c r="A302" s="1"/>
-      <c r="B302" s="1"/>
+      <c r="B302" s="2"/>
       <c r="C302" s="1"/>
       <c r="D302" s="1"/>
       <c r="E302" s="1"/>
@@ -37282,7 +37303,7 @@
     </row>
     <row r="303" ht="12.75" customHeight="1">
       <c r="A303" s="1"/>
-      <c r="B303" s="1"/>
+      <c r="B303" s="2"/>
       <c r="C303" s="1"/>
       <c r="D303" s="1"/>
       <c r="E303" s="1"/>
@@ -37310,7 +37331,7 @@
     </row>
     <row r="304" ht="12.75" customHeight="1">
       <c r="A304" s="1"/>
-      <c r="B304" s="1"/>
+      <c r="B304" s="2"/>
       <c r="C304" s="1"/>
       <c r="D304" s="1"/>
       <c r="E304" s="1"/>
@@ -37338,7 +37359,7 @@
     </row>
     <row r="305" ht="12.75" customHeight="1">
       <c r="A305" s="1"/>
-      <c r="B305" s="1"/>
+      <c r="B305" s="2"/>
       <c r="C305" s="1"/>
       <c r="D305" s="1"/>
       <c r="E305" s="1"/>
@@ -37366,7 +37387,7 @@
     </row>
     <row r="306" ht="12.75" customHeight="1">
       <c r="A306" s="1"/>
-      <c r="B306" s="1"/>
+      <c r="B306" s="2"/>
       <c r="C306" s="1"/>
       <c r="D306" s="1"/>
       <c r="E306" s="1"/>
@@ -37394,7 +37415,7 @@
     </row>
     <row r="307" ht="12.75" customHeight="1">
       <c r="A307" s="1"/>
-      <c r="B307" s="1"/>
+      <c r="B307" s="2"/>
       <c r="C307" s="1"/>
       <c r="D307" s="1"/>
       <c r="E307" s="1"/>
@@ -37422,7 +37443,7 @@
     </row>
     <row r="308" ht="12.75" customHeight="1">
       <c r="A308" s="1"/>
-      <c r="B308" s="1"/>
+      <c r="B308" s="2"/>
       <c r="C308" s="1"/>
       <c r="D308" s="1"/>
       <c r="E308" s="1"/>
@@ -37450,7 +37471,7 @@
     </row>
     <row r="309" ht="12.75" customHeight="1">
       <c r="A309" s="1"/>
-      <c r="B309" s="1"/>
+      <c r="B309" s="2"/>
       <c r="C309" s="1"/>
       <c r="D309" s="1"/>
       <c r="E309" s="1"/>
@@ -37478,7 +37499,7 @@
     </row>
     <row r="310" ht="12.75" customHeight="1">
       <c r="A310" s="1"/>
-      <c r="B310" s="1"/>
+      <c r="B310" s="2"/>
       <c r="C310" s="1"/>
       <c r="D310" s="1"/>
       <c r="E310" s="1"/>
@@ -37506,7 +37527,7 @@
     </row>
     <row r="311" ht="12.75" customHeight="1">
       <c r="A311" s="1"/>
-      <c r="B311" s="1"/>
+      <c r="B311" s="2"/>
       <c r="C311" s="1"/>
       <c r="D311" s="1"/>
       <c r="E311" s="1"/>
@@ -37534,7 +37555,7 @@
     </row>
     <row r="312" ht="12.75" customHeight="1">
       <c r="A312" s="1"/>
-      <c r="B312" s="1"/>
+      <c r="B312" s="2"/>
       <c r="C312" s="1"/>
       <c r="D312" s="1"/>
       <c r="E312" s="1"/>
@@ -37562,7 +37583,7 @@
     </row>
     <row r="313" ht="12.75" customHeight="1">
       <c r="A313" s="1"/>
-      <c r="B313" s="1"/>
+      <c r="B313" s="2"/>
       <c r="C313" s="1"/>
       <c r="D313" s="1"/>
       <c r="E313" s="1"/>
@@ -37590,7 +37611,7 @@
     </row>
     <row r="314" ht="12.75" customHeight="1">
       <c r="A314" s="1"/>
-      <c r="B314" s="1"/>
+      <c r="B314" s="2"/>
       <c r="C314" s="1"/>
       <c r="D314" s="1"/>
       <c r="E314" s="1"/>
@@ -37618,7 +37639,7 @@
     </row>
     <row r="315" ht="12.75" customHeight="1">
       <c r="A315" s="1"/>
-      <c r="B315" s="1"/>
+      <c r="B315" s="2"/>
       <c r="C315" s="1"/>
       <c r="D315" s="1"/>
       <c r="E315" s="1"/>
@@ -37646,7 +37667,7 @@
     </row>
     <row r="316" ht="12.75" customHeight="1">
       <c r="A316" s="1"/>
-      <c r="B316" s="1"/>
+      <c r="B316" s="2"/>
       <c r="C316" s="1"/>
       <c r="D316" s="1"/>
       <c r="E316" s="1"/>
@@ -37674,7 +37695,7 @@
     </row>
     <row r="317" ht="12.75" customHeight="1">
       <c r="A317" s="1"/>
-      <c r="B317" s="1"/>
+      <c r="B317" s="2"/>
       <c r="C317" s="1"/>
       <c r="D317" s="1"/>
       <c r="E317" s="1"/>
@@ -37702,7 +37723,7 @@
     </row>
     <row r="318" ht="12.75" customHeight="1">
       <c r="A318" s="1"/>
-      <c r="B318" s="1"/>
+      <c r="B318" s="2"/>
       <c r="C318" s="1"/>
       <c r="D318" s="1"/>
       <c r="E318" s="1"/>
@@ -37730,7 +37751,7 @@
     </row>
     <row r="319" ht="12.75" customHeight="1">
       <c r="A319" s="1"/>
-      <c r="B319" s="1"/>
+      <c r="B319" s="2"/>
       <c r="C319" s="1"/>
       <c r="D319" s="1"/>
       <c r="E319" s="1"/>
@@ -37758,7 +37779,7 @@
     </row>
     <row r="320" ht="12.75" customHeight="1">
       <c r="A320" s="1"/>
-      <c r="B320" s="1"/>
+      <c r="B320" s="2"/>
       <c r="C320" s="1"/>
       <c r="D320" s="1"/>
       <c r="E320" s="1"/>
@@ -37786,7 +37807,7 @@
     </row>
     <row r="321" ht="12.75" customHeight="1">
       <c r="A321" s="1"/>
-      <c r="B321" s="1"/>
+      <c r="B321" s="2"/>
       <c r="C321" s="1"/>
       <c r="D321" s="1"/>
       <c r="E321" s="1"/>
@@ -37814,7 +37835,7 @@
     </row>
     <row r="322" ht="12.75" customHeight="1">
       <c r="A322" s="1"/>
-      <c r="B322" s="1"/>
+      <c r="B322" s="2"/>
       <c r="C322" s="1"/>
       <c r="D322" s="1"/>
       <c r="E322" s="1"/>
@@ -37842,7 +37863,7 @@
     </row>
     <row r="323" ht="12.75" customHeight="1">
       <c r="A323" s="1"/>
-      <c r="B323" s="1"/>
+      <c r="B323" s="2"/>
       <c r="C323" s="1"/>
       <c r="D323" s="1"/>
       <c r="E323" s="1"/>
@@ -37870,7 +37891,7 @@
     </row>
     <row r="324" ht="12.75" customHeight="1">
       <c r="A324" s="1"/>
-      <c r="B324" s="1"/>
+      <c r="B324" s="2"/>
       <c r="C324" s="1"/>
       <c r="D324" s="1"/>
       <c r="E324" s="1"/>
@@ -37898,7 +37919,7 @@
     </row>
     <row r="325" ht="12.75" customHeight="1">
       <c r="A325" s="1"/>
-      <c r="B325" s="1"/>
+      <c r="B325" s="2"/>
       <c r="C325" s="1"/>
       <c r="D325" s="1"/>
       <c r="E325" s="1"/>
@@ -37926,7 +37947,7 @@
     </row>
     <row r="326" ht="12.75" customHeight="1">
       <c r="A326" s="1"/>
-      <c r="B326" s="1"/>
+      <c r="B326" s="2"/>
       <c r="C326" s="1"/>
       <c r="D326" s="1"/>
       <c r="E326" s="1"/>
@@ -37954,7 +37975,7 @@
     </row>
     <row r="327" ht="12.75" customHeight="1">
       <c r="A327" s="1"/>
-      <c r="B327" s="1"/>
+      <c r="B327" s="2"/>
       <c r="C327" s="1"/>
       <c r="D327" s="1"/>
       <c r="E327" s="1"/>
@@ -37982,7 +38003,7 @@
     </row>
     <row r="328" ht="12.75" customHeight="1">
       <c r="A328" s="1"/>
-      <c r="B328" s="1"/>
+      <c r="B328" s="2"/>
       <c r="C328" s="1"/>
       <c r="D328" s="1"/>
       <c r="E328" s="1"/>
@@ -38010,7 +38031,7 @@
     </row>
     <row r="329" ht="12.75" customHeight="1">
       <c r="A329" s="1"/>
-      <c r="B329" s="1"/>
+      <c r="B329" s="2"/>
       <c r="C329" s="1"/>
       <c r="D329" s="1"/>
       <c r="E329" s="1"/>
@@ -38038,7 +38059,7 @@
     </row>
     <row r="330" ht="12.75" customHeight="1">
       <c r="A330" s="1"/>
-      <c r="B330" s="1"/>
+      <c r="B330" s="2"/>
       <c r="C330" s="1"/>
       <c r="D330" s="1"/>
       <c r="E330" s="1"/>
@@ -38066,7 +38087,7 @@
     </row>
     <row r="331" ht="12.75" customHeight="1">
       <c r="A331" s="1"/>
-      <c r="B331" s="1"/>
+      <c r="B331" s="2"/>
       <c r="C331" s="1"/>
       <c r="D331" s="1"/>
       <c r="E331" s="1"/>
@@ -38094,7 +38115,7 @@
     </row>
     <row r="332" ht="12.75" customHeight="1">
       <c r="A332" s="1"/>
-      <c r="B332" s="1"/>
+      <c r="B332" s="2"/>
       <c r="C332" s="1"/>
       <c r="D332" s="1"/>
       <c r="E332" s="1"/>
@@ -38122,7 +38143,7 @@
     </row>
     <row r="333" ht="12.75" customHeight="1">
       <c r="A333" s="1"/>
-      <c r="B333" s="1"/>
+      <c r="B333" s="2"/>
       <c r="C333" s="1"/>
       <c r="D333" s="1"/>
       <c r="E333" s="1"/>
@@ -38150,7 +38171,7 @@
     </row>
     <row r="334" ht="12.75" customHeight="1">
       <c r="A334" s="1"/>
-      <c r="B334" s="1"/>
+      <c r="B334" s="2"/>
       <c r="C334" s="1"/>
       <c r="D334" s="1"/>
       <c r="E334" s="1"/>
@@ -38178,7 +38199,7 @@
     </row>
     <row r="335" ht="12.75" customHeight="1">
       <c r="A335" s="1"/>
-      <c r="B335" s="1"/>
+      <c r="B335" s="2"/>
       <c r="C335" s="1"/>
       <c r="D335" s="1"/>
       <c r="E335" s="1"/>
@@ -38206,7 +38227,7 @@
     </row>
     <row r="336" ht="12.75" customHeight="1">
       <c r="A336" s="1"/>
-      <c r="B336" s="1"/>
+      <c r="B336" s="2"/>
       <c r="C336" s="1"/>
       <c r="D336" s="1"/>
       <c r="E336" s="1"/>
@@ -38234,7 +38255,7 @@
     </row>
     <row r="337" ht="12.75" customHeight="1">
       <c r="A337" s="1"/>
-      <c r="B337" s="1"/>
+      <c r="B337" s="2"/>
       <c r="C337" s="1"/>
       <c r="D337" s="1"/>
       <c r="E337" s="1"/>
@@ -38262,7 +38283,7 @@
     </row>
     <row r="338" ht="12.75" customHeight="1">
       <c r="A338" s="1"/>
-      <c r="B338" s="1"/>
+      <c r="B338" s="2"/>
       <c r="C338" s="1"/>
       <c r="D338" s="1"/>
       <c r="E338" s="1"/>
@@ -38290,7 +38311,7 @@
     </row>
     <row r="339" ht="12.75" customHeight="1">
       <c r="A339" s="1"/>
-      <c r="B339" s="1"/>
+      <c r="B339" s="2"/>
       <c r="C339" s="1"/>
       <c r="D339" s="1"/>
       <c r="E339" s="1"/>
@@ -38318,7 +38339,7 @@
     </row>
     <row r="340" ht="12.75" customHeight="1">
       <c r="A340" s="1"/>
-      <c r="B340" s="1"/>
+      <c r="B340" s="2"/>
       <c r="C340" s="1"/>
       <c r="D340" s="1"/>
       <c r="E340" s="1"/>
@@ -38346,7 +38367,7 @@
     </row>
     <row r="341" ht="12.75" customHeight="1">
       <c r="A341" s="1"/>
-      <c r="B341" s="1"/>
+      <c r="B341" s="2"/>
       <c r="C341" s="1"/>
       <c r="D341" s="1"/>
       <c r="E341" s="1"/>
@@ -38374,7 +38395,7 @@
     </row>
     <row r="342" ht="12.75" customHeight="1">
       <c r="A342" s="1"/>
-      <c r="B342" s="1"/>
+      <c r="B342" s="2"/>
       <c r="C342" s="1"/>
       <c r="D342" s="1"/>
       <c r="E342" s="1"/>
@@ -38402,7 +38423,7 @@
     </row>
     <row r="343" ht="12.75" customHeight="1">
       <c r="A343" s="1"/>
-      <c r="B343" s="1"/>
+      <c r="B343" s="2"/>
       <c r="C343" s="1"/>
       <c r="D343" s="1"/>
       <c r="E343" s="1"/>
@@ -38430,7 +38451,7 @@
     </row>
     <row r="344" ht="12.75" customHeight="1">
       <c r="A344" s="1"/>
-      <c r="B344" s="1"/>
+      <c r="B344" s="2"/>
       <c r="C344" s="1"/>
       <c r="D344" s="1"/>
       <c r="E344" s="1"/>
@@ -38458,7 +38479,7 @@
     </row>
     <row r="345" ht="12.75" customHeight="1">
       <c r="A345" s="1"/>
-      <c r="B345" s="1"/>
+      <c r="B345" s="2"/>
       <c r="C345" s="1"/>
       <c r="D345" s="1"/>
       <c r="E345" s="1"/>
@@ -38486,7 +38507,7 @@
     </row>
     <row r="346" ht="12.75" customHeight="1">
       <c r="A346" s="1"/>
-      <c r="B346" s="1"/>
+      <c r="B346" s="2"/>
       <c r="C346" s="1"/>
       <c r="D346" s="1"/>
       <c r="E346" s="1"/>
@@ -38514,7 +38535,7 @@
     </row>
     <row r="347" ht="12.75" customHeight="1">
       <c r="A347" s="1"/>
-      <c r="B347" s="1"/>
+      <c r="B347" s="2"/>
       <c r="C347" s="1"/>
       <c r="D347" s="1"/>
       <c r="E347" s="1"/>
@@ -38542,7 +38563,7 @@
     </row>
     <row r="348" ht="12.75" customHeight="1">
       <c r="A348" s="1"/>
-      <c r="B348" s="1"/>
+      <c r="B348" s="2"/>
       <c r="C348" s="1"/>
       <c r="D348" s="1"/>
       <c r="E348" s="1"/>
@@ -38570,7 +38591,7 @@
     </row>
     <row r="349" ht="12.75" customHeight="1">
       <c r="A349" s="1"/>
-      <c r="B349" s="1"/>
+      <c r="B349" s="2"/>
       <c r="C349" s="1"/>
       <c r="D349" s="1"/>
       <c r="E349" s="1"/>
@@ -38598,7 +38619,7 @@
     </row>
     <row r="350" ht="12.75" customHeight="1">
       <c r="A350" s="1"/>
-      <c r="B350" s="1"/>
+      <c r="B350" s="2"/>
       <c r="C350" s="1"/>
       <c r="D350" s="1"/>
       <c r="E350" s="1"/>
@@ -38626,7 +38647,7 @@
     </row>
     <row r="351" ht="12.75" customHeight="1">
       <c r="A351" s="1"/>
-      <c r="B351" s="1"/>
+      <c r="B351" s="2"/>
       <c r="C351" s="1"/>
       <c r="D351" s="1"/>
       <c r="E351" s="1"/>
@@ -38654,7 +38675,7 @@
     </row>
     <row r="352" ht="12.75" customHeight="1">
       <c r="A352" s="1"/>
-      <c r="B352" s="1"/>
+      <c r="B352" s="2"/>
       <c r="C352" s="1"/>
       <c r="D352" s="1"/>
       <c r="E352" s="1"/>
@@ -38682,7 +38703,7 @@
     </row>
     <row r="353" ht="12.75" customHeight="1">
       <c r="A353" s="1"/>
-      <c r="B353" s="1"/>
+      <c r="B353" s="2"/>
       <c r="C353" s="1"/>
       <c r="D353" s="1"/>
       <c r="E353" s="1"/>
@@ -38710,7 +38731,7 @@
     </row>
     <row r="354" ht="12.75" customHeight="1">
       <c r="A354" s="1"/>
-      <c r="B354" s="1"/>
+      <c r="B354" s="2"/>
       <c r="C354" s="1"/>
       <c r="D354" s="1"/>
       <c r="E354" s="1"/>
@@ -38738,7 +38759,7 @@
     </row>
     <row r="355" ht="12.75" customHeight="1">
       <c r="A355" s="1"/>
-      <c r="B355" s="1"/>
+      <c r="B355" s="2"/>
       <c r="C355" s="1"/>
       <c r="D355" s="1"/>
       <c r="E355" s="1"/>
@@ -38766,7 +38787,7 @@
     </row>
     <row r="356" ht="12.75" customHeight="1">
       <c r="A356" s="1"/>
-      <c r="B356" s="1"/>
+      <c r="B356" s="2"/>
       <c r="C356" s="1"/>
       <c r="D356" s="1"/>
       <c r="E356" s="1"/>
@@ -38794,7 +38815,7 @@
     </row>
     <row r="357" ht="12.75" customHeight="1">
       <c r="A357" s="1"/>
-      <c r="B357" s="1"/>
+      <c r="B357" s="2"/>
       <c r="C357" s="1"/>
       <c r="D357" s="1"/>
       <c r="E357" s="1"/>
@@ -38822,7 +38843,7 @@
     </row>
     <row r="358" ht="12.75" customHeight="1">
       <c r="A358" s="1"/>
-      <c r="B358" s="1"/>
+      <c r="B358" s="2"/>
       <c r="C358" s="1"/>
       <c r="D358" s="1"/>
       <c r="E358" s="1"/>
@@ -38850,7 +38871,7 @@
     </row>
     <row r="359" ht="12.75" customHeight="1">
       <c r="A359" s="1"/>
-      <c r="B359" s="1"/>
+      <c r="B359" s="2"/>
       <c r="C359" s="1"/>
       <c r="D359" s="1"/>
       <c r="E359" s="1"/>
@@ -38878,7 +38899,7 @@
     </row>
     <row r="360" ht="12.75" customHeight="1">
       <c r="A360" s="1"/>
-      <c r="B360" s="1"/>
+      <c r="B360" s="2"/>
       <c r="C360" s="1"/>
       <c r="D360" s="1"/>
       <c r="E360" s="1"/>
@@ -38906,7 +38927,7 @@
     </row>
     <row r="361" ht="12.75" customHeight="1">
       <c r="A361" s="1"/>
-      <c r="B361" s="1"/>
+      <c r="B361" s="2"/>
       <c r="C361" s="1"/>
       <c r="D361" s="1"/>
       <c r="E361" s="1"/>
@@ -38934,7 +38955,7 @@
     </row>
     <row r="362" ht="12.75" customHeight="1">
       <c r="A362" s="1"/>
-      <c r="B362" s="1"/>
+      <c r="B362" s="2"/>
       <c r="C362" s="1"/>
       <c r="D362" s="1"/>
       <c r="E362" s="1"/>
@@ -38962,7 +38983,7 @@
     </row>
     <row r="363" ht="12.75" customHeight="1">
       <c r="A363" s="1"/>
-      <c r="B363" s="1"/>
+      <c r="B363" s="2"/>
       <c r="C363" s="1"/>
       <c r="D363" s="1"/>
       <c r="E363" s="1"/>
@@ -38990,7 +39011,7 @@
     </row>
     <row r="364" ht="12.75" customHeight="1">
       <c r="A364" s="1"/>
-      <c r="B364" s="1"/>
+      <c r="B364" s="2"/>
       <c r="C364" s="1"/>
       <c r="D364" s="1"/>
       <c r="E364" s="1"/>
@@ -39018,7 +39039,7 @@
     </row>
     <row r="365" ht="12.75" customHeight="1">
       <c r="A365" s="1"/>
-      <c r="B365" s="1"/>
+      <c r="B365" s="2"/>
       <c r="C365" s="1"/>
       <c r="D365" s="1"/>
       <c r="E365" s="1"/>
@@ -39046,7 +39067,7 @@
     </row>
     <row r="366" ht="12.75" customHeight="1">
       <c r="A366" s="1"/>
-      <c r="B366" s="1"/>
+      <c r="B366" s="2"/>
       <c r="C366" s="1"/>
       <c r="D366" s="1"/>
       <c r="E366" s="1"/>
@@ -39074,7 +39095,7 @@
     </row>
     <row r="367" ht="12.75" customHeight="1">
       <c r="A367" s="1"/>
-      <c r="B367" s="1"/>
+      <c r="B367" s="2"/>
       <c r="C367" s="1"/>
       <c r="D367" s="1"/>
       <c r="E367" s="1"/>
@@ -39102,7 +39123,7 @@
     </row>
     <row r="368" ht="12.75" customHeight="1">
       <c r="A368" s="1"/>
-      <c r="B368" s="1"/>
+      <c r="B368" s="2"/>
       <c r="C368" s="1"/>
       <c r="D368" s="1"/>
       <c r="E368" s="1"/>
@@ -39130,7 +39151,7 @@
     </row>
     <row r="369" ht="12.75" customHeight="1">
       <c r="A369" s="1"/>
-      <c r="B369" s="1"/>
+      <c r="B369" s="2"/>
       <c r="C369" s="1"/>
       <c r="D369" s="1"/>
       <c r="E369" s="1"/>
@@ -39158,7 +39179,7 @@
     </row>
     <row r="370" ht="12.75" customHeight="1">
       <c r="A370" s="1"/>
-      <c r="B370" s="1"/>
+      <c r="B370" s="2"/>
       <c r="C370" s="1"/>
       <c r="D370" s="1"/>
       <c r="E370" s="1"/>
@@ -39186,7 +39207,7 @@
     </row>
     <row r="371" ht="12.75" customHeight="1">
       <c r="A371" s="1"/>
-      <c r="B371" s="1"/>
+      <c r="B371" s="2"/>
       <c r="C371" s="1"/>
       <c r="D371" s="1"/>
       <c r="E371" s="1"/>
@@ -39214,7 +39235,7 @@
     </row>
     <row r="372" ht="12.75" customHeight="1">
       <c r="A372" s="1"/>
-      <c r="B372" s="1"/>
+      <c r="B372" s="2"/>
       <c r="C372" s="1"/>
       <c r="D372" s="1"/>
       <c r="E372" s="1"/>
@@ -39242,7 +39263,7 @@
     </row>
     <row r="373" ht="12.75" customHeight="1">
       <c r="A373" s="1"/>
-      <c r="B373" s="1"/>
+      <c r="B373" s="2"/>
       <c r="C373" s="1"/>
       <c r="D373" s="1"/>
       <c r="E373" s="1"/>
@@ -39270,7 +39291,7 @@
     </row>
     <row r="374" ht="12.75" customHeight="1">
       <c r="A374" s="1"/>
-      <c r="B374" s="1"/>
+      <c r="B374" s="2"/>
       <c r="C374" s="1"/>
       <c r="D374" s="1"/>
       <c r="E374" s="1"/>
@@ -39298,7 +39319,7 @@
     </row>
     <row r="375" ht="12.75" customHeight="1">
       <c r="A375" s="1"/>
-      <c r="B375" s="1"/>
+      <c r="B375" s="2"/>
       <c r="C375" s="1"/>
       <c r="D375" s="1"/>
       <c r="E375" s="1"/>
@@ -39326,7 +39347,7 @@
     </row>
     <row r="376" ht="12.75" customHeight="1">
       <c r="A376" s="1"/>
-      <c r="B376" s="1"/>
+      <c r="B376" s="2"/>
       <c r="C376" s="1"/>
       <c r="D376" s="1"/>
       <c r="E376" s="1"/>
@@ -39354,7 +39375,7 @@
     </row>
     <row r="377" ht="12.75" customHeight="1">
       <c r="A377" s="1"/>
-      <c r="B377" s="1"/>
+      <c r="B377" s="2"/>
       <c r="C377" s="1"/>
       <c r="D377" s="1"/>
       <c r="E377" s="1"/>
@@ -39382,7 +39403,7 @@
     </row>
     <row r="378" ht="12.75" customHeight="1">
       <c r="A378" s="1"/>
-      <c r="B378" s="1"/>
+      <c r="B378" s="2"/>
       <c r="C378" s="1"/>
       <c r="D378" s="1"/>
       <c r="E378" s="1"/>
@@ -39410,7 +39431,7 @@
     </row>
     <row r="379" ht="12.75" customHeight="1">
       <c r="A379" s="1"/>
-      <c r="B379" s="1"/>
+      <c r="B379" s="2"/>
       <c r="C379" s="1"/>
       <c r="D379" s="1"/>
       <c r="E379" s="1"/>
@@ -39438,7 +39459,7 @@
     </row>
     <row r="380" ht="12.75" customHeight="1">
       <c r="A380" s="1"/>
-      <c r="B380" s="1"/>
+      <c r="B380" s="2"/>
       <c r="C380" s="1"/>
       <c r="D380" s="1"/>
       <c r="E380" s="1"/>
@@ -39466,7 +39487,7 @@
     </row>
     <row r="381" ht="12.75" customHeight="1">
       <c r="A381" s="1"/>
-      <c r="B381" s="1"/>
+      <c r="B381" s="2"/>
       <c r="C381" s="1"/>
       <c r="D381" s="1"/>
       <c r="E381" s="1"/>
@@ -39494,7 +39515,7 @@
     </row>
     <row r="382" ht="12.75" customHeight="1">
       <c r="A382" s="1"/>
-      <c r="B382" s="1"/>
+      <c r="B382" s="2"/>
       <c r="C382" s="1"/>
       <c r="D382" s="1"/>
       <c r="E382" s="1"/>
@@ -39522,7 +39543,7 @@
     </row>
     <row r="383" ht="12.75" customHeight="1">
       <c r="A383" s="1"/>
-      <c r="B383" s="1"/>
+      <c r="B383" s="2"/>
       <c r="C383" s="1"/>
       <c r="D383" s="1"/>
       <c r="E383" s="1"/>
@@ -39550,7 +39571,7 @@
     </row>
     <row r="384" ht="12.75" customHeight="1">
       <c r="A384" s="1"/>
-      <c r="B384" s="1"/>
+      <c r="B384" s="2"/>
       <c r="C384" s="1"/>
       <c r="D384" s="1"/>
       <c r="E384" s="1"/>
@@ -39578,7 +39599,7 @@
     </row>
     <row r="385" ht="12.75" customHeight="1">
       <c r="A385" s="1"/>
-      <c r="B385" s="1"/>
+      <c r="B385" s="2"/>
       <c r="C385" s="1"/>
       <c r="D385" s="1"/>
       <c r="E385" s="1"/>
@@ -39606,7 +39627,7 @@
     </row>
     <row r="386" ht="12.75" customHeight="1">
       <c r="A386" s="1"/>
-      <c r="B386" s="1"/>
+      <c r="B386" s="2"/>
       <c r="C386" s="1"/>
       <c r="D386" s="1"/>
       <c r="E386" s="1"/>
@@ -39634,7 +39655,7 @@
     </row>
     <row r="387" ht="12.75" customHeight="1">
       <c r="A387" s="1"/>
-      <c r="B387" s="1"/>
+      <c r="B387" s="2"/>
       <c r="C387" s="1"/>
       <c r="D387" s="1"/>
       <c r="E387" s="1"/>
@@ -39662,7 +39683,7 @@
     </row>
     <row r="388" ht="12.75" customHeight="1">
       <c r="A388" s="1"/>
-      <c r="B388" s="1"/>
+      <c r="B388" s="2"/>
       <c r="C388" s="1"/>
       <c r="D388" s="1"/>
       <c r="E388" s="1"/>
@@ -39690,7 +39711,7 @@
     </row>
     <row r="389" ht="12.75" customHeight="1">
       <c r="A389" s="1"/>
-      <c r="B389" s="1"/>
+      <c r="B389" s="2"/>
       <c r="C389" s="1"/>
       <c r="D389" s="1"/>
       <c r="E389" s="1"/>
@@ -39718,7 +39739,7 @@
     </row>
     <row r="390" ht="12.75" customHeight="1">
       <c r="A390" s="1"/>
-      <c r="B390" s="1"/>
+      <c r="B390" s="2"/>
       <c r="C390" s="1"/>
       <c r="D390" s="1"/>
       <c r="E390" s="1"/>
@@ -39746,7 +39767,7 @@
     </row>
     <row r="391" ht="12.75" customHeight="1">
       <c r="A391" s="1"/>
-      <c r="B391" s="1"/>
+      <c r="B391" s="2"/>
       <c r="C391" s="1"/>
       <c r="D391" s="1"/>
       <c r="E391" s="1"/>
@@ -39774,7 +39795,7 @@
     </row>
     <row r="392" ht="12.75" customHeight="1">
       <c r="A392" s="1"/>
-      <c r="B392" s="1"/>
+      <c r="B392" s="2"/>
       <c r="C392" s="1"/>
       <c r="D392" s="1"/>
       <c r="E392" s="1"/>
@@ -39802,7 +39823,7 @@
     </row>
     <row r="393" ht="12.75" customHeight="1">
       <c r="A393" s="1"/>
-      <c r="B393" s="1"/>
+      <c r="B393" s="2"/>
       <c r="C393" s="1"/>
       <c r="D393" s="1"/>
       <c r="E393" s="1"/>
@@ -39830,7 +39851,7 @@
     </row>
     <row r="394" ht="12.75" customHeight="1">
       <c r="A394" s="1"/>
-      <c r="B394" s="1"/>
+      <c r="B394" s="2"/>
       <c r="C394" s="1"/>
       <c r="D394" s="1"/>
       <c r="E394" s="1"/>
@@ -39858,7 +39879,7 @@
     </row>
     <row r="395" ht="12.75" customHeight="1">
       <c r="A395" s="1"/>
-      <c r="B395" s="1"/>
+      <c r="B395" s="2"/>
       <c r="C395" s="1"/>
       <c r="D395" s="1"/>
       <c r="E395" s="1"/>
@@ -39886,7 +39907,7 @@
     </row>
     <row r="396" ht="12.75" customHeight="1">
       <c r="A396" s="1"/>
-      <c r="B396" s="1"/>
+      <c r="B396" s="2"/>
       <c r="C396" s="1"/>
       <c r="D396" s="1"/>
       <c r="E396" s="1"/>
@@ -39914,7 +39935,7 @@
     </row>
     <row r="397" ht="12.75" customHeight="1">
       <c r="A397" s="1"/>
-      <c r="B397" s="1"/>
+      <c r="B397" s="2"/>
       <c r="C397" s="1"/>
       <c r="D397" s="1"/>
       <c r="E397" s="1"/>
@@ -39942,7 +39963,7 @@
     </row>
     <row r="398" ht="12.75" customHeight="1">
       <c r="A398" s="1"/>
-      <c r="B398" s="1"/>
+      <c r="B398" s="2"/>
       <c r="C398" s="1"/>
       <c r="D398" s="1"/>
       <c r="E398" s="1"/>
@@ -39970,7 +39991,7 @@
     </row>
     <row r="399" ht="12.75" customHeight="1">
       <c r="A399" s="1"/>
-      <c r="B399" s="1"/>
+      <c r="B399" s="2"/>
       <c r="C399" s="1"/>
       <c r="D399" s="1"/>
       <c r="E399" s="1"/>
@@ -39998,7 +40019,7 @@
     </row>
     <row r="400" ht="12.75" customHeight="1">
       <c r="A400" s="1"/>
-      <c r="B400" s="1"/>
+      <c r="B400" s="2"/>
       <c r="C400" s="1"/>
       <c r="D400" s="1"/>
       <c r="E400" s="1"/>
@@ -40026,7 +40047,7 @@
     </row>
     <row r="401" ht="12.75" customHeight="1">
       <c r="A401" s="1"/>
-      <c r="B401" s="1"/>
+      <c r="B401" s="2"/>
       <c r="C401" s="1"/>
       <c r="D401" s="1"/>
       <c r="E401" s="1"/>
@@ -40054,7 +40075,7 @@
     </row>
     <row r="402" ht="12.75" customHeight="1">
       <c r="A402" s="1"/>
-      <c r="B402" s="1"/>
+      <c r="B402" s="2"/>
       <c r="C402" s="1"/>
       <c r="D402" s="1"/>
       <c r="E402" s="1"/>
@@ -40082,7 +40103,7 @@
     </row>
     <row r="403" ht="12.75" customHeight="1">
       <c r="A403" s="1"/>
-      <c r="B403" s="1"/>
+      <c r="B403" s="2"/>
       <c r="C403" s="1"/>
       <c r="D403" s="1"/>
       <c r="E403" s="1"/>
@@ -40110,7 +40131,7 @@
     </row>
     <row r="404" ht="12.75" customHeight="1">
       <c r="A404" s="1"/>
-      <c r="B404" s="1"/>
+      <c r="B404" s="2"/>
       <c r="C404" s="1"/>
       <c r="D404" s="1"/>
       <c r="E404" s="1"/>
@@ -40138,7 +40159,7 @@
     </row>
     <row r="405" ht="12.75" customHeight="1">
       <c r="A405" s="1"/>
-      <c r="B405" s="1"/>
+      <c r="B405" s="2"/>
       <c r="C405" s="1"/>
       <c r="D405" s="1"/>
       <c r="E405" s="1"/>
@@ -40166,7 +40187,7 @@
     </row>
     <row r="406" ht="12.75" customHeight="1">
       <c r="A406" s="1"/>
-      <c r="B406" s="1"/>
+      <c r="B406" s="2"/>
       <c r="C406" s="1"/>
       <c r="D406" s="1"/>
       <c r="E406" s="1"/>
@@ -40194,7 +40215,7 @@
     </row>
     <row r="407" ht="12.75" customHeight="1">
       <c r="A407" s="1"/>
-      <c r="B407" s="1"/>
+      <c r="B407" s="2"/>
       <c r="C407" s="1"/>
       <c r="D407" s="1"/>
       <c r="E407" s="1"/>
@@ -40222,7 +40243,7 @@
     </row>
     <row r="408" ht="12.75" customHeight="1">
       <c r="A408" s="1"/>
-      <c r="B408" s="1"/>
+      <c r="B408" s="2"/>
       <c r="C408" s="1"/>
       <c r="D408" s="1"/>
       <c r="E408" s="1"/>
@@ -40250,7 +40271,7 @@
     </row>
     <row r="409" ht="12.75" customHeight="1">
       <c r="A409" s="1"/>
-      <c r="B409" s="1"/>
+      <c r="B409" s="2"/>
       <c r="C409" s="1"/>
       <c r="D409" s="1"/>
       <c r="E409" s="1"/>
@@ -40278,7 +40299,7 @@
     </row>
     <row r="410" ht="12.75" customHeight="1">
       <c r="A410" s="1"/>
-      <c r="B410" s="1"/>
+      <c r="B410" s="2"/>
       <c r="C410" s="1"/>
       <c r="D410" s="1"/>
       <c r="E410" s="1"/>
@@ -40306,7 +40327,7 @@
     </row>
     <row r="411" ht="12.75" customHeight="1">
       <c r="A411" s="1"/>
-      <c r="B411" s="1"/>
+      <c r="B411" s="2"/>
       <c r="C411" s="1"/>
       <c r="D411" s="1"/>
       <c r="E411" s="1"/>
@@ -40334,7 +40355,7 @@
     </row>
     <row r="412" ht="12.75" customHeight="1">
       <c r="A412" s="1"/>
-      <c r="B412" s="1"/>
+      <c r="B412" s="2"/>
       <c r="C412" s="1"/>
       <c r="D412" s="1"/>
       <c r="E412" s="1"/>
@@ -40362,7 +40383,7 @@
     </row>
     <row r="413" ht="12.75" customHeight="1">
       <c r="A413" s="1"/>
-      <c r="B413" s="1"/>
+      <c r="B413" s="2"/>
       <c r="C413" s="1"/>
       <c r="D413" s="1"/>
       <c r="E413" s="1"/>
@@ -40390,7 +40411,7 @@
     </row>
     <row r="414" ht="12.75" customHeight="1">
       <c r="A414" s="1"/>
-      <c r="B414" s="1"/>
+      <c r="B414" s="2"/>
       <c r="C414" s="1"/>
       <c r="D414" s="1"/>
       <c r="E414" s="1"/>
@@ -40418,7 +40439,7 @@
     </row>
     <row r="415" ht="12.75" customHeight="1">
       <c r="A415" s="1"/>
-      <c r="B415" s="1"/>
+      <c r="B415" s="2"/>
       <c r="C415" s="1"/>
       <c r="D415" s="1"/>
       <c r="E415" s="1"/>
@@ -40446,7 +40467,7 @@
     </row>
     <row r="416" ht="12.75" customHeight="1">
       <c r="A416" s="1"/>
-      <c r="B416" s="1"/>
+      <c r="B416" s="2"/>
       <c r="C416" s="1"/>
       <c r="D416" s="1"/>
       <c r="E416" s="1"/>
@@ -40474,7 +40495,7 @@
     </row>
     <row r="417" ht="12.75" customHeight="1">
       <c r="A417" s="1"/>
-      <c r="B417" s="1"/>
+      <c r="B417" s="2"/>
       <c r="C417" s="1"/>
       <c r="D417" s="1"/>
       <c r="E417" s="1"/>
@@ -40502,7 +40523,7 @@
     </row>
     <row r="418" ht="12.75" customHeight="1">
       <c r="A418" s="1"/>
-      <c r="B418" s="1"/>
+      <c r="B418" s="2"/>
       <c r="C418" s="1"/>
       <c r="D418" s="1"/>
       <c r="E418" s="1"/>
@@ -40530,7 +40551,7 @@
     </row>
     <row r="419" ht="12.75" customHeight="1">
       <c r="A419" s="1"/>
-      <c r="B419" s="1"/>
+      <c r="B419" s="2"/>
       <c r="C419" s="1"/>
       <c r="D419" s="1"/>
       <c r="E419" s="1"/>
@@ -40558,7 +40579,7 @@
     </row>
     <row r="420" ht="12.75" customHeight="1">
       <c r="A420" s="1"/>
-      <c r="B420" s="1"/>
+      <c r="B420" s="2"/>
       <c r="C420" s="1"/>
       <c r="D420" s="1"/>
       <c r="E420" s="1"/>
@@ -40586,7 +40607,7 @@
     </row>
     <row r="421" ht="12.75" customHeight="1">
       <c r="A421" s="1"/>
-      <c r="B421" s="1"/>
+      <c r="B421" s="2"/>
       <c r="C421" s="1"/>
       <c r="D421" s="1"/>
       <c r="E421" s="1"/>
@@ -40614,7 +40635,7 @@
     </row>
     <row r="422" ht="12.75" customHeight="1">
       <c r="A422" s="1"/>
-      <c r="B422" s="1"/>
+      <c r="B422" s="2"/>
       <c r="C422" s="1"/>
       <c r="D422" s="1"/>
       <c r="E422" s="1"/>
@@ -40642,7 +40663,7 @@
     </row>
     <row r="423" ht="12.75" customHeight="1">
       <c r="A423" s="1"/>
-      <c r="B423" s="1"/>
+      <c r="B423" s="2"/>
       <c r="C423" s="1"/>
       <c r="D423" s="1"/>
       <c r="E423" s="1"/>
@@ -40670,7 +40691,7 @@
     </row>
     <row r="424" ht="12.75" customHeight="1">
       <c r="A424" s="1"/>
-      <c r="B424" s="1"/>
+      <c r="B424" s="2"/>
       <c r="C424" s="1"/>
       <c r="D424" s="1"/>
       <c r="E424" s="1"/>
@@ -40698,7 +40719,7 @@
     </row>
     <row r="425" ht="12.75" customHeight="1">
       <c r="A425" s="1"/>
-      <c r="B425" s="1"/>
+      <c r="B425" s="2"/>
       <c r="C425" s="1"/>
       <c r="D425" s="1"/>
       <c r="E425" s="1"/>
@@ -40726,7 +40747,7 @@
     </row>
     <row r="426" ht="12.75" customHeight="1">
       <c r="A426" s="1"/>
-      <c r="B426" s="1"/>
+      <c r="B426" s="2"/>
       <c r="C426" s="1"/>
       <c r="D426" s="1"/>
       <c r="E426" s="1"/>
@@ -40754,7 +40775,7 @@
     </row>
     <row r="427" ht="12.75" customHeight="1">
       <c r="A427" s="1"/>
-      <c r="B427" s="1"/>
+      <c r="B427" s="2"/>
       <c r="C427" s="1"/>
       <c r="D427" s="1"/>
       <c r="E427" s="1"/>
@@ -40782,7 +40803,7 @@
     </row>
     <row r="428" ht="12.75" customHeight="1">
       <c r="A428" s="1"/>
-      <c r="B428" s="1"/>
+      <c r="B428" s="2"/>
       <c r="C428" s="1"/>
       <c r="D428" s="1"/>
       <c r="E428" s="1"/>
@@ -40810,7 +40831,7 @@
     </row>
     <row r="429" ht="12.75" customHeight="1">
       <c r="A429" s="1"/>
-      <c r="B429" s="1"/>
+      <c r="B429" s="2"/>
       <c r="C429" s="1"/>
       <c r="D429" s="1"/>
       <c r="E429" s="1"/>
@@ -40838,7 +40859,7 @@
     </row>
     <row r="430" ht="12.75" customHeight="1">
       <c r="A430" s="1"/>
-      <c r="B430" s="1"/>
+      <c r="B430" s="2"/>
       <c r="C430" s="1"/>
       <c r="D430" s="1"/>
       <c r="E430" s="1"/>
@@ -40866,7 +40887,7 @@
     </row>
     <row r="431" ht="12.75" customHeight="1">
       <c r="A431" s="1"/>
-      <c r="B431" s="1"/>
+      <c r="B431" s="2"/>
       <c r="C431" s="1"/>
       <c r="D431" s="1"/>
       <c r="E431" s="1"/>
@@ -40894,7 +40915,7 @@
     </row>
     <row r="432" ht="12.75" customHeight="1">
       <c r="A432" s="1"/>
-      <c r="B432" s="1"/>
+      <c r="B432" s="2"/>
       <c r="C432" s="1"/>
       <c r="D432" s="1"/>
       <c r="E432" s="1"/>
@@ -40922,7 +40943,7 @@
     </row>
     <row r="433" ht="12.75" customHeight="1">
       <c r="A433" s="1"/>
-      <c r="B433" s="1"/>
+      <c r="B433" s="2"/>
       <c r="C433" s="1"/>
       <c r="D433" s="1"/>
       <c r="E433" s="1"/>
@@ -40950,7 +40971,7 @@
     </row>
     <row r="434" ht="12.75" customHeight="1">
       <c r="A434" s="1"/>
-      <c r="B434" s="1"/>
+      <c r="B434" s="2"/>
       <c r="C434" s="1"/>
       <c r="D434" s="1"/>
       <c r="E434" s="1"/>
@@ -40978,7 +40999,7 @@
     </row>
     <row r="435" ht="12.75" customHeight="1">
       <c r="A435" s="1"/>
-      <c r="B435" s="1"/>
+      <c r="B435" s="2"/>
       <c r="C435" s="1"/>
       <c r="D435" s="1"/>
       <c r="E435" s="1"/>
@@ -41006,7 +41027,7 @@
     </row>
     <row r="436" ht="12.75" customHeight="1">
       <c r="A436" s="1"/>
-      <c r="B436" s="1"/>
+      <c r="B436" s="2"/>
       <c r="C436" s="1"/>
       <c r="D436" s="1"/>
       <c r="E436" s="1"/>
@@ -41034,7 +41055,7 @@
     </row>
     <row r="437" ht="12.75" customHeight="1">
       <c r="A437" s="1"/>
-      <c r="B437" s="1"/>
+      <c r="B437" s="2"/>
       <c r="C437" s="1"/>
       <c r="D437" s="1"/>
       <c r="E437" s="1"/>
@@ -41062,7 +41083,7 @@
     </row>
     <row r="438" ht="12.75" customHeight="1">
       <c r="A438" s="1"/>
-      <c r="B438" s="1"/>
+      <c r="B438" s="2"/>
       <c r="C438" s="1"/>
       <c r="D438" s="1"/>
       <c r="E438" s="1"/>
@@ -41090,7 +41111,7 @@
     </row>
     <row r="439" ht="12.75" customHeight="1">
       <c r="A439" s="1"/>
-      <c r="B439" s="1"/>
+      <c r="B439" s="2"/>
       <c r="C439" s="1"/>
       <c r="D439" s="1"/>
       <c r="E439" s="1"/>
@@ -41118,7 +41139,7 @@
     </row>
     <row r="440" ht="12.75" customHeight="1">
       <c r="A440" s="1"/>
-      <c r="B440" s="1"/>
+      <c r="B440" s="2"/>
       <c r="C440" s="1"/>
       <c r="D440" s="1"/>
       <c r="E440" s="1"/>
@@ -41146,7 +41167,7 @@
     </row>
     <row r="441" ht="12.75" customHeight="1">
       <c r="A441" s="1"/>
-      <c r="B441" s="1"/>
+      <c r="B441" s="2"/>
       <c r="C441" s="1"/>
       <c r="D441" s="1"/>
       <c r="E441" s="1"/>
@@ -41174,7 +41195,7 @@
     </row>
     <row r="442" ht="12.75" customHeight="1">
       <c r="A442" s="1"/>
-      <c r="B442" s="1"/>
+      <c r="B442" s="2"/>
       <c r="C442" s="1"/>
       <c r="D442" s="1"/>
       <c r="E442" s="1"/>
@@ -41202,7 +41223,7 @@
     </row>
     <row r="443" ht="12.75" customHeight="1">
       <c r="A443" s="1"/>
-      <c r="B443" s="1"/>
+      <c r="B443" s="2"/>
       <c r="C443" s="1"/>
       <c r="D443" s="1"/>
       <c r="E443" s="1"/>
@@ -41230,7 +41251,7 @@
     </row>
     <row r="444" ht="12.75" customHeight="1">
       <c r="A444" s="1"/>
-      <c r="B444" s="1"/>
+      <c r="B444" s="2"/>
       <c r="C444" s="1"/>
       <c r="D444" s="1"/>
       <c r="E444" s="1"/>
@@ -41258,7 +41279,7 @@
     </row>
     <row r="445" ht="12.75" customHeight="1">
       <c r="A445" s="1"/>
-      <c r="B445" s="1"/>
+      <c r="B445" s="2"/>
       <c r="C445" s="1"/>
       <c r="D445" s="1"/>
       <c r="E445" s="1"/>
@@ -41286,7 +41307,7 @@
     </row>
     <row r="446" ht="12.75" customHeight="1">
       <c r="A446" s="1"/>
-      <c r="B446" s="1"/>
+      <c r="B446" s="2"/>
       <c r="C446" s="1"/>
       <c r="D446" s="1"/>
       <c r="E446" s="1"/>
@@ -41314,7 +41335,7 @@
     </row>
     <row r="447" ht="12.75" customHeight="1">
       <c r="A447" s="1"/>
-      <c r="B447" s="1"/>
+      <c r="B447" s="2"/>
       <c r="C447" s="1"/>
       <c r="D447" s="1"/>
       <c r="E447" s="1"/>
@@ -41342,7 +41363,7 @@
     </row>
     <row r="448" ht="12.75" customHeight="1">
       <c r="A448" s="1"/>
-      <c r="B448" s="1"/>
+      <c r="B448" s="2"/>
       <c r="C448" s="1"/>
       <c r="D448" s="1"/>
       <c r="E448" s="1"/>
@@ -41370,7 +41391,7 @@
     </row>
     <row r="449" ht="12.75" customHeight="1">
       <c r="A449" s="1"/>
-      <c r="B449" s="1"/>
+      <c r="B449" s="2"/>
       <c r="C449" s="1"/>
       <c r="D449" s="1"/>
       <c r="E449" s="1"/>
@@ -41398,7 +41419,7 @@
     </row>
     <row r="450" ht="12.75" customHeight="1">
       <c r="A450" s="1"/>
-      <c r="B450" s="1"/>
+      <c r="B450" s="2"/>
       <c r="C450" s="1"/>
       <c r="D450" s="1"/>
       <c r="E450" s="1"/>
@@ -41426,7 +41447,7 @@
     </row>
     <row r="451" ht="12.75" customHeight="1">
       <c r="A451" s="1"/>
-      <c r="B451" s="1"/>
+      <c r="B451" s="2"/>
       <c r="C451" s="1"/>
       <c r="D451" s="1"/>
       <c r="E451" s="1"/>
@@ -41454,7 +41475,7 @@
     </row>
     <row r="452" ht="12.75" customHeight="1">
       <c r="A452" s="1"/>
-      <c r="B452" s="1"/>
+      <c r="B452" s="2"/>
       <c r="C452" s="1"/>
       <c r="D452" s="1"/>
       <c r="E452" s="1"/>
@@ -41482,7 +41503,7 @@
     </row>
     <row r="453" ht="12.75" customHeight="1">
       <c r="A453" s="1"/>
-      <c r="B453" s="1"/>
+      <c r="B453" s="2"/>
       <c r="C453" s="1"/>
       <c r="D453" s="1"/>
       <c r="E453" s="1"/>
@@ -41510,7 +41531,7 @@
     </row>
     <row r="454" ht="12.75" customHeight="1">
       <c r="A454" s="1"/>
-      <c r="B454" s="1"/>
+      <c r="B454" s="2"/>
       <c r="C454" s="1"/>
       <c r="D454" s="1"/>
       <c r="E454" s="1"/>
@@ -41538,7 +41559,7 @@
     </row>
     <row r="455" ht="12.75" customHeight="1">
       <c r="A455" s="1"/>
-      <c r="B455" s="1"/>
+      <c r="B455" s="2"/>
       <c r="C455" s="1"/>
       <c r="D455" s="1"/>
       <c r="E455" s="1"/>
@@ -41566,7 +41587,7 @@
     </row>
     <row r="456" ht="12.75" customHeight="1">
       <c r="A456" s="1"/>
-      <c r="B456" s="1"/>
+      <c r="B456" s="2"/>
       <c r="C456" s="1"/>
       <c r="D456" s="1"/>
       <c r="E456" s="1"/>
@@ -41594,7 +41615,7 @@
     </row>
     <row r="457" ht="12.75" customHeight="1">
       <c r="A457" s="1"/>
-      <c r="B457" s="1"/>
+      <c r="B457" s="2"/>
       <c r="C457" s="1"/>
       <c r="D457" s="1"/>
       <c r="E457" s="1"/>
@@ -41622,7 +41643,7 @@
     </row>
     <row r="458" ht="12.75" customHeight="1">
       <c r="A458" s="1"/>
-      <c r="B458" s="1"/>
+      <c r="B458" s="2"/>
       <c r="C458" s="1"/>
       <c r="D458" s="1"/>
       <c r="E458" s="1"/>
@@ -41650,7 +41671,7 @@
     </row>
     <row r="459" ht="12.75" customHeight="1">
       <c r="A459" s="1"/>
-      <c r="B459" s="1"/>
+      <c r="B459" s="2"/>
       <c r="C459" s="1"/>
       <c r="D459" s="1"/>
       <c r="E459" s="1"/>
@@ -41678,7 +41699,7 @@
     </row>
     <row r="460" ht="12.75" customHeight="1">
       <c r="A460" s="1"/>
-      <c r="B460" s="1"/>
+      <c r="B460" s="2"/>
       <c r="C460" s="1"/>
       <c r="D460" s="1"/>
       <c r="E460" s="1"/>
@@ -41706,7 +41727,7 @@
     </row>
     <row r="461" ht="12.75" customHeight="1">
       <c r="A461" s="1"/>
-      <c r="B461" s="1"/>
+      <c r="B461" s="2"/>
       <c r="C461" s="1"/>
       <c r="D461" s="1"/>
       <c r="E461" s="1"/>
@@ -41734,7 +41755,7 @@
     </row>
     <row r="462" ht="12.75" customHeight="1">
       <c r="A462" s="1"/>
-      <c r="B462" s="1"/>
+      <c r="B462" s="2"/>
       <c r="C462" s="1"/>
       <c r="D462" s="1"/>
       <c r="E462" s="1"/>
@@ -41762,7 +41783,7 @@
     </row>
     <row r="463" ht="12.75" customHeight="1">
       <c r="A463" s="1"/>
-      <c r="B463" s="1"/>
+      <c r="B463" s="2"/>
       <c r="C463" s="1"/>
       <c r="D463" s="1"/>
       <c r="E463" s="1"/>
@@ -41790,7 +41811,7 @@
     </row>
     <row r="464" ht="12.75" customHeight="1">
       <c r="A464" s="1"/>
-      <c r="B464" s="1"/>
+      <c r="B464" s="2"/>
       <c r="C464" s="1"/>
       <c r="D464" s="1"/>
       <c r="E464" s="1"/>
@@ -41818,7 +41839,7 @@
     </row>
     <row r="465" ht="12.75" customHeight="1">
       <c r="A465" s="1"/>
-      <c r="B465" s="1"/>
+      <c r="B465" s="2"/>
       <c r="C465" s="1"/>
       <c r="D465" s="1"/>
       <c r="E465" s="1"/>
@@ -41846,7 +41867,7 @@
     </row>
     <row r="466" ht="12.75" customHeight="1">
       <c r="A466" s="1"/>
-      <c r="B466" s="1"/>
+      <c r="B466" s="2"/>
       <c r="C466" s="1"/>
       <c r="D466" s="1"/>
       <c r="E466" s="1"/>
@@ -41874,7 +41895,7 @@
     </row>
     <row r="467" ht="12.75" customHeight="1">
       <c r="A467" s="1"/>
-      <c r="B467" s="1"/>
+      <c r="B467" s="2"/>
       <c r="C467" s="1"/>
       <c r="D467" s="1"/>
       <c r="E467" s="1"/>
@@ -41902,7 +41923,7 @@
     </row>
     <row r="468" ht="12.75" customHeight="1">
       <c r="A468" s="1"/>
-      <c r="B468" s="1"/>
+      <c r="B468" s="2"/>
       <c r="C468" s="1"/>
       <c r="D468" s="1"/>
       <c r="E468" s="1"/>
@@ -41930,7 +41951,7 @@
     </row>
     <row r="469" ht="12.75" customHeight="1">
       <c r="A469" s="1"/>
-      <c r="B469" s="1"/>
+      <c r="B469" s="2"/>
       <c r="C469" s="1"/>
       <c r="D469" s="1"/>
       <c r="E469" s="1"/>
@@ -41958,7 +41979,7 @@
     </row>
     <row r="470" ht="12.75" customHeight="1">
       <c r="A470" s="1"/>
-      <c r="B470" s="1"/>
+      <c r="B470" s="2"/>
       <c r="C470" s="1"/>
       <c r="D470" s="1"/>
       <c r="E470" s="1"/>
@@ -41986,7 +42007,7 @@
     </row>
     <row r="471" ht="12.75" customHeight="1">
       <c r="A471" s="1"/>
-      <c r="B471" s="1"/>
+      <c r="B471" s="2"/>
       <c r="C471" s="1"/>
       <c r="D471" s="1"/>
       <c r="E471" s="1"/>
@@ -42014,7 +42035,7 @@
     </row>
     <row r="472" ht="12.75" customHeight="1">
       <c r="A472" s="1"/>
-      <c r="B472" s="1"/>
+      <c r="B472" s="2"/>
       <c r="C472" s="1"/>
       <c r="D472" s="1"/>
       <c r="E472" s="1"/>
@@ -42042,7 +42063,7 @@
     </row>
     <row r="473" ht="12.75" customHeight="1">
       <c r="A473" s="1"/>
-      <c r="B473" s="1"/>
+      <c r="B473" s="2"/>
       <c r="C473" s="1"/>
       <c r="D473" s="1"/>
       <c r="E473" s="1"/>
@@ -42070,7 +42091,7 @@
     </row>
     <row r="474" ht="12.75" customHeight="1">
       <c r="A474" s="1"/>
-      <c r="B474" s="1"/>
+      <c r="B474" s="2"/>
       <c r="C474" s="1"/>
       <c r="D474" s="1"/>
       <c r="E474" s="1"/>
@@ -42098,7 +42119,7 @@
     </row>
     <row r="475" ht="12.75" customHeight="1">
       <c r="A475" s="1"/>
-      <c r="B475" s="1"/>
+      <c r="B475" s="2"/>
       <c r="C475" s="1"/>
       <c r="D475" s="1"/>
       <c r="E475" s="1"/>
@@ -42126,7 +42147,7 @@
     </row>
     <row r="476" ht="12.75" customHeight="1">
       <c r="A476" s="1"/>
-      <c r="B476" s="1"/>
+      <c r="B476" s="2"/>
       <c r="C476" s="1"/>
       <c r="D476" s="1"/>
       <c r="E476" s="1"/>
@@ -42154,7 +42175,7 @@
     </row>
     <row r="477" ht="12.75" customHeight="1">
       <c r="A477" s="1"/>
-      <c r="B477" s="1"/>
+      <c r="B477" s="2"/>
       <c r="C477" s="1"/>
       <c r="D477" s="1"/>
       <c r="E477" s="1"/>
@@ -42182,7 +42203,7 @@
     </row>
     <row r="478" ht="12.75" customHeight="1">
       <c r="A478" s="1"/>
-      <c r="B478" s="1"/>
+      <c r="B478" s="2"/>
       <c r="C478" s="1"/>
       <c r="D478" s="1"/>
       <c r="E478" s="1"/>
@@ -42210,7 +42231,7 @@
     </row>
     <row r="479" ht="12.75" customHeight="1">
       <c r="A479" s="1"/>
-      <c r="B479" s="1"/>
+      <c r="B479" s="2"/>
       <c r="C479" s="1"/>
       <c r="D479" s="1"/>
       <c r="E479" s="1"/>
@@ -42238,7 +42259,7 @@
     </row>
     <row r="480" ht="12.75" customHeight="1">
       <c r="A480" s="1"/>
-      <c r="B480" s="1"/>
+      <c r="B480" s="2"/>
       <c r="C480" s="1"/>
       <c r="D480" s="1"/>
       <c r="E480" s="1"/>
@@ -42266,7 +42287,7 @@
     </row>
     <row r="481" ht="12.75" customHeight="1">
       <c r="A481" s="1"/>
-      <c r="B481" s="1"/>
+      <c r="B481" s="2"/>
       <c r="C481" s="1"/>
       <c r="D481" s="1"/>
       <c r="E481" s="1"/>
@@ -42294,7 +42315,7 @@
     </row>
     <row r="482" ht="12.75" customHeight="1">
       <c r="A482" s="1"/>
-      <c r="B482" s="1"/>
+      <c r="B482" s="2"/>
       <c r="C482" s="1"/>
       <c r="D482" s="1"/>
       <c r="E482" s="1"/>
@@ -42322,7 +42343,7 @@
     </row>
     <row r="483" ht="12.75" customHeight="1">
       <c r="A483" s="1"/>
-      <c r="B483" s="1"/>
+      <c r="B483" s="2"/>
       <c r="C483" s="1"/>
       <c r="D483" s="1"/>
       <c r="E483" s="1"/>
@@ -42350,7 +42371,7 @@
     </row>
     <row r="484" ht="12.75" customHeight="1">
       <c r="A484" s="1"/>
-      <c r="B484" s="1"/>
+      <c r="B484" s="2"/>
       <c r="C484" s="1"/>
       <c r="D484" s="1"/>
       <c r="E484" s="1"/>
@@ -42378,7 +42399,7 @@
     </row>
     <row r="485" ht="12.75" customHeight="1">
       <c r="A485" s="1"/>
-      <c r="B485" s="1"/>
+      <c r="B485" s="2"/>
       <c r="C485" s="1"/>
       <c r="D485" s="1"/>
       <c r="E485" s="1"/>
@@ -42406,7 +42427,7 @@
     </row>
     <row r="486" ht="12.75" customHeight="1">
       <c r="A486" s="1"/>
-      <c r="B486" s="1"/>
+      <c r="B486" s="2"/>
       <c r="C486" s="1"/>
       <c r="D486" s="1"/>
       <c r="E486" s="1"/>
@@ -42434,7 +42455,7 @@
     </row>
     <row r="487" ht="12.75" customHeight="1">
       <c r="A487" s="1"/>
-      <c r="B487" s="1"/>
+      <c r="B487" s="2"/>
       <c r="C487" s="1"/>
       <c r="D487" s="1"/>
       <c r="E487" s="1"/>
@@ -42462,7 +42483,7 @@
     </row>
     <row r="488" ht="12.75" customHeight="1">
       <c r="A488" s="1"/>
-      <c r="B488" s="1"/>
+      <c r="B488" s="2"/>
       <c r="C488" s="1"/>
       <c r="D488" s="1"/>
       <c r="E488" s="1"/>
@@ -42490,7 +42511,7 @@
     </row>
     <row r="489" ht="12.75" customHeight="1">
       <c r="A489" s="1"/>
-      <c r="B489" s="1"/>
+      <c r="B489" s="2"/>
       <c r="C489" s="1"/>
       <c r="D489" s="1"/>
       <c r="E489" s="1"/>
@@ -42518,7 +42539,7 @@
     </row>
     <row r="490" ht="12.75" customHeight="1">
       <c r="A490" s="1"/>
-      <c r="B490" s="1"/>
+      <c r="B490" s="2"/>
       <c r="C490" s="1"/>
       <c r="D490" s="1"/>
       <c r="E490" s="1"/>
@@ -42546,7 +42567,7 @@
     </row>
     <row r="491" ht="12.75" customHeight="1">
       <c r="A491" s="1"/>
-      <c r="B491" s="1"/>
+      <c r="B491" s="2"/>
       <c r="C491" s="1"/>
       <c r="D491" s="1"/>
       <c r="E491" s="1"/>
@@ -42574,7 +42595,7 @@
     </row>
     <row r="492" ht="12.75" customHeight="1">
       <c r="A492" s="1"/>
-      <c r="B492" s="1"/>
+      <c r="B492" s="2"/>
       <c r="C492" s="1"/>
       <c r="D492" s="1"/>
       <c r="E492" s="1"/>
@@ -42602,7 +42623,7 @@
     </row>
     <row r="493" ht="12.75" customHeight="1">
       <c r="A493" s="1"/>
-      <c r="B493" s="1"/>
+      <c r="B493" s="2"/>
       <c r="C493" s="1"/>
       <c r="D493" s="1"/>
       <c r="E493" s="1"/>
@@ -42630,7 +42651,7 @@
     </row>
     <row r="494" ht="12.75" customHeight="1">
       <c r="A494" s="1"/>
-      <c r="B494" s="1"/>
+      <c r="B494" s="2"/>
       <c r="C494" s="1"/>
       <c r="D494" s="1"/>
       <c r="E494" s="1"/>
@@ -42658,7 +42679,7 @@
     </row>
     <row r="495" ht="12.75" customHeight="1">
       <c r="A495" s="1"/>
-      <c r="B495" s="1"/>
+      <c r="B495" s="2"/>
       <c r="C495" s="1"/>
       <c r="D495" s="1"/>
       <c r="E495" s="1"/>
@@ -42686,7 +42707,7 @@
     </row>
     <row r="496" ht="12.75" customHeight="1">
       <c r="A496" s="1"/>
-      <c r="B496" s="1"/>
+      <c r="B496" s="2"/>
       <c r="C496" s="1"/>
       <c r="D496" s="1"/>
       <c r="E496" s="1"/>
@@ -42714,7 +42735,7 @@
     </row>
     <row r="497" ht="12.75" customHeight="1">
       <c r="A497" s="1"/>
-      <c r="B497" s="1"/>
+      <c r="B497" s="2"/>
       <c r="C497" s="1"/>
       <c r="D497" s="1"/>
       <c r="E497" s="1"/>
@@ -42742,7 +42763,7 @@
     </row>
     <row r="498" ht="12.75" customHeight="1">
       <c r="A498" s="1"/>
-      <c r="B498" s="1"/>
+      <c r="B498" s="2"/>
       <c r="C498" s="1"/>
       <c r="D498" s="1"/>
       <c r="E498" s="1"/>
@@ -42770,7 +42791,7 @@
     </row>
     <row r="499" ht="12.75" customHeight="1">
       <c r="A499" s="1"/>
-      <c r="B499" s="1"/>
+      <c r="B499" s="2"/>
       <c r="C499" s="1"/>
       <c r="D499" s="1"/>
       <c r="E499" s="1"/>
@@ -42798,7 +42819,7 @@
     </row>
     <row r="500" ht="12.75" customHeight="1">
       <c r="A500" s="1"/>
-      <c r="B500" s="1"/>
+      <c r="B500" s="2"/>
       <c r="C500" s="1"/>
       <c r="D500" s="1"/>
       <c r="E500" s="1"/>
@@ -42826,7 +42847,7 @@
     </row>
     <row r="501" ht="12.75" customHeight="1">
       <c r="A501" s="1"/>
-      <c r="B501" s="1"/>
+      <c r="B501" s="2"/>
       <c r="C501" s="1"/>
       <c r="D501" s="1"/>
       <c r="E501" s="1"/>
@@ -42854,7 +42875,7 @@
     </row>
     <row r="502" ht="12.75" customHeight="1">
       <c r="A502" s="1"/>
-      <c r="B502" s="1"/>
+      <c r="B502" s="2"/>
       <c r="C502" s="1"/>
       <c r="D502" s="1"/>
       <c r="E502" s="1"/>
@@ -42882,7 +42903,7 @@
     </row>
     <row r="503" ht="12.75" customHeight="1">
       <c r="A503" s="1"/>
-      <c r="B503" s="1"/>
+      <c r="B503" s="2"/>
       <c r="C503" s="1"/>
       <c r="D503" s="1"/>
       <c r="E503" s="1"/>
@@ -42910,7 +42931,7 @@
     </row>
     <row r="504" ht="12.75" customHeight="1">
       <c r="A504" s="1"/>
-      <c r="B504" s="1"/>
+      <c r="B504" s="2"/>
       <c r="C504" s="1"/>
       <c r="D504" s="1"/>
       <c r="E504" s="1"/>
@@ -42938,7 +42959,7 @@
     </row>
     <row r="505" ht="12.75" customHeight="1">
       <c r="A505" s="1"/>
-      <c r="B505" s="1"/>
+      <c r="B505" s="2"/>
       <c r="C505" s="1"/>
       <c r="D505" s="1"/>
       <c r="E505" s="1"/>
@@ -42966,7 +42987,7 @@
     </row>
     <row r="506" ht="12.75" customHeight="1">
       <c r="A506" s="1"/>
-      <c r="B506" s="1"/>
+      <c r="B506" s="2"/>
       <c r="C506" s="1"/>
       <c r="D506" s="1"/>
       <c r="E506" s="1"/>
@@ -42994,7 +43015,7 @@
     </row>
     <row r="507" ht="12.75" customHeight="1">
       <c r="A507" s="1"/>
-      <c r="B507" s="1"/>
+      <c r="B507" s="2"/>
       <c r="C507" s="1"/>
       <c r="D507" s="1"/>
       <c r="E507" s="1"/>
@@ -43022,7 +43043,7 @@
     </row>
     <row r="508" ht="12.75" customHeight="1">
       <c r="A508" s="1"/>
-      <c r="B508" s="1"/>
+      <c r="B508" s="2"/>
       <c r="C508" s="1"/>
       <c r="D508" s="1"/>
       <c r="E508" s="1"/>
@@ -43050,7 +43071,7 @@
     </row>
     <row r="509" ht="12.75" customHeight="1">
       <c r="A509" s="1"/>
-      <c r="B509" s="1"/>
+      <c r="B509" s="2"/>
       <c r="C509" s="1"/>
       <c r="D509" s="1"/>
       <c r="E509" s="1"/>
@@ -43078,7 +43099,7 @@
     </row>
     <row r="510" ht="12.75" customHeight="1">
       <c r="A510" s="1"/>
-      <c r="B510" s="1"/>
+      <c r="B510" s="2"/>
       <c r="C510" s="1"/>
       <c r="D510" s="1"/>
       <c r="E510" s="1"/>
@@ -43106,7 +43127,7 @@
     </row>
     <row r="511" ht="12.75" customHeight="1">
       <c r="A511" s="1"/>
-      <c r="B511" s="1"/>
+      <c r="B511" s="2"/>
       <c r="C511" s="1"/>
       <c r="D511" s="1"/>
       <c r="E511" s="1"/>
@@ -43134,7 +43155,7 @@
     </row>
     <row r="512" ht="12.75" customHeight="1">
       <c r="A512" s="1"/>
-      <c r="B512" s="1"/>
+      <c r="B512" s="2"/>
       <c r="C512" s="1"/>
       <c r="D512" s="1"/>
       <c r="E512" s="1"/>
@@ -43162,7 +43183,7 @@
     </row>
     <row r="513" ht="12.75" customHeight="1">
       <c r="A513" s="1"/>
-      <c r="B513" s="1"/>
+      <c r="B513" s="2"/>
       <c r="C513" s="1"/>
       <c r="D513" s="1"/>
       <c r="E513" s="1"/>
@@ -43190,7 +43211,7 @@
     </row>
     <row r="514" ht="12.75" customHeight="1">
       <c r="A514" s="1"/>
-      <c r="B514" s="1"/>
+      <c r="B514" s="2"/>
       <c r="C514" s="1"/>
       <c r="D514" s="1"/>
       <c r="E514" s="1"/>
@@ -43218,7 +43239,7 @@
     </row>
     <row r="515" ht="12.75" customHeight="1">
       <c r="A515" s="1"/>
-      <c r="B515" s="1"/>
+      <c r="B515" s="2"/>
       <c r="C515" s="1"/>
       <c r="D515" s="1"/>
       <c r="E515" s="1"/>
@@ -43246,7 +43267,7 @@
     </row>
     <row r="516" ht="12.75" customHeight="1">
       <c r="A516" s="1"/>
-      <c r="B516" s="1"/>
+      <c r="B516" s="2"/>
       <c r="C516" s="1"/>
       <c r="D516" s="1"/>
       <c r="E516" s="1"/>
@@ -43274,7 +43295,7 @@
     </row>
     <row r="517" ht="12.75" customHeight="1">
       <c r="A517" s="1"/>
-      <c r="B517" s="1"/>
+      <c r="B517" s="2"/>
       <c r="C517" s="1"/>
       <c r="D517" s="1"/>
       <c r="E517" s="1"/>
@@ -43302,7 +43323,7 @@
     </row>
     <row r="518" ht="12.75" customHeight="1">
       <c r="A518" s="1"/>
-      <c r="B518" s="1"/>
+      <c r="B518" s="2"/>
       <c r="C518" s="1"/>
       <c r="D518" s="1"/>
       <c r="E518" s="1"/>
@@ -43330,7 +43351,7 @@
     </row>
     <row r="519" ht="12.75" customHeight="1">
       <c r="A519" s="1"/>
-      <c r="B519" s="1"/>
+      <c r="B519" s="2"/>
       <c r="C519" s="1"/>
       <c r="D519" s="1"/>
       <c r="E519" s="1"/>
@@ -43358,7 +43379,7 @@
     </row>
     <row r="520" ht="12.75" customHeight="1">
       <c r="A520" s="1"/>
-      <c r="B520" s="1"/>
+      <c r="B520" s="2"/>
       <c r="C520" s="1"/>
       <c r="D520" s="1"/>
       <c r="E520" s="1"/>
@@ -43386,7 +43407,7 @@
     </row>
     <row r="521" ht="12.75" customHeight="1">
       <c r="A521" s="1"/>
-      <c r="B521" s="1"/>
+      <c r="B521" s="2"/>
       <c r="C521" s="1"/>
       <c r="D521" s="1"/>
       <c r="E521" s="1"/>
@@ -43414,7 +43435,7 @@
     </row>
     <row r="522" ht="12.75" customHeight="1">
       <c r="A522" s="1"/>
-      <c r="B522" s="1"/>
+      <c r="B522" s="2"/>
       <c r="C522" s="1"/>
       <c r="D522" s="1"/>
       <c r="E522" s="1"/>
@@ -43442,7 +43463,7 @@
     </row>
     <row r="523" ht="12.75" customHeight="1">
       <c r="A523" s="1"/>
-      <c r="B523" s="1"/>
+      <c r="B523" s="2"/>
       <c r="C523" s="1"/>
       <c r="D523" s="1"/>
       <c r="E523" s="1"/>
@@ -43470,7 +43491,7 @@
     </row>
     <row r="524" ht="12.75" customHeight="1">
       <c r="A524" s="1"/>
-      <c r="B524" s="1"/>
+      <c r="B524" s="2"/>
       <c r="C524" s="1"/>
       <c r="D524" s="1"/>
       <c r="E524" s="1"/>
@@ -43498,7 +43519,7 @@
     </row>
     <row r="525" ht="12.75" customHeight="1">
       <c r="A525" s="1"/>
-      <c r="B525" s="1"/>
+      <c r="B525" s="2"/>
       <c r="C525" s="1"/>
       <c r="D525" s="1"/>
       <c r="E525" s="1"/>
@@ -43526,7 +43547,7 @@
     </row>
     <row r="526" ht="12.75" customHeight="1">
       <c r="A526" s="1"/>
-      <c r="B526" s="1"/>
+      <c r="B526" s="2"/>
       <c r="C526" s="1"/>
       <c r="D526" s="1"/>
       <c r="E526" s="1"/>
@@ -43554,7 +43575,7 @@
     </row>
     <row r="527" ht="12.75" customHeight="1">
       <c r="A527" s="1"/>
-      <c r="B527" s="1"/>
+      <c r="B527" s="2"/>
       <c r="C527" s="1"/>
       <c r="D527" s="1"/>
       <c r="E527" s="1"/>
@@ -43582,7 +43603,7 @@
     </row>
     <row r="528" ht="12.75" customHeight="1">
       <c r="A528" s="1"/>
-      <c r="B528" s="1"/>
+      <c r="B528" s="2"/>
       <c r="C528" s="1"/>
       <c r="D528" s="1"/>
       <c r="E528" s="1"/>
@@ -43610,7 +43631,7 @@
     </row>
     <row r="529" ht="12.75" customHeight="1">
       <c r="A529" s="1"/>
-      <c r="B529" s="1"/>
+      <c r="B529" s="2"/>
       <c r="C529" s="1"/>
       <c r="D529" s="1"/>
       <c r="E529" s="1"/>
@@ -43638,7 +43659,7 @@
     </row>
     <row r="530" ht="12.75" customHeight="1">
       <c r="A530" s="1"/>
-      <c r="B530" s="1"/>
+      <c r="B530" s="2"/>
       <c r="C530" s="1"/>
       <c r="D530" s="1"/>
       <c r="E530" s="1"/>
@@ -43666,7 +43687,7 @@
     </row>
     <row r="531" ht="12.75" customHeight="1">
       <c r="A531" s="1"/>
-      <c r="B531" s="1"/>
+      <c r="B531" s="2"/>
       <c r="C531" s="1"/>
       <c r="D531" s="1"/>
       <c r="E531" s="1"/>
@@ -43694,7 +43715,7 @@
     </row>
     <row r="532" ht="12.75" customHeight="1">
       <c r="A532" s="1"/>
-      <c r="B532" s="1"/>
+      <c r="B532" s="2"/>
       <c r="C532" s="1"/>
       <c r="D532" s="1"/>
       <c r="E532" s="1"/>
@@ -43722,7 +43743,7 @@
     </row>
     <row r="533" ht="12.75" customHeight="1">
       <c r="A533" s="1"/>
-      <c r="B533" s="1"/>
+      <c r="B533" s="2"/>
       <c r="C533" s="1"/>
       <c r="D533" s="1"/>
       <c r="E533" s="1"/>
@@ -43750,7 +43771,7 @@
     </row>
     <row r="534" ht="12.75" customHeight="1">
       <c r="A534" s="1"/>
-      <c r="B534" s="1"/>
+      <c r="B534" s="2"/>
       <c r="C534" s="1"/>
       <c r="D534" s="1"/>
       <c r="E534" s="1"/>
@@ -43778,7 +43799,7 @@
     </row>
     <row r="535" ht="12.75" customHeight="1">
       <c r="A535" s="1"/>
-      <c r="B535" s="1"/>
+      <c r="B535" s="2"/>
       <c r="C535" s="1"/>
       <c r="D535" s="1"/>
       <c r="E535" s="1"/>
@@ -43806,7 +43827,7 @@
     </row>
     <row r="536" ht="12.75" customHeight="1">
       <c r="A536" s="1"/>
-      <c r="B536" s="1"/>
+      <c r="B536" s="2"/>
       <c r="C536" s="1"/>
       <c r="D536" s="1"/>
       <c r="E536" s="1"/>
@@ -43834,7 +43855,7 @@
     </row>
     <row r="537" ht="12.75" customHeight="1">
       <c r="A537" s="1"/>
-      <c r="B537" s="1"/>
+      <c r="B537" s="2"/>
       <c r="C537" s="1"/>
       <c r="D537" s="1"/>
       <c r="E537" s="1"/>
@@ -43862,7 +43883,7 @@
     </row>
     <row r="538" ht="12.75" customHeight="1">
       <c r="A538" s="1"/>
-      <c r="B538" s="1"/>
+      <c r="B538" s="2"/>
       <c r="C538" s="1"/>
       <c r="D538" s="1"/>
       <c r="E538" s="1"/>
@@ -43890,7 +43911,7 @@
     </row>
     <row r="539" ht="12.75" customHeight="1">
       <c r="A539" s="1"/>
-      <c r="B539" s="1"/>
+      <c r="B539" s="2"/>
       <c r="C539" s="1"/>
       <c r="D539" s="1"/>
       <c r="E539" s="1"/>
@@ -43918,7 +43939,7 @@
     </row>
     <row r="540" ht="12.75" customHeight="1">
       <c r="A540" s="1"/>
-      <c r="B540" s="1"/>
+      <c r="B540" s="2"/>
       <c r="C540" s="1"/>
       <c r="D540" s="1"/>
       <c r="E540" s="1"/>
@@ -43946,7 +43967,7 @@
     </row>
     <row r="541" ht="12.75" customHeight="1">
       <c r="A541" s="1"/>
-      <c r="B541" s="1"/>
+      <c r="B541" s="2"/>
       <c r="C541" s="1"/>
       <c r="D541" s="1"/>
       <c r="E541" s="1"/>
@@ -43974,7 +43995,7 @@
     </row>
     <row r="542" ht="12.75" customHeight="1">
       <c r="A542" s="1"/>
-      <c r="B542" s="1"/>
+      <c r="B542" s="2"/>
       <c r="C542" s="1"/>
       <c r="D542" s="1"/>
       <c r="E542" s="1"/>
@@ -44002,7 +44023,7 @@
     </row>
     <row r="543" ht="12.75" customHeight="1">
       <c r="A543" s="1"/>
-      <c r="B543" s="1"/>
+      <c r="B543" s="2"/>
       <c r="C543" s="1"/>
       <c r="D543" s="1"/>
       <c r="E543" s="1"/>
@@ -44030,7 +44051,7 @@
     </row>
     <row r="544" ht="12.75" customHeight="1">
       <c r="A544" s="1"/>
-      <c r="B544" s="1"/>
+      <c r="B544" s="2"/>
       <c r="C544" s="1"/>
       <c r="D544" s="1"/>
       <c r="E544" s="1"/>
@@ -44058,7 +44079,7 @@
     </row>
     <row r="545" ht="12.75" customHeight="1">
       <c r="A545" s="1"/>
-      <c r="B545" s="1"/>
+      <c r="B545" s="2"/>
       <c r="C545" s="1"/>
       <c r="D545" s="1"/>
       <c r="E545" s="1"/>
@@ -44086,7 +44107,7 @@
     </row>
     <row r="546" ht="12.75" customHeight="1">
       <c r="A546" s="1"/>
-      <c r="B546" s="1"/>
+      <c r="B546" s="2"/>
       <c r="C546" s="1"/>
       <c r="D546" s="1"/>
       <c r="E546" s="1"/>
@@ -44114,7 +44135,7 @@
     </row>
     <row r="547" ht="12.75" customHeight="1">
       <c r="A547" s="1"/>
-      <c r="B547" s="1"/>
+      <c r="B547" s="2"/>
       <c r="C547" s="1"/>
       <c r="D547" s="1"/>
       <c r="E547" s="1"/>
@@ -44142,7 +44163,7 @@
     </row>
     <row r="548" ht="12.75" customHeight="1">
       <c r="A548" s="1"/>
-      <c r="B548" s="1"/>
+      <c r="B548" s="2"/>
       <c r="C548" s="1"/>
       <c r="D548" s="1"/>
       <c r="E548" s="1"/>
@@ -44170,7 +44191,7 @@
     </row>
     <row r="549" ht="12.75" customHeight="1">
       <c r="A549" s="1"/>
-      <c r="B549" s="1"/>
+      <c r="B549" s="2"/>
       <c r="C549" s="1"/>
       <c r="D549" s="1"/>
       <c r="E549" s="1"/>
@@ -44198,7 +44219,7 @@
     </row>
     <row r="550" ht="12.75" customHeight="1">
       <c r="A550" s="1"/>
-      <c r="B550" s="1"/>
+      <c r="B550" s="2"/>
       <c r="C550" s="1"/>
       <c r="D550" s="1"/>
       <c r="E550" s="1"/>
@@ -44226,7 +44247,7 @@
     </row>
     <row r="551" ht="12.75" customHeight="1">
       <c r="A551" s="1"/>
-      <c r="B551" s="1"/>
+      <c r="B551" s="2"/>
       <c r="C551" s="1"/>
       <c r="D551" s="1"/>
       <c r="E551" s="1"/>
@@ -44254,7 +44275,7 @@
     </row>
     <row r="552" ht="12.75" customHeight="1">
       <c r="A552" s="1"/>
-      <c r="B552" s="1"/>
+      <c r="B552" s="2"/>
       <c r="C552" s="1"/>
       <c r="D552" s="1"/>
       <c r="E552" s="1"/>
@@ -44282,7 +44303,7 @@
     </row>
     <row r="553" ht="12.75" customHeight="1">
       <c r="A553" s="1"/>
-      <c r="B553" s="1"/>
+      <c r="B553" s="2"/>
       <c r="C553" s="1"/>
       <c r="D553" s="1"/>
       <c r="E553" s="1"/>
@@ -44310,7 +44331,7 @@
     </row>
     <row r="554" ht="12.75" customHeight="1">
       <c r="A554" s="1"/>
-      <c r="B554" s="1"/>
+      <c r="B554" s="2"/>
       <c r="C554" s="1"/>
       <c r="D554" s="1"/>
       <c r="E554" s="1"/>
@@ -44338,7 +44359,7 @@
     </row>
     <row r="555" ht="12.75" customHeight="1">
       <c r="A555" s="1"/>
-      <c r="B555" s="1"/>
+      <c r="B555" s="2"/>
       <c r="C555" s="1"/>
       <c r="D555" s="1"/>
       <c r="E555" s="1"/>
@@ -44366,7 +44387,7 @@
     </row>
     <row r="556" ht="12.75" customHeight="1">
       <c r="A556" s="1"/>
-      <c r="B556" s="1"/>
+      <c r="B556" s="2"/>
       <c r="C556" s="1"/>
       <c r="D556" s="1"/>
       <c r="E556" s="1"/>
@@ -44394,7 +44415,7 @@
     </row>
     <row r="557" ht="12.75" customHeight="1">
       <c r="A557" s="1"/>
-      <c r="B557" s="1"/>
+      <c r="B557" s="2"/>
       <c r="C557" s="1"/>
       <c r="D557" s="1"/>
       <c r="E557" s="1"/>
@@ -44422,7 +44443,7 @@
     </row>
     <row r="558" ht="12.75" customHeight="1">
       <c r="A558" s="1"/>
-      <c r="B558" s="1"/>
+      <c r="B558" s="2"/>
       <c r="C558" s="1"/>
       <c r="D558" s="1"/>
       <c r="E558" s="1"/>
@@ -44450,7 +44471,7 @@
     </row>
     <row r="559" ht="12.75" customHeight="1">
       <c r="A559" s="1"/>
-      <c r="B559" s="1"/>
+      <c r="B559" s="2"/>
       <c r="C559" s="1"/>
       <c r="D559" s="1"/>
       <c r="E559" s="1"/>
@@ -44478,7 +44499,7 @@
     </row>
     <row r="560" ht="12.75" customHeight="1">
       <c r="A560" s="1"/>
-      <c r="B560" s="1"/>
+      <c r="B560" s="2"/>
       <c r="C560" s="1"/>
       <c r="D560" s="1"/>
       <c r="E560" s="1"/>
@@ -44506,7 +44527,7 @@
     </row>
     <row r="561" ht="12.75" customHeight="1">
       <c r="A561" s="1"/>
-      <c r="B561" s="1"/>
+      <c r="B561" s="2"/>
       <c r="C561" s="1"/>
       <c r="D561" s="1"/>
       <c r="E561" s="1"/>
@@ -44534,7 +44555,7 @@
     </row>
     <row r="562" ht="12.75" customHeight="1">
       <c r="A562" s="1"/>
-      <c r="B562" s="1"/>
+      <c r="B562" s="2"/>
       <c r="C562" s="1"/>
       <c r="D562" s="1"/>
       <c r="E562" s="1"/>
@@ -44562,7 +44583,7 @@
     </row>
     <row r="563" ht="12.75" customHeight="1">
       <c r="A563" s="1"/>
-      <c r="B563" s="1"/>
+      <c r="B563" s="2"/>
       <c r="C563" s="1"/>
       <c r="D563" s="1"/>
       <c r="E563" s="1"/>
@@ -44590,7 +44611,7 @@
     </row>
     <row r="564" ht="12.75" customHeight="1">
       <c r="A564" s="1"/>
-      <c r="B564" s="1"/>
+      <c r="B564" s="2"/>
       <c r="C564" s="1"/>
       <c r="D564" s="1"/>
       <c r="E564" s="1"/>
@@ -44618,7 +44639,7 @@
     </row>
     <row r="565" ht="12.75" customHeight="1">
       <c r="A565" s="1"/>
-      <c r="B565" s="1"/>
+      <c r="B565" s="2"/>
       <c r="C565" s="1"/>
       <c r="D565" s="1"/>
       <c r="E565" s="1"/>
@@ -44646,7 +44667,7 @@
     </row>
     <row r="566" ht="12.75" customHeight="1">
       <c r="A566" s="1"/>
-      <c r="B566" s="1"/>
+      <c r="B566" s="2"/>
       <c r="C566" s="1"/>
       <c r="D566" s="1"/>
       <c r="E566" s="1"/>
@@ -44674,7 +44695,7 @@
     </row>
     <row r="567" ht="12.75" customHeight="1">
       <c r="A567" s="1"/>
-      <c r="B567" s="1"/>
+      <c r="B567" s="2"/>
       <c r="C567" s="1"/>
       <c r="D567" s="1"/>
       <c r="E567" s="1"/>
@@ -44702,7 +44723,7 @@
     </row>
     <row r="568" ht="12.75" customHeight="1">
       <c r="A568" s="1"/>
-      <c r="B568" s="1"/>
+      <c r="B568" s="2"/>
       <c r="C568" s="1"/>
       <c r="D568" s="1"/>
       <c r="E568" s="1"/>
@@ -44730,7 +44751,7 @@
     </row>
     <row r="569" ht="12.75" customHeight="1">
       <c r="A569" s="1"/>
-      <c r="B569" s="1"/>
+      <c r="B569" s="2"/>
       <c r="C569" s="1"/>
       <c r="D569" s="1"/>
       <c r="E569" s="1"/>
@@ -44758,7 +44779,7 @@
     </row>
     <row r="570" ht="12.75" customHeight="1">
       <c r="A570" s="1"/>
-      <c r="B570" s="1"/>
+      <c r="B570" s="2"/>
       <c r="C570" s="1"/>
       <c r="D570" s="1"/>
       <c r="E570" s="1"/>
@@ -44786,7 +44807,7 @@
     </row>
     <row r="571" ht="12.75" customHeight="1">
       <c r="A571" s="1"/>
-      <c r="B571" s="1"/>
+      <c r="B571" s="2"/>
       <c r="C571" s="1"/>
       <c r="D571" s="1"/>
       <c r="E571" s="1"/>
@@ -44814,7 +44835,7 @@
     </row>
     <row r="572" ht="12.75" customHeight="1">
       <c r="A572" s="1"/>
-      <c r="B572" s="1"/>
+      <c r="B572" s="2"/>
       <c r="C572" s="1"/>
       <c r="D572" s="1"/>
       <c r="E572" s="1"/>
@@ -44842,7 +44863,7 @@
     </row>
     <row r="573" ht="12.75" customHeight="1">
       <c r="A573" s="1"/>
-      <c r="B573" s="1"/>
+      <c r="B573" s="2"/>
       <c r="C573" s="1"/>
       <c r="D573" s="1"/>
       <c r="E573" s="1"/>
@@ -44870,7 +44891,7 @@
     </row>
     <row r="574" ht="12.75" customHeight="1">
       <c r="A574" s="1"/>
-      <c r="B574" s="1"/>
+      <c r="B574" s="2"/>
       <c r="C574" s="1"/>
       <c r="D574" s="1"/>
       <c r="E574" s="1"/>
@@ -44898,7 +44919,7 @@
     </row>
     <row r="575" ht="12.75" customHeight="1">
       <c r="A575" s="1"/>
-      <c r="B575" s="1"/>
+      <c r="B575" s="2"/>
       <c r="C575" s="1"/>
       <c r="D575" s="1"/>
       <c r="E575" s="1"/>
@@ -44926,7 +44947,7 @@
     </row>
     <row r="576" ht="12.75" customHeight="1">
       <c r="A576" s="1"/>
-      <c r="B576" s="1"/>
+      <c r="B576" s="2"/>
       <c r="C576" s="1"/>
       <c r="D576" s="1"/>
       <c r="E576" s="1"/>
@@ -44954,7 +44975,7 @@
     </row>
     <row r="577" ht="12.75" customHeight="1">
       <c r="A577" s="1"/>
-      <c r="B577" s="1"/>
+      <c r="B577" s="2"/>
       <c r="C577" s="1"/>
       <c r="D577" s="1"/>
       <c r="E577" s="1"/>
@@ -44982,7 +45003,7 @@
     </row>
     <row r="578" ht="12.75" customHeight="1">
       <c r="A578" s="1"/>
-      <c r="B578" s="1"/>
+      <c r="B578" s="2"/>
       <c r="C578" s="1"/>
       <c r="D578" s="1"/>
       <c r="E578" s="1"/>
@@ -45010,7 +45031,7 @@
     </row>
     <row r="579" ht="12.75" customHeight="1">
       <c r="A579" s="1"/>
-      <c r="B579" s="1"/>
+      <c r="B579" s="2"/>
       <c r="C579" s="1"/>
       <c r="D579" s="1"/>
       <c r="E579" s="1"/>
@@ -45038,7 +45059,7 @@
     </row>
     <row r="580" ht="12.75" customHeight="1">
       <c r="A580" s="1"/>
-      <c r="B580" s="1"/>
+      <c r="B580" s="2"/>
       <c r="C580" s="1"/>
       <c r="D580" s="1"/>
       <c r="E580" s="1"/>
@@ -45066,7 +45087,7 @@
     </row>
     <row r="581" ht="12.75" customHeight="1">
       <c r="A581" s="1"/>
-      <c r="B581" s="1"/>
+      <c r="B581" s="2"/>
       <c r="C581" s="1"/>
       <c r="D581" s="1"/>
       <c r="E581" s="1"/>
@@ -45094,7 +45115,7 @@
     </row>
     <row r="582" ht="12.75" customHeight="1">
       <c r="A582" s="1"/>
-      <c r="B582" s="1"/>
+      <c r="B582" s="2"/>
       <c r="C582" s="1"/>
       <c r="D582" s="1"/>
       <c r="E582" s="1"/>
@@ -45122,7 +45143,7 @@
     </row>
     <row r="583" ht="12.75" customHeight="1">
       <c r="A583" s="1"/>
-      <c r="B583" s="1"/>
+      <c r="B583" s="2"/>
       <c r="C583" s="1"/>
       <c r="D583" s="1"/>
       <c r="E583" s="1"/>
@@ -45150,7 +45171,7 @@
     </row>
     <row r="584" ht="12.75" customHeight="1">
       <c r="A584" s="1"/>
-      <c r="B584" s="1"/>
+      <c r="B584" s="2"/>
       <c r="C584" s="1"/>
       <c r="D584" s="1"/>
       <c r="E584" s="1"/>
@@ -45178,7 +45199,7 @@
     </row>
     <row r="585" ht="12.75" customHeight="1">
       <c r="A585" s="1"/>
-      <c r="B585" s="1"/>
+      <c r="B585" s="2"/>
       <c r="C585" s="1"/>
       <c r="D585" s="1"/>
       <c r="E585" s="1"/>
@@ -45206,7 +45227,7 @@
     </row>
     <row r="586" ht="12.75" customHeight="1">
       <c r="A586" s="1"/>
-      <c r="B586" s="1"/>
+      <c r="B586" s="2"/>
       <c r="C586" s="1"/>
       <c r="D586" s="1"/>
       <c r="E586" s="1"/>
@@ -45234,7 +45255,7 @@
     </row>
     <row r="587" ht="12.75" customHeight="1">
       <c r="A587" s="1"/>
-      <c r="B587" s="1"/>
+      <c r="B587" s="2"/>
       <c r="C587" s="1"/>
       <c r="D587" s="1"/>
       <c r="E587" s="1"/>
@@ -45262,7 +45283,7 @@
     </row>
     <row r="588" ht="12.75" customHeight="1">
       <c r="A588" s="1"/>
-      <c r="B588" s="1"/>
+      <c r="B588" s="2"/>
       <c r="C588" s="1"/>
       <c r="D588" s="1"/>
       <c r="E588" s="1"/>
@@ -45290,7 +45311,7 @@
     </row>
     <row r="589" ht="12.75" customHeight="1">
       <c r="A589" s="1"/>
-      <c r="B589" s="1"/>
+      <c r="B589" s="2"/>
       <c r="C589" s="1"/>
       <c r="D589" s="1"/>
       <c r="E589" s="1"/>
@@ -45318,7 +45339,7 @@
     </row>
     <row r="590" ht="12.75" customHeight="1">
       <c r="A590" s="1"/>
-      <c r="B590" s="1"/>
+      <c r="B590" s="2"/>
       <c r="C590" s="1"/>
       <c r="D590" s="1"/>
       <c r="E590" s="1"/>
@@ -45346,7 +45367,7 @@
     </row>
     <row r="591" ht="12.75" customHeight="1">
       <c r="A591" s="1"/>
-      <c r="B591" s="1"/>
+      <c r="B591" s="2"/>
       <c r="C591" s="1"/>
       <c r="D591" s="1"/>
       <c r="E591" s="1"/>
@@ -45374,7 +45395,7 @@
     </row>
     <row r="592" ht="12.75" customHeight="1">
       <c r="A592" s="1"/>
-      <c r="B592" s="1"/>
+      <c r="B592" s="2"/>
       <c r="C592" s="1"/>
       <c r="D592" s="1"/>
       <c r="E592" s="1"/>
@@ -45402,7 +45423,7 @@
     </row>
     <row r="593" ht="12.75" customHeight="1">
       <c r="A593" s="1"/>
-      <c r="B593" s="1"/>
+      <c r="B593" s="2"/>
       <c r="C593" s="1"/>
       <c r="D593" s="1"/>
       <c r="E593" s="1"/>
@@ -45430,7 +45451,7 @@
     </row>
     <row r="594" ht="12.75" customHeight="1">
       <c r="A594" s="1"/>
-      <c r="B594" s="1"/>
+      <c r="B594" s="2"/>
       <c r="C594" s="1"/>
       <c r="D594" s="1"/>
       <c r="E594" s="1"/>
@@ -45458,7 +45479,7 @@
     </row>
     <row r="595" ht="12.75" customHeight="1">
       <c r="A595" s="1"/>
-      <c r="B595" s="1"/>
+      <c r="B595" s="2"/>
       <c r="C595" s="1"/>
       <c r="D595" s="1"/>
       <c r="E595" s="1"/>
@@ -45486,7 +45507,7 @@
     </row>
     <row r="596" ht="12.75" customHeight="1">
       <c r="A596" s="1"/>
-      <c r="B596" s="1"/>
+      <c r="B596" s="2"/>
       <c r="C596" s="1"/>
       <c r="D596" s="1"/>
       <c r="E596" s="1"/>
@@ -45514,7 +45535,7 @@
     </row>
     <row r="597" ht="12.75" customHeight="1">
       <c r="A597" s="1"/>
-      <c r="B597" s="1"/>
+      <c r="B597" s="2"/>
       <c r="C597" s="1"/>
       <c r="D597" s="1"/>
       <c r="E597" s="1"/>
@@ -45542,7 +45563,7 @@
     </row>
     <row r="598" ht="12.75" customHeight="1">
       <c r="A598" s="1"/>
-      <c r="B598" s="1"/>
+      <c r="B598" s="2"/>
       <c r="C598" s="1"/>
       <c r="D598" s="1"/>
       <c r="E598" s="1"/>
@@ -45570,7 +45591,7 @@
     </row>
     <row r="599" ht="12.75" customHeight="1">
       <c r="A599" s="1"/>
-      <c r="B599" s="1"/>
+      <c r="B599" s="2"/>
       <c r="C599" s="1"/>
       <c r="D599" s="1"/>
       <c r="E599" s="1"/>
@@ -45598,7 +45619,7 @@
     </row>
     <row r="600" ht="12.75" customHeight="1">
       <c r="A600" s="1"/>
-      <c r="B600" s="1"/>
+      <c r="B600" s="2"/>
       <c r="C600" s="1"/>
       <c r="D600" s="1"/>
       <c r="E600" s="1"/>
@@ -45626,7 +45647,7 @@
     </row>
     <row r="601" ht="12.75" customHeight="1">
       <c r="A601" s="1"/>
-      <c r="B601" s="1"/>
+      <c r="B601" s="2"/>
       <c r="C601" s="1"/>
       <c r="D601" s="1"/>
       <c r="E601" s="1"/>
@@ -45654,7 +45675,7 @@
     </row>
     <row r="602" ht="12.75" customHeight="1">
       <c r="A602" s="1"/>
-      <c r="B602" s="1"/>
+      <c r="B602" s="2"/>
       <c r="C602" s="1"/>
       <c r="D602" s="1"/>
       <c r="E602" s="1"/>
@@ -45682,7 +45703,7 @@
     </row>
     <row r="603" ht="12.75" customHeight="1">
       <c r="A603" s="1"/>
-      <c r="B603" s="1"/>
+      <c r="B603" s="2"/>
       <c r="C603" s="1"/>
       <c r="D603" s="1"/>
       <c r="E603" s="1"/>
@@ -45710,7 +45731,7 @@
     </row>
     <row r="604" ht="12.75" customHeight="1">
       <c r="A604" s="1"/>
-      <c r="B604" s="1"/>
+      <c r="B604" s="2"/>
       <c r="C604" s="1"/>
       <c r="D604" s="1"/>
       <c r="E604" s="1"/>
@@ -45738,7 +45759,7 @@
     </row>
     <row r="605" ht="12.75" customHeight="1">
       <c r="A605" s="1"/>
-      <c r="B605" s="1"/>
+      <c r="B605" s="2"/>
       <c r="C605" s="1"/>
       <c r="D605" s="1"/>
       <c r="E605" s="1"/>
@@ -45766,7 +45787,7 @@
     </row>
     <row r="606" ht="12.75" customHeight="1">
       <c r="A606" s="1"/>
-      <c r="B606" s="1"/>
+      <c r="B606" s="2"/>
       <c r="C606" s="1"/>
       <c r="D606" s="1"/>
       <c r="E606" s="1"/>
@@ -45794,7 +45815,7 @@
     </row>
     <row r="607" ht="12.75" customHeight="1">
       <c r="A607" s="1"/>
-      <c r="B607" s="1"/>
+      <c r="B607" s="2"/>
       <c r="C607" s="1"/>
       <c r="D607" s="1"/>
       <c r="E607" s="1"/>
@@ -45822,7 +45843,7 @@
     </row>
     <row r="608" ht="12.75" customHeight="1">
       <c r="A608" s="1"/>
-      <c r="B608" s="1"/>
+      <c r="B608" s="2"/>
       <c r="C608" s="1"/>
       <c r="D608" s="1"/>
       <c r="E608" s="1"/>
@@ -45850,7 +45871,7 @@
     </row>
     <row r="609" ht="12.75" customHeight="1">
       <c r="A609" s="1"/>
-      <c r="B609" s="1"/>
+      <c r="B609" s="2"/>
       <c r="C609" s="1"/>
       <c r="D609" s="1"/>
       <c r="E609" s="1"/>
@@ -45878,7 +45899,7 @@
     </row>
     <row r="610" ht="12.75" customHeight="1">
       <c r="A610" s="1"/>
-      <c r="B610" s="1"/>
+      <c r="B610" s="2"/>
       <c r="C610" s="1"/>
       <c r="D610" s="1"/>
       <c r="E610" s="1"/>
@@ -45906,7 +45927,7 @@
     </row>
     <row r="611" ht="12.75" customHeight="1">
       <c r="A611" s="1"/>
-      <c r="B611" s="1"/>
+      <c r="B611" s="2"/>
       <c r="C611" s="1"/>
       <c r="D611" s="1"/>
       <c r="E611" s="1"/>
@@ -45934,7 +45955,7 @@
     </row>
     <row r="612" ht="12.75" customHeight="1">
       <c r="A612" s="1"/>
-      <c r="B612" s="1"/>
+      <c r="B612" s="2"/>
       <c r="C612" s="1"/>
       <c r="D612" s="1"/>
       <c r="E612" s="1"/>
@@ -45962,7 +45983,7 @@
     </row>
     <row r="613" ht="12.75" customHeight="1">
       <c r="A613" s="1"/>
-      <c r="B613" s="1"/>
+      <c r="B613" s="2"/>
       <c r="C613" s="1"/>
       <c r="D613" s="1"/>
       <c r="E613" s="1"/>
@@ -45990,7 +46011,7 @@
     </row>
     <row r="614" ht="12.75" customHeight="1">
       <c r="A614" s="1"/>
-      <c r="B614" s="1"/>
+      <c r="B614" s="2"/>
       <c r="C614" s="1"/>
       <c r="D614" s="1"/>
       <c r="E614" s="1"/>
@@ -46018,7 +46039,7 @@
     </row>
     <row r="615" ht="12.75" customHeight="1">
       <c r="A615" s="1"/>
-      <c r="B615" s="1"/>
+      <c r="B615" s="2"/>
       <c r="C615" s="1"/>
       <c r="D615" s="1"/>
       <c r="E615" s="1"/>
@@ -46046,7 +46067,7 @@
     </row>
     <row r="616" ht="12.75" customHeight="1">
       <c r="A616" s="1"/>
-      <c r="B616" s="1"/>
+      <c r="B616" s="2"/>
       <c r="C616" s="1"/>
       <c r="D616" s="1"/>
       <c r="E616" s="1"/>
@@ -46074,7 +46095,7 @@
     </row>
     <row r="617" ht="12.75" customHeight="1">
       <c r="A617" s="1"/>
-      <c r="B617" s="1"/>
+      <c r="B617" s="2"/>
       <c r="C617" s="1"/>
       <c r="D617" s="1"/>
       <c r="E617" s="1"/>
@@ -46102,7 +46123,7 @@
     </row>
     <row r="618" ht="12.75" customHeight="1">
       <c r="A618" s="1"/>
-      <c r="B618" s="1"/>
+      <c r="B618" s="2"/>
       <c r="C618" s="1"/>
       <c r="D618" s="1"/>
       <c r="E618" s="1"/>
@@ -46130,7 +46151,7 @@
     </row>
     <row r="619" ht="12.75" customHeight="1">
       <c r="A619" s="1"/>
-      <c r="B619" s="1"/>
+      <c r="B619" s="2"/>
       <c r="C619" s="1"/>
       <c r="D619" s="1"/>
       <c r="E619" s="1"/>
@@ -46158,7 +46179,7 @@
     </row>
     <row r="620" ht="12.75" customHeight="1">
       <c r="A620" s="1"/>
-      <c r="B620" s="1"/>
+      <c r="B620" s="2"/>
       <c r="C620" s="1"/>
       <c r="D620" s="1"/>
       <c r="E620" s="1"/>
@@ -46186,7 +46207,7 @@
     </row>
     <row r="621" ht="12.75" customHeight="1">
       <c r="A621" s="1"/>
-      <c r="B621" s="1"/>
+      <c r="B621" s="2"/>
       <c r="C621" s="1"/>
       <c r="D621" s="1"/>
       <c r="E621" s="1"/>
@@ -46214,7 +46235,7 @@
     </row>
     <row r="622" ht="12.75" customHeight="1">
       <c r="A622" s="1"/>
-      <c r="B622" s="1"/>
+      <c r="B622" s="2"/>
       <c r="C622" s="1"/>
       <c r="D622" s="1"/>
       <c r="E622" s="1"/>
@@ -46242,7 +46263,7 @@
     </row>
     <row r="623" ht="12.75" customHeight="1">
       <c r="A623" s="1"/>
-      <c r="B623" s="1"/>
+      <c r="B623" s="2"/>
       <c r="C623" s="1"/>
       <c r="D623" s="1"/>
       <c r="E623" s="1"/>
@@ -46270,7 +46291,7 @@
     </row>
     <row r="624" ht="12.75" customHeight="1">
       <c r="A624" s="1"/>
-      <c r="B624" s="1"/>
+      <c r="B624" s="2"/>
       <c r="C624" s="1"/>
       <c r="D624" s="1"/>
       <c r="E624" s="1"/>
@@ -46298,7 +46319,7 @@
     </row>
     <row r="625" ht="12.75" customHeight="1">
       <c r="A625" s="1"/>
-      <c r="B625" s="1"/>
+      <c r="B625" s="2"/>
       <c r="C625" s="1"/>
       <c r="D625" s="1"/>
       <c r="E625" s="1"/>
@@ -46326,7 +46347,7 @@
     </row>
     <row r="626" ht="12.75" customHeight="1">
       <c r="A626" s="1"/>
-      <c r="B626" s="1"/>
+      <c r="B626" s="2"/>
       <c r="C626" s="1"/>
       <c r="D626" s="1"/>
       <c r="E626" s="1"/>
@@ -46354,7 +46375,7 @@
     </row>
     <row r="627" ht="12.75" customHeight="1">
       <c r="A627" s="1"/>
-      <c r="B627" s="1"/>
+      <c r="B627" s="2"/>
       <c r="C627" s="1"/>
       <c r="D627" s="1"/>
       <c r="E627" s="1"/>
@@ -46382,7 +46403,7 @@
     </row>
     <row r="628" ht="12.75" customHeight="1">
       <c r="A628" s="1"/>
-      <c r="B628" s="1"/>
+      <c r="B628" s="2"/>
       <c r="C628" s="1"/>
       <c r="D628" s="1"/>
       <c r="E628" s="1"/>
@@ -46410,7 +46431,7 @@
     </row>
     <row r="629" ht="12.75" customHeight="1">
       <c r="A629" s="1"/>
-      <c r="B629" s="1"/>
+      <c r="B629" s="2"/>
       <c r="C629" s="1"/>
       <c r="D629" s="1"/>
       <c r="E629" s="1"/>
@@ -46438,7 +46459,7 @@
     </row>
     <row r="630" ht="12.75" customHeight="1">
       <c r="A630" s="1"/>
-      <c r="B630" s="1"/>
+      <c r="B630" s="2"/>
       <c r="C630" s="1"/>
       <c r="D630" s="1"/>
       <c r="E630" s="1"/>
@@ -46466,7 +46487,7 @@
     </row>
     <row r="631" ht="12.75" customHeight="1">
       <c r="A631" s="1"/>
-      <c r="B631" s="1"/>
+      <c r="B631" s="2"/>
       <c r="C631" s="1"/>
       <c r="D631" s="1"/>
       <c r="E631" s="1"/>
@@ -46494,7 +46515,7 @@
     </row>
     <row r="632" ht="12.75" customHeight="1">
       <c r="A632" s="1"/>
-      <c r="B632" s="1"/>
+      <c r="B632" s="2"/>
       <c r="C632" s="1"/>
       <c r="D632" s="1"/>
       <c r="E632" s="1"/>
@@ -46522,7 +46543,7 @@
     </row>
     <row r="633" ht="12.75" customHeight="1">
       <c r="A633" s="1"/>
-      <c r="B633" s="1"/>
+      <c r="B633" s="2"/>
       <c r="C633" s="1"/>
       <c r="D633" s="1"/>
       <c r="E633" s="1"/>
@@ -46550,7 +46571,7 @@
     </row>
     <row r="634" ht="12.75" customHeight="1">
       <c r="A634" s="1"/>
-      <c r="B634" s="1"/>
+      <c r="B634" s="2"/>
       <c r="C634" s="1"/>
       <c r="D634" s="1"/>
       <c r="E634" s="1"/>
@@ -46578,7 +46599,7 @@
     </row>
     <row r="635" ht="12.75" customHeight="1">
       <c r="A635" s="1"/>
-      <c r="B635" s="1"/>
+      <c r="B635" s="2"/>
       <c r="C635" s="1"/>
       <c r="D635" s="1"/>
       <c r="E635" s="1"/>
@@ -46606,7 +46627,7 @@
     </row>
     <row r="636" ht="12.75" customHeight="1">
       <c r="A636" s="1"/>
-      <c r="B636" s="1"/>
+      <c r="B636" s="2"/>
       <c r="C636" s="1"/>
       <c r="D636" s="1"/>
       <c r="E636" s="1"/>
@@ -46634,7 +46655,7 @@
     </row>
     <row r="637" ht="12.75" customHeight="1">
       <c r="A637" s="1"/>
-      <c r="B637" s="1"/>
+      <c r="B637" s="2"/>
       <c r="C637" s="1"/>
       <c r="D637" s="1"/>
       <c r="E637" s="1"/>
@@ -46662,7 +46683,7 @@
     </row>
     <row r="638" ht="12.75" customHeight="1">
       <c r="A638" s="1"/>
-      <c r="B638" s="1"/>
+      <c r="B638" s="2"/>
       <c r="C638" s="1"/>
       <c r="D638" s="1"/>
       <c r="E638" s="1"/>
@@ -46690,7 +46711,7 @@
     </row>
     <row r="639" ht="12.75" customHeight="1">
       <c r="A639" s="1"/>
-      <c r="B639" s="1"/>
+      <c r="B639" s="2"/>
       <c r="C639" s="1"/>
       <c r="D639" s="1"/>
       <c r="E639" s="1"/>
@@ -46718,7 +46739,7 @@
     </row>
     <row r="640" ht="12.75" customHeight="1">
       <c r="A640" s="1"/>
-      <c r="B640" s="1"/>
+      <c r="B640" s="2"/>
       <c r="C640" s="1"/>
       <c r="D640" s="1"/>
       <c r="E640" s="1"/>
@@ -46746,7 +46767,7 @@
     </row>
     <row r="641" ht="12.75" customHeight="1">
       <c r="A641" s="1"/>
-      <c r="B641" s="1"/>
+      <c r="B641" s="2"/>
       <c r="C641" s="1"/>
       <c r="D641" s="1"/>
       <c r="E641" s="1"/>
@@ -46774,7 +46795,7 @@
     </row>
     <row r="642" ht="12.75" customHeight="1">
       <c r="A642" s="1"/>
-      <c r="B642" s="1"/>
+      <c r="B642" s="2"/>
       <c r="C642" s="1"/>
       <c r="D642" s="1"/>
       <c r="E642" s="1"/>
@@ -46802,7 +46823,7 @@
     </row>
     <row r="643" ht="12.75" customHeight="1">
       <c r="A643" s="1"/>
-      <c r="B643" s="1"/>
+      <c r="B643" s="2"/>
       <c r="C643" s="1"/>
       <c r="D643" s="1"/>
       <c r="E643" s="1"/>
@@ -46830,7 +46851,7 @@
     </row>
     <row r="644" ht="12.75" customHeight="1">
       <c r="A644" s="1"/>
-      <c r="B644" s="1"/>
+      <c r="B644" s="2"/>
       <c r="C644" s="1"/>
       <c r="D644" s="1"/>
       <c r="E644" s="1"/>
@@ -46858,7 +46879,7 @@
     </row>
     <row r="645" ht="12.75" customHeight="1">
       <c r="A645" s="1"/>
-      <c r="B645" s="1"/>
+      <c r="B645" s="2"/>
       <c r="C645" s="1"/>
       <c r="D645" s="1"/>
       <c r="E645" s="1"/>
@@ -46886,7 +46907,7 @@
     </row>
     <row r="646" ht="12.75" customHeight="1">
       <c r="A646" s="1"/>
-      <c r="B646" s="1"/>
+      <c r="B646" s="2"/>
       <c r="C646" s="1"/>
       <c r="D646" s="1"/>
       <c r="E646" s="1"/>
@@ -46914,7 +46935,7 @@
     </row>
     <row r="647" ht="12.75" customHeight="1">
       <c r="A647" s="1"/>
-      <c r="B647" s="1"/>
+      <c r="B647" s="2"/>
       <c r="C647" s="1"/>
       <c r="D647" s="1"/>
       <c r="E647" s="1"/>
@@ -46942,7 +46963,7 @@
     </row>
     <row r="648" ht="12.75" customHeight="1">
       <c r="A648" s="1"/>
-      <c r="B648" s="1"/>
+      <c r="B648" s="2"/>
       <c r="C648" s="1"/>
       <c r="D648" s="1"/>
       <c r="E648" s="1"/>
@@ -46970,7 +46991,7 @@
     </row>
     <row r="649" ht="12.75" customHeight="1">
       <c r="A649" s="1"/>
-      <c r="B649" s="1"/>
+      <c r="B649" s="2"/>
       <c r="C649" s="1"/>
       <c r="D649" s="1"/>
       <c r="E649" s="1"/>
@@ -46998,7 +47019,7 @@
     </row>
     <row r="650" ht="12.75" customHeight="1">
       <c r="A650" s="1"/>
-      <c r="B650" s="1"/>
+      <c r="B650" s="2"/>
       <c r="C650" s="1"/>
       <c r="D650" s="1"/>
       <c r="E650" s="1"/>
@@ -47026,7 +47047,7 @@
     </row>
     <row r="651" ht="12.75" customHeight="1">
       <c r="A651" s="1"/>
-      <c r="B651" s="1"/>
+      <c r="B651" s="2"/>
       <c r="C651" s="1"/>
       <c r="D651" s="1"/>
       <c r="E651" s="1"/>
@@ -47054,7 +47075,7 @@
     </row>
     <row r="652" ht="12.75" customHeight="1">
       <c r="A652" s="1"/>
-      <c r="B652" s="1"/>
+      <c r="B652" s="2"/>
       <c r="C652" s="1"/>
       <c r="D652" s="1"/>
       <c r="E652" s="1"/>
@@ -47082,7 +47103,7 @@
     </row>
     <row r="653" ht="12.75" customHeight="1">
       <c r="A653" s="1"/>
-      <c r="B653" s="1"/>
+      <c r="B653" s="2"/>
       <c r="C653" s="1"/>
       <c r="D653" s="1"/>
       <c r="E653" s="1"/>
@@ -47110,7 +47131,7 @@
     </row>
     <row r="654" ht="12.75" customHeight="1">
       <c r="A654" s="1"/>
-      <c r="B654" s="1"/>
+      <c r="B654" s="2"/>
       <c r="C654" s="1"/>
       <c r="D654" s="1"/>
       <c r="E654" s="1"/>
@@ -47138,7 +47159,7 @@
     </row>
     <row r="655" ht="12.75" customHeight="1">
       <c r="A655" s="1"/>
-      <c r="B655" s="1"/>
+      <c r="B655" s="2"/>
       <c r="C655" s="1"/>
       <c r="D655" s="1"/>
       <c r="E655" s="1"/>
@@ -47166,7 +47187,7 @@
     </row>
     <row r="656" ht="12.75" customHeight="1">
       <c r="A656" s="1"/>
-      <c r="B656" s="1"/>
+      <c r="B656" s="2"/>
       <c r="C656" s="1"/>
       <c r="D656" s="1"/>
       <c r="E656" s="1"/>
@@ -47194,7 +47215,7 @@
     </row>
     <row r="657" ht="12.75" customHeight="1">
       <c r="A657" s="1"/>
-      <c r="B657" s="1"/>
+      <c r="B657" s="2"/>
       <c r="C657" s="1"/>
       <c r="D657" s="1"/>
       <c r="E657" s="1"/>
@@ -47222,7 +47243,7 @@
     </row>
     <row r="658" ht="12.75" customHeight="1">
       <c r="A658" s="1"/>
-      <c r="B658" s="1"/>
+      <c r="B658" s="2"/>
       <c r="C658" s="1"/>
       <c r="D658" s="1"/>
       <c r="E658" s="1"/>
@@ -47250,7 +47271,7 @@
     </row>
     <row r="659" ht="12.75" customHeight="1">
       <c r="A659" s="1"/>
-      <c r="B659" s="1"/>
+      <c r="B659" s="2"/>
       <c r="C659" s="1"/>
       <c r="D659" s="1"/>
       <c r="E659" s="1"/>
@@ -47278,7 +47299,7 @@
     </row>
     <row r="660" ht="12.75" customHeight="1">
       <c r="A660" s="1"/>
-      <c r="B660" s="1"/>
+      <c r="B660" s="2"/>
       <c r="C660" s="1"/>
       <c r="D660" s="1"/>
       <c r="E660" s="1"/>
@@ -47306,7 +47327,7 @@
     </row>
     <row r="661" ht="12.75" customHeight="1">
       <c r="A661" s="1"/>
-      <c r="B661" s="1"/>
+      <c r="B661" s="2"/>
       <c r="C661" s="1"/>
       <c r="D661" s="1"/>
       <c r="E661" s="1"/>
@@ -47334,7 +47355,7 @@
     </row>
     <row r="662" ht="12.75" customHeight="1">
       <c r="A662" s="1"/>
-      <c r="B662" s="1"/>
+      <c r="B662" s="2"/>
       <c r="C662" s="1"/>
       <c r="D662" s="1"/>
       <c r="E662" s="1"/>
@@ -47362,7 +47383,7 @@
     </row>
     <row r="663" ht="12.75" customHeight="1">
       <c r="A663" s="1"/>
-      <c r="B663" s="1"/>
+      <c r="B663" s="2"/>
       <c r="C663" s="1"/>
       <c r="D663" s="1"/>
       <c r="E663" s="1"/>
@@ -47390,7 +47411,7 @@
     </row>
     <row r="664" ht="12.75" customHeight="1">
       <c r="A664" s="1"/>
-      <c r="B664" s="1"/>
+      <c r="B664" s="2"/>
       <c r="C664" s="1"/>
       <c r="D664" s="1"/>
       <c r="E664" s="1"/>
@@ -47418,7 +47439,7 @@
     </row>
     <row r="665" ht="12.75" customHeight="1">
       <c r="A665" s="1"/>
-      <c r="B665" s="1"/>
+      <c r="B665" s="2"/>
       <c r="C665" s="1"/>
       <c r="D665" s="1"/>
       <c r="E665" s="1"/>
@@ -47446,7 +47467,7 @@
     </row>
     <row r="666" ht="12.75" customHeight="1">
       <c r="A666" s="1"/>
-      <c r="B666" s="1"/>
+      <c r="B666" s="2"/>
       <c r="C666" s="1"/>
       <c r="D666" s="1"/>
       <c r="E666" s="1"/>
@@ -47474,7 +47495,7 @@
     </row>
     <row r="667" ht="12.75" customHeight="1">
       <c r="A667" s="1"/>
-      <c r="B667" s="1"/>
+      <c r="B667" s="2"/>
       <c r="C667" s="1"/>
       <c r="D667" s="1"/>
       <c r="E667" s="1"/>
@@ -47502,7 +47523,7 @@
     </row>
     <row r="668" ht="12.75" customHeight="1">
       <c r="A668" s="1"/>
-      <c r="B668" s="1"/>
+      <c r="B668" s="2"/>
       <c r="C668" s="1"/>
       <c r="D668" s="1"/>
       <c r="E668" s="1"/>
@@ -47530,7 +47551,7 @@
     </row>
     <row r="669" ht="12.75" customHeight="1">
       <c r="A669" s="1"/>
-      <c r="B669" s="1"/>
+      <c r="B669" s="2"/>
       <c r="C669" s="1"/>
       <c r="D669" s="1"/>
       <c r="E669" s="1"/>
@@ -47558,7 +47579,7 @@
     </row>
     <row r="670" ht="12.75" customHeight="1">
       <c r="A670" s="1"/>
-      <c r="B670" s="1"/>
+      <c r="B670" s="2"/>
       <c r="C670" s="1"/>
       <c r="D670" s="1"/>
       <c r="E670" s="1"/>
@@ -47586,7 +47607,7 @@
     </row>
     <row r="671" ht="12.75" customHeight="1">
       <c r="A671" s="1"/>
-      <c r="B671" s="1"/>
+      <c r="B671" s="2"/>
       <c r="C671" s="1"/>
       <c r="D671" s="1"/>
       <c r="E671" s="1"/>
@@ -47614,7 +47635,7 @@
     </row>
     <row r="672" ht="12.75" customHeight="1">
       <c r="A672" s="1"/>
-      <c r="B672" s="1"/>
+      <c r="B672" s="2"/>
       <c r="C672" s="1"/>
       <c r="D672" s="1"/>
       <c r="E672" s="1"/>
@@ -47642,7 +47663,7 @@
     </row>
     <row r="673" ht="12.75" customHeight="1">
       <c r="A673" s="1"/>
-      <c r="B673" s="1"/>
+      <c r="B673" s="2"/>
       <c r="C673" s="1"/>
       <c r="D673" s="1"/>
       <c r="E673" s="1"/>
@@ -47670,7 +47691,7 @@
     </row>
     <row r="674" ht="12.75" customHeight="1">
       <c r="A674" s="1"/>
-      <c r="B674" s="1"/>
+      <c r="B674" s="2"/>
       <c r="C674" s="1"/>
       <c r="D674" s="1"/>
       <c r="E674" s="1"/>
@@ -47698,7 +47719,7 @@
     </row>
     <row r="675" ht="12.75" customHeight="1">
       <c r="A675" s="1"/>
-      <c r="B675" s="1"/>
+      <c r="B675" s="2"/>
       <c r="C675" s="1"/>
       <c r="D675" s="1"/>
       <c r="E675" s="1"/>
@@ -47726,7 +47747,7 @@
     </row>
     <row r="676" ht="12.75" customHeight="1">
       <c r="A676" s="1"/>
-      <c r="B676" s="1"/>
+      <c r="B676" s="2"/>
       <c r="C676" s="1"/>
       <c r="D676" s="1"/>
       <c r="E676" s="1"/>
@@ -47754,7 +47775,7 @@
     </row>
     <row r="677" ht="12.75" customHeight="1">
       <c r="A677" s="1"/>
-      <c r="B677" s="1"/>
+      <c r="B677" s="2"/>
       <c r="C677" s="1"/>
       <c r="D677" s="1"/>
       <c r="E677" s="1"/>
@@ -47782,7 +47803,7 @@
     </row>
     <row r="678" ht="12.75" customHeight="1">
       <c r="A678" s="1"/>
-      <c r="B678" s="1"/>
+      <c r="B678" s="2"/>
       <c r="C678" s="1"/>
       <c r="D678" s="1"/>
       <c r="E678" s="1"/>
@@ -47810,7 +47831,7 @@
     </row>
     <row r="679" ht="12.75" customHeight="1">
       <c r="A679" s="1"/>
-      <c r="B679" s="1"/>
+      <c r="B679" s="2"/>
       <c r="C679" s="1"/>
       <c r="D679" s="1"/>
       <c r="E679" s="1"/>
@@ -47838,7 +47859,7 @@
     </row>
     <row r="680" ht="12.75" customHeight="1">
       <c r="A680" s="1"/>
-      <c r="B680" s="1"/>
+      <c r="B680" s="2"/>
       <c r="C680" s="1"/>
       <c r="D680" s="1"/>
       <c r="E680" s="1"/>
@@ -47866,7 +47887,7 @@
     </row>
     <row r="681" ht="12.75" customHeight="1">
       <c r="A681" s="1"/>
-      <c r="B681" s="1"/>
+      <c r="B681" s="2"/>
       <c r="C681" s="1"/>
       <c r="D681" s="1"/>
       <c r="E681" s="1"/>
@@ -47894,7 +47915,7 @@
     </row>
     <row r="682" ht="12.75" customHeight="1">
       <c r="A682" s="1"/>
-      <c r="B682" s="1"/>
+      <c r="B682" s="2"/>
       <c r="C682" s="1"/>
       <c r="D682" s="1"/>
       <c r="E682" s="1"/>
@@ -47922,7 +47943,7 @@
     </row>
     <row r="683" ht="12.75" customHeight="1">
       <c r="A683" s="1"/>
-      <c r="B683" s="1"/>
+      <c r="B683" s="2"/>
       <c r="C683" s="1"/>
       <c r="D683" s="1"/>
       <c r="E683" s="1"/>
@@ -47950,7 +47971,7 @@
     </row>
     <row r="684" ht="12.75" customHeight="1">
       <c r="A684" s="1"/>
-      <c r="B684" s="1"/>
+      <c r="B684" s="2"/>
       <c r="C684" s="1"/>
       <c r="D684" s="1"/>
       <c r="E684" s="1"/>
@@ -47978,7 +47999,7 @@
     </row>
     <row r="685" ht="12.75" customHeight="1">
       <c r="A685" s="1"/>
-      <c r="B685" s="1"/>
+      <c r="B685" s="2"/>
       <c r="C685" s="1"/>
       <c r="D685" s="1"/>
       <c r="E685" s="1"/>
@@ -48006,7 +48027,7 @@
     </row>
     <row r="686" ht="12.75" customHeight="1">
       <c r="A686" s="1"/>
-      <c r="B686" s="1"/>
+      <c r="B686" s="2"/>
       <c r="C686" s="1"/>
       <c r="D686" s="1"/>
       <c r="E686" s="1"/>
@@ -48034,7 +48055,7 @@
     </row>
     <row r="687" ht="12.75" customHeight="1">
       <c r="A687" s="1"/>
-      <c r="B687" s="1"/>
+      <c r="B687" s="2"/>
       <c r="C687" s="1"/>
       <c r="D687" s="1"/>
       <c r="E687" s="1"/>
@@ -48062,7 +48083,7 @@
     </row>
     <row r="688" ht="12.75" customHeight="1">
       <c r="A688" s="1"/>
-      <c r="B688" s="1"/>
+      <c r="B688" s="2"/>
       <c r="C688" s="1"/>
       <c r="D688" s="1"/>
       <c r="E688" s="1"/>
@@ -48090,7 +48111,7 @@
     </row>
     <row r="689" ht="12.75" customHeight="1">
       <c r="A689" s="1"/>
-      <c r="B689" s="1"/>
+      <c r="B689" s="2"/>
       <c r="C689" s="1"/>
       <c r="D689" s="1"/>
       <c r="E689" s="1"/>
@@ -48118,7 +48139,7 @@
     </row>
     <row r="690" ht="12.75" customHeight="1">
       <c r="A690" s="1"/>
-      <c r="B690" s="1"/>
+      <c r="B690" s="2"/>
       <c r="C690" s="1"/>
       <c r="D690" s="1"/>
       <c r="E690" s="1"/>
@@ -48146,7 +48167,7 @@
     </row>
     <row r="691" ht="12.75" customHeight="1">
       <c r="A691" s="1"/>
-      <c r="B691" s="1"/>
+      <c r="B691" s="2"/>
       <c r="C691" s="1"/>
       <c r="D691" s="1"/>
       <c r="E691" s="1"/>
@@ -48174,7 +48195,7 @@
     </row>
     <row r="692" ht="12.75" customHeight="1">
       <c r="A692" s="1"/>
-      <c r="B692" s="1"/>
+      <c r="B692" s="2"/>
       <c r="C692" s="1"/>
       <c r="D692" s="1"/>
       <c r="E692" s="1"/>
@@ -48202,7 +48223,7 @@
     </row>
     <row r="693" ht="12.75" customHeight="1">
       <c r="A693" s="1"/>
-      <c r="B693" s="1"/>
+      <c r="B693" s="2"/>
       <c r="C693" s="1"/>
       <c r="D693" s="1"/>
       <c r="E693" s="1"/>
@@ -48230,7 +48251,7 @@
     </row>
     <row r="694" ht="12.75" customHeight="1">
       <c r="A694" s="1"/>
-      <c r="B694" s="1"/>
+      <c r="B694" s="2"/>
       <c r="C694" s="1"/>
       <c r="D694" s="1"/>
       <c r="E694" s="1"/>
@@ -48258,7 +48279,7 @@
     </row>
     <row r="695" ht="12.75" customHeight="1">
       <c r="A695" s="1"/>
-      <c r="B695" s="1"/>
+      <c r="B695" s="2"/>
       <c r="C695" s="1"/>
       <c r="D695" s="1"/>
       <c r="E695" s="1"/>
@@ -48286,7 +48307,7 @@
     </row>
     <row r="696" ht="12.75" customHeight="1">
       <c r="A696" s="1"/>
-      <c r="B696" s="1"/>
+      <c r="B696" s="2"/>
       <c r="C696" s="1"/>
       <c r="D696" s="1"/>
       <c r="E696" s="1"/>
@@ -48314,7 +48335,7 @@
     </row>
     <row r="697" ht="12.75" customHeight="1">
       <c r="A697" s="1"/>
-      <c r="B697" s="1"/>
+      <c r="B697" s="2"/>
       <c r="C697" s="1"/>
       <c r="D697" s="1"/>
       <c r="E697" s="1"/>
@@ -48342,7 +48363,7 @@
     </row>
     <row r="698" ht="12.75" customHeight="1">
       <c r="A698" s="1"/>
-      <c r="B698" s="1"/>
+      <c r="B698" s="2"/>
       <c r="C698" s="1"/>
       <c r="D698" s="1"/>
       <c r="E698" s="1"/>
@@ -48370,7 +48391,7 @@
     </row>
     <row r="699" ht="12.75" customHeight="1">
       <c r="A699" s="1"/>
-      <c r="B699" s="1"/>
+      <c r="B699" s="2"/>
       <c r="C699" s="1"/>
       <c r="D699" s="1"/>
       <c r="E699" s="1"/>
@@ -48398,7 +48419,7 @@
     </row>
     <row r="700" ht="12.75" customHeight="1">
       <c r="A700" s="1"/>
-      <c r="B700" s="1"/>
+      <c r="B700" s="2"/>
       <c r="C700" s="1"/>
       <c r="D700" s="1"/>
       <c r="E700" s="1"/>
@@ -48426,7 +48447,7 @@
     </row>
     <row r="701" ht="12.75" customHeight="1">
       <c r="A701" s="1"/>
-      <c r="B701" s="1"/>
+      <c r="B701" s="2"/>
       <c r="C701" s="1"/>
       <c r="D701" s="1"/>
       <c r="E701" s="1"/>
@@ -48454,7 +48475,7 @@
     </row>
     <row r="702" ht="12.75" customHeight="1">
       <c r="A702" s="1"/>
-      <c r="B702" s="1"/>
+      <c r="B702" s="2"/>
       <c r="C702" s="1"/>
       <c r="D702" s="1"/>
       <c r="E702" s="1"/>
@@ -48482,7 +48503,7 @@
     </row>
     <row r="703" ht="12.75" customHeight="1">
       <c r="A703" s="1"/>
-      <c r="B703" s="1"/>
+      <c r="B703" s="2"/>
       <c r="C703" s="1"/>
       <c r="D703" s="1"/>
       <c r="E703" s="1"/>
@@ -48510,7 +48531,7 @@
     </row>
     <row r="704" ht="12.75" customHeight="1">
       <c r="A704" s="1"/>
-      <c r="B704" s="1"/>
+      <c r="B704" s="2"/>
       <c r="C704" s="1"/>
       <c r="D704" s="1"/>
       <c r="E704" s="1"/>
@@ -48538,7 +48559,7 @@
     </row>
     <row r="705" ht="12.75" customHeight="1">
       <c r="A705" s="1"/>
-      <c r="B705" s="1"/>
+      <c r="B705" s="2"/>
       <c r="C705" s="1"/>
       <c r="D705" s="1"/>
       <c r="E705" s="1"/>
@@ -48566,7 +48587,7 @@
     </row>
     <row r="706" ht="12.75" customHeight="1">
       <c r="A706" s="1"/>
-      <c r="B706" s="1"/>
+      <c r="B706" s="2"/>
       <c r="C706" s="1"/>
       <c r="D706" s="1"/>
       <c r="E706" s="1"/>
@@ -48594,7 +48615,7 @@
     </row>
     <row r="707" ht="12.75" customHeight="1">
       <c r="A707" s="1"/>
-      <c r="B707" s="1"/>
+      <c r="B707" s="2"/>
       <c r="C707" s="1"/>
       <c r="D707" s="1"/>
       <c r="E707" s="1"/>
@@ -48622,7 +48643,7 @@
     </row>
     <row r="708" ht="12.75" customHeight="1">
       <c r="A708" s="1"/>
-      <c r="B708" s="1"/>
+      <c r="B708" s="2"/>
       <c r="C708" s="1"/>
       <c r="D708" s="1"/>
       <c r="E708" s="1"/>
@@ -48650,7 +48671,7 @@
     </row>
     <row r="709" ht="12.75" customHeight="1">
       <c r="A709" s="1"/>
-      <c r="B709" s="1"/>
+      <c r="B709" s="2"/>
       <c r="C709" s="1"/>
       <c r="D709" s="1"/>
       <c r="E709" s="1"/>
@@ -48678,7 +48699,7 @@
     </row>
     <row r="710" ht="12.75" customHeight="1">
       <c r="A710" s="1"/>
-      <c r="B710" s="1"/>
+      <c r="B710" s="2"/>
       <c r="C710" s="1"/>
       <c r="D710" s="1"/>
       <c r="E710" s="1"/>
@@ -48706,7 +48727,7 @@
     </row>
     <row r="711" ht="12.75" customHeight="1">
       <c r="A711" s="1"/>
-      <c r="B711" s="1"/>
+      <c r="B711" s="2"/>
       <c r="C711" s="1"/>
       <c r="D711" s="1"/>
       <c r="E711" s="1"/>
@@ -48734,7 +48755,7 @@
     </row>
     <row r="712" ht="12.75" customHeight="1">
       <c r="A712" s="1"/>
-      <c r="B712" s="1"/>
+      <c r="B712" s="2"/>
       <c r="C712" s="1"/>
       <c r="D712" s="1"/>
       <c r="E712" s="1"/>
@@ -48762,7 +48783,7 @@
     </row>
     <row r="713" ht="12.75" customHeight="1">
       <c r="A713" s="1"/>
-      <c r="B713" s="1"/>
+      <c r="B713" s="2"/>
       <c r="C713" s="1"/>
       <c r="D713" s="1"/>
       <c r="E713" s="1"/>
@@ -48790,7 +48811,7 @@
     </row>
     <row r="714" ht="12.75" customHeight="1">
       <c r="A714" s="1"/>
-      <c r="B714" s="1"/>
+      <c r="B714" s="2"/>
       <c r="C714" s="1"/>
       <c r="D714" s="1"/>
       <c r="E714" s="1"/>
@@ -48818,7 +48839,7 @@
     </row>
     <row r="715" ht="12.75" customHeight="1">
       <c r="A715" s="1"/>
-      <c r="B715" s="1"/>
+      <c r="B715" s="2"/>
       <c r="C715" s="1"/>
       <c r="D715" s="1"/>
       <c r="E715" s="1"/>
@@ -48846,7 +48867,7 @@
     </row>
     <row r="716" ht="12.75" customHeight="1">
       <c r="A716" s="1"/>
-      <c r="B716" s="1"/>
+      <c r="B716" s="2"/>
       <c r="C716" s="1"/>
       <c r="D716" s="1"/>
       <c r="E716" s="1"/>
@@ -48874,7 +48895,7 @@
     </row>
     <row r="717" ht="12.75" customHeight="1">
       <c r="A717" s="1"/>
-      <c r="B717" s="1"/>
+      <c r="B717" s="2"/>
       <c r="C717" s="1"/>
       <c r="D717" s="1"/>
       <c r="E717" s="1"/>
@@ -48902,7 +48923,7 @@
     </row>
     <row r="718" ht="12.75" customHeight="1">
       <c r="A718" s="1"/>
-      <c r="B718" s="1"/>
+      <c r="B718" s="2"/>
       <c r="C718" s="1"/>
       <c r="D718" s="1"/>
       <c r="E718" s="1"/>
@@ -48930,7 +48951,7 @@
     </row>
     <row r="719" ht="12.75" customHeight="1">
       <c r="A719" s="1"/>
-      <c r="B719" s="1"/>
+      <c r="B719" s="2"/>
       <c r="C719" s="1"/>
       <c r="D719" s="1"/>
       <c r="E719" s="1"/>
@@ -48958,7 +48979,7 @@
     </row>
     <row r="720" ht="12.75" customHeight="1">
       <c r="A720" s="1"/>
-      <c r="B720" s="1"/>
+      <c r="B720" s="2"/>
       <c r="C720" s="1"/>
       <c r="D720" s="1"/>
       <c r="E720" s="1"/>
@@ -48986,7 +49007,7 @@
     </row>
     <row r="721" ht="12.75" customHeight="1">
       <c r="A721" s="1"/>
-      <c r="B721" s="1"/>
+      <c r="B721" s="2"/>
       <c r="C721" s="1"/>
       <c r="D721" s="1"/>
       <c r="E721" s="1"/>
@@ -49014,7 +49035,7 @@
     </row>
     <row r="722" ht="12.75" customHeight="1">
       <c r="A722" s="1"/>
-      <c r="B722" s="1"/>
+      <c r="B722" s="2"/>
       <c r="C722" s="1"/>
       <c r="D722" s="1"/>
       <c r="E722" s="1"/>
@@ -49042,7 +49063,7 @@
     </row>
     <row r="723" ht="12.75" customHeight="1">
       <c r="A723" s="1"/>
-      <c r="B723" s="1"/>
+      <c r="B723" s="2"/>
       <c r="C723" s="1"/>
       <c r="D723" s="1"/>
       <c r="E723" s="1"/>
@@ -49070,7 +49091,7 @@
     </row>
     <row r="724" ht="12.75" customHeight="1">
       <c r="A724" s="1"/>
-      <c r="B724" s="1"/>
+      <c r="B724" s="2"/>
       <c r="C724" s="1"/>
       <c r="D724" s="1"/>
       <c r="E724" s="1"/>
@@ -49098,7 +49119,7 @@
     </row>
     <row r="725" ht="12.75" customHeight="1">
       <c r="A725" s="1"/>
-      <c r="B725" s="1"/>
+      <c r="B725" s="2"/>
       <c r="C725" s="1"/>
       <c r="D725" s="1"/>
       <c r="E725" s="1"/>
@@ -49126,7 +49147,7 @@
     </row>
     <row r="726" ht="12.75" customHeight="1">
       <c r="A726" s="1"/>
-      <c r="B726" s="1"/>
+      <c r="B726" s="2"/>
       <c r="C726" s="1"/>
       <c r="D726" s="1"/>
       <c r="E726" s="1"/>
@@ -49154,7 +49175,7 @@
     </row>
     <row r="727" ht="12.75" customHeight="1">
       <c r="A727" s="1"/>
-      <c r="B727" s="1"/>
+      <c r="B727" s="2"/>
       <c r="C727" s="1"/>
       <c r="D727" s="1"/>
       <c r="E727" s="1"/>
@@ -49182,7 +49203,7 @@
     </row>
     <row r="728" ht="12.75" customHeight="1">
       <c r="A728" s="1"/>
-      <c r="B728" s="1"/>
+      <c r="B728" s="2"/>
       <c r="C728" s="1"/>
       <c r="D728" s="1"/>
       <c r="E728" s="1"/>
@@ -49210,7 +49231,7 @@
     </row>
     <row r="729" ht="12.75" customHeight="1">
       <c r="A729" s="1"/>
-      <c r="B729" s="1"/>
+      <c r="B729" s="2"/>
       <c r="C729" s="1"/>
       <c r="D729" s="1"/>
       <c r="E729" s="1"/>
@@ -49238,7 +49259,7 @@
     </row>
     <row r="730" ht="12.75" customHeight="1">
       <c r="A730" s="1"/>
-      <c r="B730" s="1"/>
+      <c r="B730" s="2"/>
       <c r="C730" s="1"/>
       <c r="D730" s="1"/>
       <c r="E730" s="1"/>
@@ -49266,7 +49287,7 @@
     </row>
     <row r="731" ht="12.75" customHeight="1">
       <c r="A731" s="1"/>
-      <c r="B731" s="1"/>
+      <c r="B731" s="2"/>
       <c r="C731" s="1"/>
       <c r="D731" s="1"/>
       <c r="E731" s="1"/>
@@ -49294,7 +49315,7 @@
     </row>
     <row r="732" ht="12.75" customHeight="1">
       <c r="A732" s="1"/>
-      <c r="B732" s="1"/>
+      <c r="B732" s="2"/>
       <c r="C732" s="1"/>
       <c r="D732" s="1"/>
       <c r="E732" s="1"/>
@@ -49322,7 +49343,7 @@
     </row>
     <row r="733" ht="12.75" customHeight="1">
       <c r="A733" s="1"/>
-      <c r="B733" s="1"/>
+      <c r="B733" s="2"/>
       <c r="C733" s="1"/>
       <c r="D733" s="1"/>
       <c r="E733" s="1"/>
@@ -49350,7 +49371,7 @@
     </row>
     <row r="734" ht="12.75" customHeight="1">
       <c r="A734" s="1"/>
-      <c r="B734" s="1"/>
+      <c r="B734" s="2"/>
       <c r="C734" s="1"/>
       <c r="D734" s="1"/>
       <c r="E734" s="1"/>
@@ -49378,7 +49399,7 @@
     </row>
     <row r="735" ht="12.75" customHeight="1">
       <c r="A735" s="1"/>
-      <c r="B735" s="1"/>
+      <c r="B735" s="2"/>
       <c r="C735" s="1"/>
       <c r="D735" s="1"/>
       <c r="E735" s="1"/>
@@ -49406,7 +49427,7 @@
     </row>
     <row r="736" ht="12.75" customHeight="1">
       <c r="A736" s="1"/>
-      <c r="B736" s="1"/>
+      <c r="B736" s="2"/>
       <c r="C736" s="1"/>
       <c r="D736" s="1"/>
       <c r="E736" s="1"/>
@@ -49434,7 +49455,7 @@
     </row>
     <row r="737" ht="12.75" customHeight="1">
       <c r="A737" s="1"/>
-      <c r="B737" s="1"/>
+      <c r="B737" s="2"/>
       <c r="C737" s="1"/>
       <c r="D737" s="1"/>
       <c r="E737" s="1"/>
@@ -49462,7 +49483,7 @@
     </row>
     <row r="738" ht="12.75" customHeight="1">
       <c r="A738" s="1"/>
-      <c r="B738" s="1"/>
+      <c r="B738" s="2"/>
       <c r="C738" s="1"/>
       <c r="D738" s="1"/>
       <c r="E738" s="1"/>
@@ -49490,7 +49511,7 @@
     </row>
     <row r="739" ht="12.75" customHeight="1">
       <c r="A739" s="1"/>
-      <c r="B739" s="1"/>
+      <c r="B739" s="2"/>
       <c r="C739" s="1"/>
       <c r="D739" s="1"/>
       <c r="E739" s="1"/>
@@ -49518,7 +49539,7 @@
     </row>
     <row r="740" ht="12.75" customHeight="1">
       <c r="A740" s="1"/>
-      <c r="B740" s="1"/>
+      <c r="B740" s="2"/>
       <c r="C740" s="1"/>
       <c r="D740" s="1"/>
       <c r="E740" s="1"/>
@@ -49546,7 +49567,7 @@
     </row>
     <row r="741" ht="12.75" customHeight="1">
       <c r="A741" s="1"/>
-      <c r="B741" s="1"/>
+      <c r="B741" s="2"/>
       <c r="C741" s="1"/>
       <c r="D741" s="1"/>
       <c r="E741" s="1"/>
@@ -49574,7 +49595,7 @@
     </row>
     <row r="742" ht="12.75" customHeight="1">
       <c r="A742" s="1"/>
-      <c r="B742" s="1"/>
+      <c r="B742" s="2"/>
       <c r="C742" s="1"/>
       <c r="D742" s="1"/>
       <c r="E742" s="1"/>
@@ -49602,7 +49623,7 @@
     </row>
     <row r="743" ht="12.75" customHeight="1">
       <c r="A743" s="1"/>
-      <c r="B743" s="1"/>
+      <c r="B743" s="2"/>
       <c r="C743" s="1"/>
       <c r="D743" s="1"/>
       <c r="E743" s="1"/>
@@ -49630,7 +49651,7 @@
     </row>
     <row r="744" ht="12.75" customHeight="1">
       <c r="A744" s="1"/>
-      <c r="B744" s="1"/>
+      <c r="B744" s="2"/>
       <c r="C744" s="1"/>
       <c r="D744" s="1"/>
       <c r="E744" s="1"/>
@@ -49658,7 +49679,7 @@
     </row>
     <row r="745" ht="12.75" customHeight="1">
       <c r="A745" s="1"/>
-      <c r="B745" s="1"/>
+      <c r="B745" s="2"/>
       <c r="C745" s="1"/>
       <c r="D745" s="1"/>
       <c r="E745" s="1"/>
@@ -49686,7 +49707,7 @@
     </row>
     <row r="746" ht="12.75" customHeight="1">
       <c r="A746" s="1"/>
-      <c r="B746" s="1"/>
+      <c r="B746" s="2"/>
       <c r="C746" s="1"/>
       <c r="D746" s="1"/>
       <c r="E746" s="1"/>
@@ -49714,7 +49735,7 @@
     </row>
     <row r="747" ht="12.75" customHeight="1">
       <c r="A747" s="1"/>
-      <c r="B747" s="1"/>
+      <c r="B747" s="2"/>
       <c r="C747" s="1"/>
       <c r="D747" s="1"/>
       <c r="E747" s="1"/>
@@ -49742,7 +49763,7 @@
     </row>
     <row r="748" ht="12.75" customHeight="1">
       <c r="A748" s="1"/>
-      <c r="B748" s="1"/>
+      <c r="B748" s="2"/>
       <c r="C748" s="1"/>
       <c r="D748" s="1"/>
       <c r="E748" s="1"/>
@@ -49770,7 +49791,7 @@
     </row>
     <row r="749" ht="12.75" customHeight="1">
       <c r="A749" s="1"/>
-      <c r="B749" s="1"/>
+      <c r="B749" s="2"/>
       <c r="C749" s="1"/>
       <c r="D749" s="1"/>
       <c r="E749" s="1"/>
@@ -49798,7 +49819,7 @@
     </row>
     <row r="750" ht="12.75" customHeight="1">
       <c r="A750" s="1"/>
-      <c r="B750" s="1"/>
+      <c r="B750" s="2"/>
       <c r="C750" s="1"/>
       <c r="D750" s="1"/>
       <c r="E750" s="1"/>
@@ -49826,7 +49847,7 @@
     </row>
     <row r="751" ht="12.75" customHeight="1">
       <c r="A751" s="1"/>
-      <c r="B751" s="1"/>
+      <c r="B751" s="2"/>
       <c r="C751" s="1"/>
       <c r="D751" s="1"/>
       <c r="E751" s="1"/>
@@ -49854,7 +49875,7 @@
     </row>
     <row r="752" ht="12.75" customHeight="1">
       <c r="A752" s="1"/>
-      <c r="B752" s="1"/>
+      <c r="B752" s="2"/>
       <c r="C752" s="1"/>
       <c r="D752" s="1"/>
       <c r="E752" s="1"/>
@@ -49882,7 +49903,7 @@
     </row>
     <row r="753" ht="12.75" customHeight="1">
       <c r="A753" s="1"/>
-      <c r="B753" s="1"/>
+      <c r="B753" s="2"/>
       <c r="C753" s="1"/>
       <c r="D753" s="1"/>
       <c r="E753" s="1"/>
@@ -49910,7 +49931,7 @@
     </row>
     <row r="754" ht="12.75" customHeight="1">
       <c r="A754" s="1"/>
-      <c r="B754" s="1"/>
+      <c r="B754" s="2"/>
       <c r="C754" s="1"/>
       <c r="D754" s="1"/>
       <c r="E754" s="1"/>
@@ -49938,7 +49959,7 @@
     </row>
     <row r="755" ht="12.75" customHeight="1">
       <c r="A755" s="1"/>
-      <c r="B755" s="1"/>
+      <c r="B755" s="2"/>
       <c r="C755" s="1"/>
       <c r="D755" s="1"/>
       <c r="E755" s="1"/>
@@ -49966,7 +49987,7 @@
     </row>
     <row r="756" ht="12.75" customHeight="1">
       <c r="A756" s="1"/>
-      <c r="B756" s="1"/>
+      <c r="B756" s="2"/>
       <c r="C756" s="1"/>
       <c r="D756" s="1"/>
       <c r="E756" s="1"/>
@@ -49994,7 +50015,7 @@
     </row>
     <row r="757" ht="12.75" customHeight="1">
       <c r="A757" s="1"/>
-      <c r="B757" s="1"/>
+      <c r="B757" s="2"/>
       <c r="C757" s="1"/>
       <c r="D757" s="1"/>
       <c r="E757" s="1"/>
@@ -50022,7 +50043,7 @@
     </row>
     <row r="758" ht="12.75" customHeight="1">
       <c r="A758" s="1"/>
-      <c r="B758" s="1"/>
+      <c r="B758" s="2"/>
       <c r="C758" s="1"/>
       <c r="D758" s="1"/>
       <c r="E758" s="1"/>
@@ -50050,7 +50071,7 @@
     </row>
     <row r="759" ht="12.75" customHeight="1">
       <c r="A759" s="1"/>
-      <c r="B759" s="1"/>
+      <c r="B759" s="2"/>
       <c r="C759" s="1"/>
       <c r="D759" s="1"/>
       <c r="E759" s="1"/>
@@ -50078,7 +50099,7 @@
     </row>
     <row r="760" ht="12.75" customHeight="1">
       <c r="A760" s="1"/>
-      <c r="B760" s="1"/>
+      <c r="B760" s="2"/>
       <c r="C760" s="1"/>
       <c r="D760" s="1"/>
       <c r="E760" s="1"/>
@@ -50106,7 +50127,7 @@
     </row>
     <row r="761" ht="12.75" customHeight="1">
       <c r="A761" s="1"/>
-      <c r="B761" s="1"/>
+      <c r="B761" s="2"/>
       <c r="C761" s="1"/>
       <c r="D761" s="1"/>
       <c r="E761" s="1"/>
@@ -50134,7 +50155,7 @@
     </row>
     <row r="762" ht="12.75" customHeight="1">
       <c r="A762" s="1"/>
-      <c r="B762" s="1"/>
+      <c r="B762" s="2"/>
       <c r="C762" s="1"/>
       <c r="D762" s="1"/>
       <c r="E762" s="1"/>
@@ -50162,7 +50183,7 @@
     </row>
     <row r="763" ht="12.75" customHeight="1">
       <c r="A763" s="1"/>
-      <c r="B763" s="1"/>
+      <c r="B763" s="2"/>
       <c r="C763" s="1"/>
       <c r="D763" s="1"/>
       <c r="E763" s="1"/>
@@ -50190,7 +50211,7 @@
     </row>
     <row r="764" ht="12.75" customHeight="1">
       <c r="A764" s="1"/>
-      <c r="B764" s="1"/>
+      <c r="B764" s="2"/>
       <c r="C764" s="1"/>
       <c r="D764" s="1"/>
       <c r="E764" s="1"/>
@@ -50218,7 +50239,7 @@
     </row>
     <row r="765" ht="12.75" customHeight="1">
       <c r="A765" s="1"/>
-      <c r="B765" s="1"/>
+      <c r="B765" s="2"/>
       <c r="C765" s="1"/>
       <c r="D765" s="1"/>
       <c r="E765" s="1"/>
@@ -50246,7 +50267,7 @@
     </row>
     <row r="766" ht="12.75" customHeight="1">
       <c r="A766" s="1"/>
-      <c r="B766" s="1"/>
+      <c r="B766" s="2"/>
       <c r="C766" s="1"/>
       <c r="D766" s="1"/>
       <c r="E766" s="1"/>
@@ -50274,7 +50295,7 @@
     </row>
     <row r="767" ht="12.75" customHeight="1">
       <c r="A767" s="1"/>
-      <c r="B767" s="1"/>
+      <c r="B767" s="2"/>
       <c r="C767" s="1"/>
       <c r="D767" s="1"/>
       <c r="E767" s="1"/>
@@ -50302,7 +50323,7 @@
     </row>
     <row r="768" ht="12.75" customHeight="1">
       <c r="A768" s="1"/>
-      <c r="B768" s="1"/>
+      <c r="B768" s="2"/>
       <c r="C768" s="1"/>
       <c r="D768" s="1"/>
       <c r="E768" s="1"/>
@@ -50330,7 +50351,7 @@
     </row>
     <row r="769" ht="12.75" customHeight="1">
       <c r="A769" s="1"/>
-      <c r="B769" s="1"/>
+      <c r="B769" s="2"/>
       <c r="C769" s="1"/>
       <c r="D769" s="1"/>
       <c r="E769" s="1"/>
@@ -50358,7 +50379,7 @@
     </row>
     <row r="770" ht="12.75" customHeight="1">
       <c r="A770" s="1"/>
-      <c r="B770" s="1"/>
+      <c r="B770" s="2"/>
       <c r="C770" s="1"/>
       <c r="D770" s="1"/>
       <c r="E770" s="1"/>
@@ -50386,7 +50407,7 @@
     </row>
     <row r="771" ht="12.75" customHeight="1">
       <c r="A771" s="1"/>
-      <c r="B771" s="1"/>
+      <c r="B771" s="2"/>
       <c r="C771" s="1"/>
       <c r="D771" s="1"/>
       <c r="E771" s="1"/>
@@ -50414,7 +50435,7 @@
     </row>
     <row r="772" ht="12.75" customHeight="1">
       <c r="A772" s="1"/>
-      <c r="B772" s="1"/>
+      <c r="B772" s="2"/>
       <c r="C772" s="1"/>
       <c r="D772" s="1"/>
       <c r="E772" s="1"/>
@@ -50442,7 +50463,7 @@
     </row>
     <row r="773" ht="12.75" customHeight="1">
       <c r="A773" s="1"/>
-      <c r="B773" s="1"/>
+      <c r="B773" s="2"/>
       <c r="C773" s="1"/>
       <c r="D773" s="1"/>
       <c r="E773" s="1"/>
@@ -50470,7 +50491,7 @@
     </row>
     <row r="774" ht="12.75" customHeight="1">
       <c r="A774" s="1"/>
-      <c r="B774" s="1"/>
+      <c r="B774" s="2"/>
       <c r="C774" s="1"/>
       <c r="D774" s="1"/>
       <c r="E774" s="1"/>
@@ -50498,7 +50519,7 @@
     </row>
     <row r="775" ht="12.75" customHeight="1">
       <c r="A775" s="1"/>
-      <c r="B775" s="1"/>
+      <c r="B775" s="2"/>
       <c r="C775" s="1"/>
       <c r="D775" s="1"/>
       <c r="E775" s="1"/>
@@ -50526,7 +50547,7 @@
     </row>
     <row r="776" ht="12.75" customHeight="1">
       <c r="A776" s="1"/>
-      <c r="B776" s="1"/>
+      <c r="B776" s="2"/>
       <c r="C776" s="1"/>
       <c r="D776" s="1"/>
       <c r="E776" s="1"/>
@@ -50554,7 +50575,7 @@
     </row>
     <row r="777" ht="12.75" customHeight="1">
       <c r="A777" s="1"/>
-      <c r="B777" s="1"/>
+      <c r="B777" s="2"/>
       <c r="C777" s="1"/>
       <c r="D777" s="1"/>
       <c r="E777" s="1"/>
@@ -50582,7 +50603,7 @@
     </row>
     <row r="778" ht="12.75" customHeight="1">
       <c r="A778" s="1"/>
-      <c r="B778" s="1"/>
+      <c r="B778" s="2"/>
       <c r="C778" s="1"/>
       <c r="D778" s="1"/>
       <c r="E778" s="1"/>
@@ -50610,7 +50631,7 @@
     </row>
     <row r="779" ht="12.75" customHeight="1">
       <c r="A779" s="1"/>
-      <c r="B779" s="1"/>
+      <c r="B779" s="2"/>
       <c r="C779" s="1"/>
       <c r="D779" s="1"/>
       <c r="E779" s="1"/>
@@ -50638,7 +50659,7 @@
     </row>
     <row r="780" ht="12.75" customHeight="1">
       <c r="A780" s="1"/>
-      <c r="B780" s="1"/>
+      <c r="B780" s="2"/>
       <c r="C780" s="1"/>
       <c r="D780" s="1"/>
       <c r="E780" s="1"/>
@@ -50666,7 +50687,7 @@
     </row>
     <row r="781" ht="12.75" customHeight="1">
       <c r="A781" s="1"/>
-      <c r="B781" s="1"/>
+      <c r="B781" s="2"/>
       <c r="C781" s="1"/>
       <c r="D781" s="1"/>
       <c r="E781" s="1"/>
@@ -50694,7 +50715,7 @@
     </row>
     <row r="782" ht="12.75" customHeight="1">
       <c r="A782" s="1"/>
-      <c r="B782" s="1"/>
+      <c r="B782" s="2"/>
       <c r="C782" s="1"/>
       <c r="D782" s="1"/>
       <c r="E782" s="1"/>
@@ -50722,7 +50743,7 @@
     </row>
     <row r="783" ht="12.75" customHeight="1">
       <c r="A783" s="1"/>
-      <c r="B783" s="1"/>
+      <c r="B783" s="2"/>
       <c r="C783" s="1"/>
       <c r="D783" s="1"/>
       <c r="E783" s="1"/>
@@ -50750,7 +50771,7 @@
     </row>
     <row r="784" ht="12.75" customHeight="1">
       <c r="A784" s="1"/>
-      <c r="B784" s="1"/>
+      <c r="B784" s="2"/>
       <c r="C784" s="1"/>
       <c r="D784" s="1"/>
       <c r="E784" s="1"/>
@@ -50778,7 +50799,7 @@
     </row>
     <row r="785" ht="12.75" customHeight="1">
       <c r="A785" s="1"/>
-      <c r="B785" s="1"/>
+      <c r="B785" s="2"/>
       <c r="C785" s="1"/>
       <c r="D785" s="1"/>
       <c r="E785" s="1"/>
@@ -50806,7 +50827,7 @@
     </row>
     <row r="786" ht="12.75" customHeight="1">
       <c r="A786" s="1"/>
-      <c r="B786" s="1"/>
+      <c r="B786" s="2"/>
       <c r="C786" s="1"/>
       <c r="D786" s="1"/>
       <c r="E786" s="1"/>
@@ -50834,7 +50855,7 @@
     </row>
     <row r="787" ht="12.75" customHeight="1">
       <c r="A787" s="1"/>
-      <c r="B787" s="1"/>
+      <c r="B787" s="2"/>
       <c r="C787" s="1"/>
       <c r="D787" s="1"/>
       <c r="E787" s="1"/>
@@ -50862,7 +50883,7 @@
     </row>
     <row r="788" ht="12.75" customHeight="1">
       <c r="A788" s="1"/>
-      <c r="B788" s="1"/>
+      <c r="B788" s="2"/>
       <c r="C788" s="1"/>
       <c r="D788" s="1"/>
       <c r="E788" s="1"/>
@@ -50890,7 +50911,7 @@
     </row>
     <row r="789" ht="12.75" customHeight="1">
       <c r="A789" s="1"/>
-      <c r="B789" s="1"/>
+      <c r="B789" s="2"/>
       <c r="C789" s="1"/>
       <c r="D789" s="1"/>
       <c r="E789" s="1"/>
@@ -50918,7 +50939,7 @@
     </row>
     <row r="790" ht="12.75" customHeight="1">
       <c r="A790" s="1"/>
-      <c r="B790" s="1"/>
+      <c r="B790" s="2"/>
       <c r="C790" s="1"/>
       <c r="D790" s="1"/>
       <c r="E790" s="1"/>
@@ -50946,7 +50967,7 @@
     </row>
     <row r="791" ht="12.75" customHeight="1">
       <c r="A791" s="1"/>
-      <c r="B791" s="1"/>
+      <c r="B791" s="2"/>
       <c r="C791" s="1"/>
       <c r="D791" s="1"/>
       <c r="E791" s="1"/>
@@ -50974,7 +50995,7 @@
     </row>
     <row r="792" ht="12.75" customHeight="1">
       <c r="A792" s="1"/>
-      <c r="B792" s="1"/>
+      <c r="B792" s="2"/>
       <c r="C792" s="1"/>
       <c r="D792" s="1"/>
       <c r="E792" s="1"/>
@@ -51002,7 +51023,7 @@
     </row>
     <row r="793" ht="12.75" customHeight="1">
       <c r="A793" s="1"/>
-      <c r="B793" s="1"/>
+      <c r="B793" s="2"/>
       <c r="C793" s="1"/>
       <c r="D793" s="1"/>
       <c r="E793" s="1"/>
@@ -51030,7 +51051,7 @@
     </row>
     <row r="794" ht="12.75" customHeight="1">
       <c r="A794" s="1"/>
-      <c r="B794" s="1"/>
+      <c r="B794" s="2"/>
       <c r="C794" s="1"/>
       <c r="D794" s="1"/>
       <c r="E794" s="1"/>
@@ -51058,7 +51079,7 @@
     </row>
     <row r="795" ht="12.75" customHeight="1">
       <c r="A795" s="1"/>
-      <c r="B795" s="1"/>
+      <c r="B795" s="2"/>
       <c r="C795" s="1"/>
       <c r="D795" s="1"/>
       <c r="E795" s="1"/>
@@ -51086,7 +51107,7 @@
     </row>
     <row r="796" ht="12.75" customHeight="1">
       <c r="A796" s="1"/>
-      <c r="B796" s="1"/>
+      <c r="B796" s="2"/>
       <c r="C796" s="1"/>
       <c r="D796" s="1"/>
       <c r="E796" s="1"/>
@@ -51114,7 +51135,7 @@
     </row>
     <row r="797" ht="12.75" customHeight="1">
       <c r="A797" s="1"/>
-      <c r="B797" s="1"/>
+      <c r="B797" s="2"/>
       <c r="C797" s="1"/>
       <c r="D797" s="1"/>
       <c r="E797" s="1"/>
@@ -51142,7 +51163,7 @@
     </row>
     <row r="798" ht="12.75" customHeight="1">
       <c r="A798" s="1"/>
-      <c r="B798" s="1"/>
+      <c r="B798" s="2"/>
       <c r="C798" s="1"/>
       <c r="D798" s="1"/>
       <c r="E798" s="1"/>
@@ -51170,7 +51191,7 @@
     </row>
     <row r="799" ht="12.75" customHeight="1">
       <c r="A799" s="1"/>
-      <c r="B799" s="1"/>
+      <c r="B799" s="2"/>
       <c r="C799" s="1"/>
       <c r="D799" s="1"/>
       <c r="E799" s="1"/>
@@ -51198,7 +51219,7 @@
     </row>
     <row r="800" ht="12.75" customHeight="1">
       <c r="A800" s="1"/>
-      <c r="B800" s="1"/>
+      <c r="B800" s="2"/>
       <c r="C800" s="1"/>
       <c r="D800" s="1"/>
       <c r="E800" s="1"/>
@@ -51226,7 +51247,7 @@
     </row>
     <row r="801" ht="12.75" customHeight="1">
       <c r="A801" s="1"/>
-      <c r="B801" s="1"/>
+      <c r="B801" s="2"/>
       <c r="C801" s="1"/>
       <c r="D801" s="1"/>
       <c r="E801" s="1"/>
@@ -51254,7 +51275,7 @@
     </row>
     <row r="802" ht="12.75" customHeight="1">
       <c r="A802" s="1"/>
-      <c r="B802" s="1"/>
+      <c r="B802" s="2"/>
       <c r="C802" s="1"/>
       <c r="D802" s="1"/>
       <c r="E802" s="1"/>
@@ -51282,7 +51303,7 @@
     </row>
     <row r="803" ht="12.75" customHeight="1">
       <c r="A803" s="1"/>
-      <c r="B803" s="1"/>
+      <c r="B803" s="2"/>
       <c r="C803" s="1"/>
       <c r="D803" s="1"/>
       <c r="E803" s="1"/>
@@ -51310,7 +51331,7 @@
     </row>
     <row r="804" ht="12.75" customHeight="1">
       <c r="A804" s="1"/>
-      <c r="B804" s="1"/>
+      <c r="B804" s="2"/>
       <c r="C804" s="1"/>
       <c r="D804" s="1"/>
       <c r="E804" s="1"/>
@@ -51338,7 +51359,7 @@
     </row>
     <row r="805" ht="12.75" customHeight="1">
       <c r="A805" s="1"/>
-      <c r="B805" s="1"/>
+      <c r="B805" s="2"/>
       <c r="C805" s="1"/>
       <c r="D805" s="1"/>
       <c r="E805" s="1"/>
@@ -51366,7 +51387,7 @@
     </row>
     <row r="806" ht="12.75" customHeight="1">
       <c r="A806" s="1"/>
-      <c r="B806" s="1"/>
+      <c r="B806" s="2"/>
       <c r="C806" s="1"/>
       <c r="D806" s="1"/>
       <c r="E806" s="1"/>
@@ -51394,7 +51415,7 @@
     </row>
     <row r="807" ht="12.75" customHeight="1">
       <c r="A807" s="1"/>
-      <c r="B807" s="1"/>
+      <c r="B807" s="2"/>
       <c r="C807" s="1"/>
       <c r="D807" s="1"/>
       <c r="E807" s="1"/>
@@ -51422,7 +51443,7 @@
     </row>
     <row r="808" ht="12.75" customHeight="1">
       <c r="A808" s="1"/>
-      <c r="B808" s="1"/>
+      <c r="B808" s="2"/>
       <c r="C808" s="1"/>
       <c r="D808" s="1"/>
       <c r="E808" s="1"/>
@@ -51450,7 +51471,7 @@
     </row>
     <row r="809" ht="12.75" customHeight="1">
       <c r="A809" s="1"/>
-      <c r="B809" s="1"/>
+      <c r="B809" s="2"/>
       <c r="C809" s="1"/>
       <c r="D809" s="1"/>
       <c r="E809" s="1"/>
@@ -51478,7 +51499,7 @@
     </row>
     <row r="810" ht="12.75" customHeight="1">
       <c r="A810" s="1"/>
-      <c r="B810" s="1"/>
+      <c r="B810" s="2"/>
       <c r="C810" s="1"/>
       <c r="D810" s="1"/>
       <c r="E810" s="1"/>
@@ -51506,7 +51527,7 @@
     </row>
     <row r="811" ht="12.75" customHeight="1">
       <c r="A811" s="1"/>
-      <c r="B811" s="1"/>
+      <c r="B811" s="2"/>
       <c r="C811" s="1"/>
       <c r="D811" s="1"/>
       <c r="E811" s="1"/>
@@ -51534,7 +51555,7 @@
     </row>
     <row r="812" ht="12.75" customHeight="1">
       <c r="A812" s="1"/>
-      <c r="B812" s="1"/>
+      <c r="B812" s="2"/>
       <c r="C812" s="1"/>
       <c r="D812" s="1"/>
       <c r="E812" s="1"/>
@@ -51562,7 +51583,7 @@
     </row>
     <row r="813" ht="12.75" customHeight="1">
       <c r="A813" s="1"/>
-      <c r="B813" s="1"/>
+      <c r="B813" s="2"/>
       <c r="C813" s="1"/>
       <c r="D813" s="1"/>
       <c r="E813" s="1"/>
@@ -51590,7 +51611,7 @@
     </row>
     <row r="814" ht="12.75" customHeight="1">
       <c r="A814" s="1"/>
-      <c r="B814" s="1"/>
+      <c r="B814" s="2"/>
       <c r="C814" s="1"/>
       <c r="D814" s="1"/>
       <c r="E814" s="1"/>
@@ -51618,7 +51639,7 @@
     </row>
     <row r="815" ht="12.75" customHeight="1">
       <c r="A815" s="1"/>
-      <c r="B815" s="1"/>
+      <c r="B815" s="2"/>
       <c r="C815" s="1"/>
       <c r="D815" s="1"/>
       <c r="E815" s="1"/>
@@ -51646,7 +51667,7 @@
     </row>
     <row r="816" ht="12.75" customHeight="1">
       <c r="A816" s="1"/>
-      <c r="B816" s="1"/>
+      <c r="B816" s="2"/>
       <c r="C816" s="1"/>
       <c r="D816" s="1"/>
       <c r="E816" s="1"/>
@@ -51674,7 +51695,7 @@
     </row>
     <row r="817" ht="12.75" customHeight="1">
       <c r="A817" s="1"/>
-      <c r="B817" s="1"/>
+      <c r="B817" s="2"/>
       <c r="C817" s="1"/>
       <c r="D817" s="1"/>
       <c r="E817" s="1"/>
@@ -51702,7 +51723,7 @@
     </row>
     <row r="818" ht="12.75" customHeight="1">
       <c r="A818" s="1"/>
-      <c r="B818" s="1"/>
+      <c r="B818" s="2"/>
       <c r="C818" s="1"/>
       <c r="D818" s="1"/>
       <c r="E818" s="1"/>
@@ -51730,7 +51751,7 @@
     </row>
     <row r="819" ht="12.75" customHeight="1">
       <c r="A819" s="1"/>
-      <c r="B819" s="1"/>
+      <c r="B819" s="2"/>
       <c r="C819" s="1"/>
       <c r="D819" s="1"/>
       <c r="E819" s="1"/>
@@ -51758,7 +51779,7 @@
     </row>
     <row r="820" ht="12.75" customHeight="1">
       <c r="A820" s="1"/>
-      <c r="B820" s="1"/>
+      <c r="B820" s="2"/>
       <c r="C820" s="1"/>
       <c r="D820" s="1"/>
       <c r="E820" s="1"/>
@@ -51786,7 +51807,7 @@
     </row>
     <row r="821" ht="12.75" customHeight="1">
       <c r="A821" s="1"/>
-      <c r="B821" s="1"/>
+      <c r="B821" s="2"/>
       <c r="C821" s="1"/>
       <c r="D821" s="1"/>
       <c r="E821" s="1"/>
@@ -51814,7 +51835,7 @@
     </row>
     <row r="822" ht="12.75" customHeight="1">
       <c r="A822" s="1"/>
-      <c r="B822" s="1"/>
+      <c r="B822" s="2"/>
       <c r="C822" s="1"/>
       <c r="D822" s="1"/>
       <c r="E822" s="1"/>
@@ -51842,7 +51863,7 @@
     </row>
     <row r="823" ht="12.75" customHeight="1">
       <c r="A823" s="1"/>
-      <c r="B823" s="1"/>
+      <c r="B823" s="2"/>
       <c r="C823" s="1"/>
       <c r="D823" s="1"/>
       <c r="E823" s="1"/>
@@ -51870,7 +51891,7 @@
     </row>
     <row r="824" ht="12.75" customHeight="1">
       <c r="A824" s="1"/>
-      <c r="B824" s="1"/>
+      <c r="B824" s="2"/>
       <c r="C824" s="1"/>
       <c r="D824" s="1"/>
       <c r="E824" s="1"/>
@@ -51898,7 +51919,7 @@
     </row>
     <row r="825" ht="12.75" customHeight="1">
       <c r="A825" s="1"/>
-      <c r="B825" s="1"/>
+      <c r="B825" s="2"/>
       <c r="C825" s="1"/>
       <c r="D825" s="1"/>
       <c r="E825" s="1"/>
@@ -51926,7 +51947,7 @@
     </row>
     <row r="826" ht="12.75" customHeight="1">
       <c r="A826" s="1"/>
-      <c r="B826" s="1"/>
+      <c r="B826" s="2"/>
       <c r="C826" s="1"/>
       <c r="D826" s="1"/>
       <c r="E826" s="1"/>
@@ -51954,7 +51975,7 @@
     </row>
     <row r="827" ht="12.75" customHeight="1">
       <c r="A827" s="1"/>
-      <c r="B827" s="1"/>
+      <c r="B827" s="2"/>
       <c r="C827" s="1"/>
       <c r="D827" s="1"/>
       <c r="E827" s="1"/>
@@ -51982,7 +52003,7 @@
     </row>
     <row r="828" ht="12.75" customHeight="1">
       <c r="A828" s="1"/>
-      <c r="B828" s="1"/>
+      <c r="B828" s="2"/>
       <c r="C828" s="1"/>
       <c r="D828" s="1"/>
       <c r="E828" s="1"/>
@@ -52010,7 +52031,7 @@
     </row>
     <row r="829" ht="12.75" customHeight="1">
       <c r="A829" s="1"/>
-      <c r="B829" s="1"/>
+      <c r="B829" s="2"/>
       <c r="C829" s="1"/>
       <c r="D829" s="1"/>
       <c r="E829" s="1"/>
@@ -52038,7 +52059,7 @@
     </row>
     <row r="830" ht="12.75" customHeight="1">
       <c r="A830" s="1"/>
-      <c r="B830" s="1"/>
+      <c r="B830" s="2"/>
       <c r="C830" s="1"/>
       <c r="D830" s="1"/>
       <c r="E830" s="1"/>
@@ -52066,7 +52087,7 @@
     </row>
     <row r="831" ht="12.75" customHeight="1">
       <c r="A831" s="1"/>
-      <c r="B831" s="1"/>
+      <c r="B831" s="2"/>
       <c r="C831" s="1"/>
       <c r="D831" s="1"/>
       <c r="E831" s="1"/>
@@ -52094,7 +52115,7 @@
     </row>
     <row r="832" ht="12.75" customHeight="1">
       <c r="A832" s="1"/>
-      <c r="B832" s="1"/>
+      <c r="B832" s="2"/>
       <c r="C832" s="1"/>
       <c r="D832" s="1"/>
       <c r="E832" s="1"/>
@@ -52122,7 +52143,7 @@
     </row>
     <row r="833" ht="12.75" customHeight="1">
       <c r="A833" s="1"/>
-      <c r="B833" s="1"/>
+      <c r="B833" s="2"/>
       <c r="C833" s="1"/>
       <c r="D833" s="1"/>
       <c r="E833" s="1"/>
@@ -52150,7 +52171,7 @@
     </row>
     <row r="834" ht="12.75" customHeight="1">
       <c r="A834" s="1"/>
-      <c r="B834" s="1"/>
+      <c r="B834" s="2"/>
       <c r="C834" s="1"/>
       <c r="D834" s="1"/>
       <c r="E834" s="1"/>
@@ -52178,7 +52199,7 @@
     </row>
     <row r="835" ht="12.75" customHeight="1">
       <c r="A835" s="1"/>
-      <c r="B835" s="1"/>
+      <c r="B835" s="2"/>
       <c r="C835" s="1"/>
       <c r="D835" s="1"/>
       <c r="E835" s="1"/>
@@ -52206,7 +52227,7 @@
     </row>
     <row r="836" ht="12.75" customHeight="1">
       <c r="A836" s="1"/>
-      <c r="B836" s="1"/>
+      <c r="B836" s="2"/>
       <c r="C836" s="1"/>
       <c r="D836" s="1"/>
       <c r="E836" s="1"/>
@@ -52234,7 +52255,7 @@
     </row>
     <row r="837" ht="12.75" customHeight="1">
       <c r="A837" s="1"/>
-      <c r="B837" s="1"/>
+      <c r="B837" s="2"/>
       <c r="C837" s="1"/>
       <c r="D837" s="1"/>
       <c r="E837" s="1"/>
@@ -52262,7 +52283,7 @@
     </row>
     <row r="838" ht="12.75" customHeight="1">
       <c r="A838" s="1"/>
-      <c r="B838" s="1"/>
+      <c r="B838" s="2"/>
       <c r="C838" s="1"/>
       <c r="D838" s="1"/>
       <c r="E838" s="1"/>
@@ -52290,7 +52311,7 @@
     </row>
     <row r="839" ht="12.75" customHeight="1">
       <c r="A839" s="1"/>
-      <c r="B839" s="1"/>
+      <c r="B839" s="2"/>
       <c r="C839" s="1"/>
       <c r="D839" s="1"/>
       <c r="E839" s="1"/>
@@ -52318,7 +52339,7 @@
     </row>
     <row r="840" ht="12.75" customHeight="1">
       <c r="A840" s="1"/>
-      <c r="B840" s="1"/>
+      <c r="B840" s="2"/>
       <c r="C840" s="1"/>
       <c r="D840" s="1"/>
       <c r="E840" s="1"/>
@@ -52346,7 +52367,7 @@
     </row>
     <row r="841" ht="12.75" customHeight="1">
       <c r="A841" s="1"/>
-      <c r="B841" s="1"/>
+      <c r="B841" s="2"/>
       <c r="C841" s="1"/>
       <c r="D841" s="1"/>
       <c r="E841" s="1"/>
@@ -52374,7 +52395,7 @@
     </row>
     <row r="842" ht="12.75" customHeight="1">
       <c r="A842" s="1"/>
-      <c r="B842" s="1"/>
+      <c r="B842" s="2"/>
       <c r="C842" s="1"/>
       <c r="D842" s="1"/>
       <c r="E842" s="1"/>
@@ -52402,7 +52423,7 @@
     </row>
     <row r="843" ht="12.75" customHeight="1">
       <c r="A843" s="1"/>
-      <c r="B843" s="1"/>
+      <c r="B843" s="2"/>
       <c r="C843" s="1"/>
       <c r="D843" s="1"/>
       <c r="E843" s="1"/>
@@ -52430,7 +52451,7 @@
     </row>
     <row r="844" ht="12.75" customHeight="1">
       <c r="A844" s="1"/>
-      <c r="B844" s="1"/>
+      <c r="B844" s="2"/>
       <c r="C844" s="1"/>
       <c r="D844" s="1"/>
       <c r="E844" s="1"/>
@@ -52458,7 +52479,7 @@
     </row>
     <row r="845" ht="12.75" customHeight="1">
       <c r="A845" s="1"/>
-      <c r="B845" s="1"/>
+      <c r="B845" s="2"/>
       <c r="C845" s="1"/>
       <c r="D845" s="1"/>
       <c r="E845" s="1"/>
@@ -52486,7 +52507,7 @@
     </row>
     <row r="846" ht="12.75" customHeight="1">
       <c r="A846" s="1"/>
-      <c r="B846" s="1"/>
+      <c r="B846" s="2"/>
       <c r="C846" s="1"/>
       <c r="D846" s="1"/>
       <c r="E846" s="1"/>
@@ -52514,7 +52535,7 @@
     </row>
     <row r="847" ht="12.75" customHeight="1">
       <c r="A847" s="1"/>
-      <c r="B847" s="1"/>
+      <c r="B847" s="2"/>
       <c r="C847" s="1"/>
       <c r="D847" s="1"/>
       <c r="E847" s="1"/>
@@ -52542,7 +52563,7 @@
     </row>
     <row r="848" ht="12.75" customHeight="1">
       <c r="A848" s="1"/>
-      <c r="B848" s="1"/>
+      <c r="B848" s="2"/>
       <c r="C848" s="1"/>
       <c r="D848" s="1"/>
       <c r="E848" s="1"/>
@@ -52570,7 +52591,7 @@
     </row>
     <row r="849" ht="12.75" customHeight="1">
       <c r="A849" s="1"/>
-      <c r="B849" s="1"/>
+      <c r="B849" s="2"/>
       <c r="C849" s="1"/>
       <c r="D849" s="1"/>
       <c r="E849" s="1"/>
@@ -52598,7 +52619,7 @@
     </row>
     <row r="850" ht="12.75" customHeight="1">
       <c r="A850" s="1"/>
-      <c r="B850" s="1"/>
+      <c r="B850" s="2"/>
       <c r="C850" s="1"/>
       <c r="D850" s="1"/>
       <c r="E850" s="1"/>
@@ -52626,7 +52647,7 @@
     </row>
     <row r="851" ht="12.75" customHeight="1">
       <c r="A851" s="1"/>
-      <c r="B851" s="1"/>
+      <c r="B851" s="2"/>
       <c r="C851" s="1"/>
       <c r="D851" s="1"/>
       <c r="E851" s="1"/>
@@ -52654,7 +52675,7 @@
     </row>
     <row r="852" ht="12.75" customHeight="1">
       <c r="A852" s="1"/>
-      <c r="B852" s="1"/>
+      <c r="B852" s="2"/>
       <c r="C852" s="1"/>
       <c r="D852" s="1"/>
       <c r="E852" s="1"/>
@@ -52682,7 +52703,7 @@
     </row>
     <row r="853" ht="12.75" customHeight="1">
       <c r="A853" s="1"/>
-      <c r="B853" s="1"/>
+      <c r="B853" s="2"/>
       <c r="C853" s="1"/>
       <c r="D853" s="1"/>
       <c r="E853" s="1"/>
@@ -52710,7 +52731,7 @@
     </row>
     <row r="854" ht="12.75" customHeight="1">
       <c r="A854" s="1"/>
-      <c r="B854" s="1"/>
+      <c r="B854" s="2"/>
       <c r="C854" s="1"/>
       <c r="D854" s="1"/>
       <c r="E854" s="1"/>
@@ -52738,7 +52759,7 @@
     </row>
     <row r="855" ht="12.75" customHeight="1">
       <c r="A855" s="1"/>
-      <c r="B855" s="1"/>
+      <c r="B855" s="2"/>
       <c r="C855" s="1"/>
       <c r="D855" s="1"/>
       <c r="E855" s="1"/>
@@ -52766,7 +52787,7 @@
     </row>
     <row r="856" ht="12.75" customHeight="1">
       <c r="A856" s="1"/>
-      <c r="B856" s="1"/>
+      <c r="B856" s="2"/>
       <c r="C856" s="1"/>
       <c r="D856" s="1"/>
       <c r="E856" s="1"/>
@@ -52794,7 +52815,7 @@
     </row>
     <row r="857" ht="12.75" customHeight="1">
       <c r="A857" s="1"/>
-      <c r="B857" s="1"/>
+      <c r="B857" s="2"/>
       <c r="C857" s="1"/>
       <c r="D857" s="1"/>
       <c r="E857" s="1"/>
@@ -52822,7 +52843,7 @@
     </row>
     <row r="858" ht="12.75" customHeight="1">
       <c r="A858" s="1"/>
-      <c r="B858" s="1"/>
+      <c r="B858" s="2"/>
       <c r="C858" s="1"/>
       <c r="D858" s="1"/>
       <c r="E858" s="1"/>
@@ -52850,7 +52871,7 @@
     </row>
     <row r="859" ht="12.75" customHeight="1">
       <c r="A859" s="1"/>
-      <c r="B859" s="1"/>
+      <c r="B859" s="2"/>
       <c r="C859" s="1"/>
       <c r="D859" s="1"/>
       <c r="E859" s="1"/>
@@ -52878,7 +52899,7 @@
     </row>
     <row r="860" ht="12.75" customHeight="1">
       <c r="A860" s="1"/>
-      <c r="B860" s="1"/>
+      <c r="B860" s="2"/>
       <c r="C860" s="1"/>
       <c r="D860" s="1"/>
       <c r="E860" s="1"/>
@@ -52906,7 +52927,7 @@
     </row>
     <row r="861" ht="12.75" customHeight="1">
       <c r="A861" s="1"/>
-      <c r="B861" s="1"/>
+      <c r="B861" s="2"/>
       <c r="C861" s="1"/>
       <c r="D861" s="1"/>
       <c r="E861" s="1"/>
@@ -52934,7 +52955,7 @@
     </row>
     <row r="862" ht="12.75" customHeight="1">
       <c r="A862" s="1"/>
-      <c r="B862" s="1"/>
+      <c r="B862" s="2"/>
       <c r="C862" s="1"/>
       <c r="D862" s="1"/>
       <c r="E862" s="1"/>
@@ -52962,7 +52983,7 @@
     </row>
     <row r="863" ht="12.75" customHeight="1">
       <c r="A863" s="1"/>
-      <c r="B863" s="1"/>
+      <c r="B863" s="2"/>
       <c r="C863" s="1"/>
       <c r="D863" s="1"/>
       <c r="E863" s="1"/>
@@ -52990,7 +53011,7 @@
     </row>
     <row r="864" ht="12.75" customHeight="1">
       <c r="A864" s="1"/>
-      <c r="B864" s="1"/>
+      <c r="B864" s="2"/>
       <c r="C864" s="1"/>
       <c r="D864" s="1"/>
       <c r="E864" s="1"/>
@@ -53018,7 +53039,7 @@
     </row>
     <row r="865" ht="12.75" customHeight="1">
       <c r="A865" s="1"/>
-      <c r="B865" s="1"/>
+      <c r="B865" s="2"/>
       <c r="C865" s="1"/>
       <c r="D865" s="1"/>
       <c r="E865" s="1"/>
@@ -53046,7 +53067,7 @@
     </row>
     <row r="866" ht="12.75" customHeight="1">
       <c r="A866" s="1"/>
-      <c r="B866" s="1"/>
+      <c r="B866" s="2"/>
       <c r="C866" s="1"/>
       <c r="D866" s="1"/>
       <c r="E866" s="1"/>
@@ -53074,7 +53095,7 @@
     </row>
     <row r="867" ht="12.75" customHeight="1">
       <c r="A867" s="1"/>
-      <c r="B867" s="1"/>
+      <c r="B867" s="2"/>
       <c r="C867" s="1"/>
       <c r="D867" s="1"/>
       <c r="E867" s="1"/>
@@ -53102,7 +53123,7 @@
     </row>
     <row r="868" ht="12.75" customHeight="1">
       <c r="A868" s="1"/>
-      <c r="B868" s="1"/>
+      <c r="B868" s="2"/>
       <c r="C868" s="1"/>
       <c r="D868" s="1"/>
       <c r="E868" s="1"/>
@@ -53130,7 +53151,7 @@
     </row>
     <row r="869" ht="12.75" customHeight="1">
       <c r="A869" s="1"/>
-      <c r="B869" s="1"/>
+      <c r="B869" s="2"/>
       <c r="C869" s="1"/>
       <c r="D869" s="1"/>
       <c r="E869" s="1"/>
@@ -53158,7 +53179,7 @@
     </row>
     <row r="870" ht="12.75" customHeight="1">
       <c r="A870" s="1"/>
-      <c r="B870" s="1"/>
+      <c r="B870" s="2"/>
       <c r="C870" s="1"/>
       <c r="D870" s="1"/>
       <c r="E870" s="1"/>
@@ -53186,7 +53207,7 @@
     </row>
     <row r="871" ht="12.75" customHeight="1">
       <c r="A871" s="1"/>
-      <c r="B871" s="1"/>
+      <c r="B871" s="2"/>
       <c r="C871" s="1"/>
       <c r="D871" s="1"/>
       <c r="E871" s="1"/>
@@ -53214,7 +53235,7 @@
     </row>
     <row r="872" ht="12.75" customHeight="1">
       <c r="A872" s="1"/>
-      <c r="B872" s="1"/>
+      <c r="B872" s="2"/>
       <c r="C872" s="1"/>
       <c r="D872" s="1"/>
       <c r="E872" s="1"/>
@@ -53242,7 +53263,7 @@
     </row>
     <row r="873" ht="12.75" customHeight="1">
       <c r="A873" s="1"/>
-      <c r="B873" s="1"/>
+      <c r="B873" s="2"/>
       <c r="C873" s="1"/>
       <c r="D873" s="1"/>
       <c r="E873" s="1"/>
@@ -53270,7 +53291,7 @@
     </row>
     <row r="874" ht="12.75" customHeight="1">
       <c r="A874" s="1"/>
-      <c r="B874" s="1"/>
+      <c r="B874" s="2"/>
       <c r="C874" s="1"/>
       <c r="D874" s="1"/>
       <c r="E874" s="1"/>
@@ -53298,7 +53319,7 @@
     </row>
     <row r="875" ht="12.75" customHeight="1">
       <c r="A875" s="1"/>
-      <c r="B875" s="1"/>
+      <c r="B875" s="2"/>
       <c r="C875" s="1"/>
       <c r="D875" s="1"/>
       <c r="E875" s="1"/>
@@ -53326,7 +53347,7 @@
     </row>
     <row r="876" ht="12.75" customHeight="1">
       <c r="A876" s="1"/>
-      <c r="B876" s="1"/>
+      <c r="B876" s="2"/>
       <c r="C876" s="1"/>
       <c r="D876" s="1"/>
       <c r="E876" s="1"/>
@@ -53354,7 +53375,7 @@
     </row>
     <row r="877" ht="12.75" customHeight="1">
       <c r="A877" s="1"/>
-      <c r="B877" s="1"/>
+      <c r="B877" s="2"/>
       <c r="C877" s="1"/>
       <c r="D877" s="1"/>
       <c r="E877" s="1"/>
@@ -53382,7 +53403,7 @@
     </row>
     <row r="878" ht="12.75" customHeight="1">
       <c r="A878" s="1"/>
-      <c r="B878" s="1"/>
+      <c r="B878" s="2"/>
       <c r="C878" s="1"/>
       <c r="D878" s="1"/>
       <c r="E878" s="1"/>
@@ -53410,7 +53431,7 @@
     </row>
     <row r="879" ht="12.75" customHeight="1">
       <c r="A879" s="1"/>
-      <c r="B879" s="1"/>
+      <c r="B879" s="2"/>
       <c r="C879" s="1"/>
       <c r="D879" s="1"/>
       <c r="E879" s="1"/>
@@ -53438,7 +53459,7 @@
     </row>
     <row r="880" ht="12.75" customHeight="1">
       <c r="A880" s="1"/>
-      <c r="B880" s="1"/>
+      <c r="B880" s="2"/>
       <c r="C880" s="1"/>
       <c r="D880" s="1"/>
       <c r="E880" s="1"/>
@@ -53466,7 +53487,7 @@
     </row>
     <row r="881" ht="12.75" customHeight="1">
       <c r="A881" s="1"/>
-      <c r="B881" s="1"/>
+      <c r="B881" s="2"/>
       <c r="C881" s="1"/>
       <c r="D881" s="1"/>
       <c r="E881" s="1"/>
@@ -53494,7 +53515,7 @@
     </row>
     <row r="882" ht="12.75" customHeight="1">
       <c r="A882" s="1"/>
-      <c r="B882" s="1"/>
+      <c r="B882" s="2"/>
       <c r="C882" s="1"/>
       <c r="D882" s="1"/>
       <c r="E882" s="1"/>
@@ -53522,7 +53543,7 @@
     </row>
     <row r="883" ht="12.75" customHeight="1">
       <c r="A883" s="1"/>
-      <c r="B883" s="1"/>
+      <c r="B883" s="2"/>
       <c r="C883" s="1"/>
       <c r="D883" s="1"/>
       <c r="E883" s="1"/>
@@ -53550,7 +53571,7 @@
     </row>
     <row r="884" ht="12.75" customHeight="1">
       <c r="A884" s="1"/>
-      <c r="B884" s="1"/>
+      <c r="B884" s="2"/>
       <c r="C884" s="1"/>
       <c r="D884" s="1"/>
       <c r="E884" s="1"/>
@@ -53578,7 +53599,7 @@
     </row>
     <row r="885" ht="12.75" customHeight="1">
       <c r="A885" s="1"/>
-      <c r="B885" s="1"/>
+      <c r="B885" s="2"/>
       <c r="C885" s="1"/>
       <c r="D885" s="1"/>
       <c r="E885" s="1"/>
@@ -53606,7 +53627,7 @@
     </row>
     <row r="886" ht="12.75" customHeight="1">
       <c r="A886" s="1"/>
-      <c r="B886" s="1"/>
+      <c r="B886" s="2"/>
       <c r="C886" s="1"/>
       <c r="D886" s="1"/>
       <c r="E886" s="1"/>
@@ -53634,7 +53655,7 @@
     </row>
     <row r="887" ht="12.75" customHeight="1">
       <c r="A887" s="1"/>
-      <c r="B887" s="1"/>
+      <c r="B887" s="2"/>
       <c r="C887" s="1"/>
       <c r="D887" s="1"/>
       <c r="E887" s="1"/>
@@ -53662,7 +53683,7 @@
     </row>
     <row r="888" ht="12.75" customHeight="1">
       <c r="A888" s="1"/>
-      <c r="B888" s="1"/>
+      <c r="B888" s="2"/>
       <c r="C888" s="1"/>
       <c r="D888" s="1"/>
       <c r="E888" s="1"/>
@@ -53690,7 +53711,7 @@
     </row>
     <row r="889" ht="12.75" customHeight="1">
       <c r="A889" s="1"/>
-      <c r="B889" s="1"/>
+      <c r="B889" s="2"/>
       <c r="C889" s="1"/>
       <c r="D889" s="1"/>
       <c r="E889" s="1"/>
@@ -53718,7 +53739,7 @@
     </row>
     <row r="890" ht="12.75" customHeight="1">
       <c r="A890" s="1"/>
-      <c r="B890" s="1"/>
+      <c r="B890" s="2"/>
       <c r="C890" s="1"/>
       <c r="D890" s="1"/>
       <c r="E890" s="1"/>
@@ -53746,7 +53767,7 @@
     </row>
     <row r="891" ht="12.75" customHeight="1">
       <c r="A891" s="1"/>
-      <c r="B891" s="1"/>
+      <c r="B891" s="2"/>
       <c r="C891" s="1"/>
       <c r="D891" s="1"/>
       <c r="E891" s="1"/>
@@ -53774,7 +53795,7 @@
     </row>
     <row r="892" ht="12.75" customHeight="1">
       <c r="A892" s="1"/>
-      <c r="B892" s="1"/>
+      <c r="B892" s="2"/>
       <c r="C892" s="1"/>
       <c r="D892" s="1"/>
       <c r="E892" s="1"/>
@@ -53802,7 +53823,7 @@
     </row>
     <row r="893" ht="12.75" customHeight="1">
       <c r="A893" s="1"/>
-      <c r="B893" s="1"/>
+      <c r="B893" s="2"/>
       <c r="C893" s="1"/>
       <c r="D893" s="1"/>
       <c r="E893" s="1"/>
@@ -53830,7 +53851,7 @@
     </row>
     <row r="894" ht="12.75" customHeight="1">
       <c r="A894" s="1"/>
-      <c r="B894" s="1"/>
+      <c r="B894" s="2"/>
       <c r="C894" s="1"/>
       <c r="D894" s="1"/>
       <c r="E894" s="1"/>
@@ -53858,7 +53879,7 @@
     </row>
     <row r="895" ht="12.75" customHeight="1">
       <c r="A895" s="1"/>
-      <c r="B895" s="1"/>
+      <c r="B895" s="2"/>
       <c r="C895" s="1"/>
       <c r="D895" s="1"/>
       <c r="E895" s="1"/>
@@ -53886,7 +53907,7 @@
     </row>
     <row r="896" ht="12.75" customHeight="1">
       <c r="A896" s="1"/>
-      <c r="B896" s="1"/>
+      <c r="B896" s="2"/>
       <c r="C896" s="1"/>
       <c r="D896" s="1"/>
       <c r="E896" s="1"/>
@@ -53914,7 +53935,7 @@
     </row>
     <row r="897" ht="12.75" customHeight="1">
       <c r="A897" s="1"/>
-      <c r="B897" s="1"/>
+      <c r="B897" s="2"/>
       <c r="C897" s="1"/>
       <c r="D897" s="1"/>
       <c r="E897" s="1"/>
@@ -53942,7 +53963,7 @@
     </row>
     <row r="898" ht="12.75" customHeight="1">
       <c r="A898" s="1"/>
-      <c r="B898" s="1"/>
+      <c r="B898" s="2"/>
       <c r="C898" s="1"/>
       <c r="D898" s="1"/>
       <c r="E898" s="1"/>
@@ -53970,7 +53991,7 @@
     </row>
     <row r="899" ht="12.75" customHeight="1">
       <c r="A899" s="1"/>
-      <c r="B899" s="1"/>
+      <c r="B899" s="2"/>
       <c r="C899" s="1"/>
       <c r="D899" s="1"/>
       <c r="E899" s="1"/>
@@ -53998,7 +54019,7 @@
     </row>
     <row r="900" ht="12.75" customHeight="1">
       <c r="A900" s="1"/>
-      <c r="B900" s="1"/>
+      <c r="B900" s="2"/>
       <c r="C900" s="1"/>
       <c r="D900" s="1"/>
       <c r="E900" s="1"/>
@@ -54026,7 +54047,7 @@
     </row>
     <row r="901" ht="12.75" customHeight="1">
       <c r="A901" s="1"/>
-      <c r="B901" s="1"/>
+      <c r="B901" s="2"/>
       <c r="C901" s="1"/>
       <c r="D901" s="1"/>
       <c r="E901" s="1"/>
@@ -54054,7 +54075,7 @@
     </row>
     <row r="902" ht="12.75" customHeight="1">
       <c r="A902" s="1"/>
-      <c r="B902" s="1"/>
+      <c r="B902" s="2"/>
       <c r="C902" s="1"/>
       <c r="D902" s="1"/>
       <c r="E902" s="1"/>
@@ -54082,7 +54103,7 @@
     </row>
     <row r="903" ht="12.75" customHeight="1">
       <c r="A903" s="1"/>
-      <c r="B903" s="1"/>
+      <c r="B903" s="2"/>
       <c r="C903" s="1"/>
       <c r="D903" s="1"/>
       <c r="E903" s="1"/>
@@ -54110,7 +54131,7 @@
     </row>
     <row r="904" ht="12.75" customHeight="1">
       <c r="A904" s="1"/>
-      <c r="B904" s="1"/>
+      <c r="B904" s="2"/>
       <c r="C904" s="1"/>
       <c r="D904" s="1"/>
       <c r="E904" s="1"/>
@@ -54138,7 +54159,7 @@
     </row>
     <row r="905" ht="12.75" customHeight="1">
       <c r="A905" s="1"/>
-      <c r="B905" s="1"/>
+      <c r="B905" s="2"/>
       <c r="C905" s="1"/>
       <c r="D905" s="1"/>
       <c r="E905" s="1"/>
@@ -54166,7 +54187,7 @@
     </row>
     <row r="906" ht="12.75" customHeight="1">
       <c r="A906" s="1"/>
-      <c r="B906" s="1"/>
+      <c r="B906" s="2"/>
       <c r="C906" s="1"/>
       <c r="D906" s="1"/>
       <c r="E906" s="1"/>
@@ -54194,7 +54215,7 @@
     </row>
     <row r="907" ht="12.75" customHeight="1">
       <c r="A907" s="1"/>
-      <c r="B907" s="1"/>
+      <c r="B907" s="2"/>
       <c r="C907" s="1"/>
       <c r="D907" s="1"/>
       <c r="E907" s="1"/>
@@ -54222,7 +54243,7 @@
     </row>
     <row r="908" ht="12.75" customHeight="1">
       <c r="A908" s="1"/>
-      <c r="B908" s="1"/>
+      <c r="B908" s="2"/>
       <c r="C908" s="1"/>
       <c r="D908" s="1"/>
       <c r="E908" s="1"/>
@@ -54250,7 +54271,7 @@
     </row>
     <row r="909" ht="12.75" customHeight="1">
       <c r="A909" s="1"/>
-      <c r="B909" s="1"/>
+      <c r="B909" s="2"/>
       <c r="C909" s="1"/>
       <c r="D909" s="1"/>
       <c r="E909" s="1"/>
@@ -54278,7 +54299,7 @@
     </row>
     <row r="910" ht="12.75" customHeight="1">
       <c r="A910" s="1"/>
-      <c r="B910" s="1"/>
+      <c r="B910" s="2"/>
       <c r="C910" s="1"/>
       <c r="D910" s="1"/>
       <c r="E910" s="1"/>
@@ -54306,7 +54327,7 @@
     </row>
     <row r="911" ht="12.75" customHeight="1">
       <c r="A911" s="1"/>
-      <c r="B911" s="1"/>
+      <c r="B911" s="2"/>
       <c r="C911" s="1"/>
       <c r="D911" s="1"/>
       <c r="E911" s="1"/>
@@ -54334,7 +54355,7 @@
     </row>
     <row r="912" ht="12.75" customHeight="1">
       <c r="A912" s="1"/>
-      <c r="B912" s="1"/>
+      <c r="B912" s="2"/>
       <c r="C912" s="1"/>
       <c r="D912" s="1"/>
       <c r="E912" s="1"/>
@@ -54362,7 +54383,7 @@
     </row>
     <row r="913" ht="12.75" customHeight="1">
       <c r="A913" s="1"/>
-      <c r="B913" s="1"/>
+      <c r="B913" s="2"/>
       <c r="C913" s="1"/>
       <c r="D913" s="1"/>
       <c r="E913" s="1"/>
@@ -54390,7 +54411,7 @@
     </row>
     <row r="914" ht="12.75" customHeight="1">
       <c r="A914" s="1"/>
-      <c r="B914" s="1"/>
+      <c r="B914" s="2"/>
       <c r="C914" s="1"/>
       <c r="D914" s="1"/>
       <c r="E914" s="1"/>
@@ -54418,7 +54439,7 @@
     </row>
     <row r="915" ht="12.75" customHeight="1">
       <c r="A915" s="1"/>
-      <c r="B915" s="1"/>
+      <c r="B915" s="2"/>
       <c r="C915" s="1"/>
       <c r="D915" s="1"/>
       <c r="E915" s="1"/>
@@ -54446,7 +54467,7 @@
     </row>
     <row r="916" ht="12.75" customHeight="1">
       <c r="A916" s="1"/>
-      <c r="B916" s="1"/>
+      <c r="B916" s="2"/>
       <c r="C916" s="1"/>
       <c r="D916" s="1"/>
       <c r="E916" s="1"/>
@@ -54474,7 +54495,7 @@
     </row>
     <row r="917" ht="12.75" customHeight="1">
       <c r="A917" s="1"/>
-      <c r="B917" s="1"/>
+      <c r="B917" s="2"/>
       <c r="C917" s="1"/>
       <c r="D917" s="1"/>
       <c r="E917" s="1"/>
@@ -54502,7 +54523,7 @@
     </row>
     <row r="918" ht="12.75" customHeight="1">
       <c r="A918" s="1"/>
-      <c r="B918" s="1"/>
+      <c r="B918" s="2"/>
       <c r="C918" s="1"/>
       <c r="D918" s="1"/>
       <c r="E918" s="1"/>
@@ -54530,7 +54551,7 @@
     </row>
     <row r="919" ht="12.75" customHeight="1">
       <c r="A919" s="1"/>
-      <c r="B919" s="1"/>
+      <c r="B919" s="2"/>
       <c r="C919" s="1"/>
       <c r="D919" s="1"/>
       <c r="E919" s="1"/>
@@ -54558,7 +54579,7 @@
     </row>
     <row r="920" ht="12.75" customHeight="1">
       <c r="A920" s="1"/>
-      <c r="B920" s="1"/>
+      <c r="B920" s="2"/>
       <c r="C920" s="1"/>
       <c r="D920" s="1"/>
       <c r="E920" s="1"/>
@@ -54586,7 +54607,7 @@
     </row>
     <row r="921" ht="12.75" customHeight="1">
       <c r="A921" s="1"/>
-      <c r="B921" s="1"/>
+      <c r="B921" s="2"/>
       <c r="C921" s="1"/>
       <c r="D921" s="1"/>
       <c r="E921" s="1"/>
@@ -54614,7 +54635,7 @@
     </row>
     <row r="922" ht="12.75" customHeight="1">
       <c r="A922" s="1"/>
-      <c r="B922" s="1"/>
+      <c r="B922" s="2"/>
       <c r="C922" s="1"/>
       <c r="D922" s="1"/>
       <c r="E922" s="1"/>
@@ -54642,7 +54663,7 @@
     </row>
     <row r="923" ht="12.75" customHeight="1">
       <c r="A923" s="1"/>
-      <c r="B923" s="1"/>
+      <c r="B923" s="2"/>
       <c r="C923" s="1"/>
       <c r="D923" s="1"/>
       <c r="E923" s="1"/>
@@ -54670,7 +54691,7 @@
     </row>
     <row r="924" ht="12.75" customHeight="1">
       <c r="A924" s="1"/>
-      <c r="B924" s="1"/>
+      <c r="B924" s="2"/>
       <c r="C924" s="1"/>
       <c r="D924" s="1"/>
       <c r="E924" s="1"/>
@@ -54698,7 +54719,7 @@
     </row>
     <row r="925" ht="12.75" customHeight="1">
       <c r="A925" s="1"/>
-      <c r="B925" s="1"/>
+      <c r="B925" s="2"/>
       <c r="C925" s="1"/>
       <c r="D925" s="1"/>
       <c r="E925" s="1"/>
@@ -54726,7 +54747,7 @@
     </row>
     <row r="926" ht="12.75" customHeight="1">
       <c r="A926" s="1"/>
-      <c r="B926" s="1"/>
+      <c r="B926" s="2"/>
       <c r="C926" s="1"/>
       <c r="D926" s="1"/>
       <c r="E926" s="1"/>
@@ -54754,7 +54775,7 @@
     </row>
     <row r="927" ht="12.75" customHeight="1">
       <c r="A927" s="1"/>
-      <c r="B927" s="1"/>
+      <c r="B927" s="2"/>
       <c r="C927" s="1"/>
       <c r="D927" s="1"/>
       <c r="E927" s="1"/>
@@ -54782,7 +54803,7 @@
     </row>
     <row r="928" ht="12.75" customHeight="1">
       <c r="A928" s="1"/>
-      <c r="B928" s="1"/>
+      <c r="B928" s="2"/>
       <c r="C928" s="1"/>
       <c r="D928" s="1"/>
       <c r="E928" s="1"/>
@@ -54810,7 +54831,7 @@
     </row>
     <row r="929" ht="12.75" customHeight="1">
       <c r="A929" s="1"/>
-      <c r="B929" s="1"/>
+      <c r="B929" s="2"/>
       <c r="C929" s="1"/>
       <c r="D929" s="1"/>
       <c r="E929" s="1"/>
@@ -54838,7 +54859,7 @@
     </row>
     <row r="930" ht="12.75" customHeight="1">
       <c r="A930" s="1"/>
-      <c r="B930" s="1"/>
+      <c r="B930" s="2"/>
       <c r="C930" s="1"/>
       <c r="D930" s="1"/>
       <c r="E930" s="1"/>
@@ -54866,7 +54887,7 @@
     </row>
     <row r="931" ht="12.75" customHeight="1">
       <c r="A931" s="1"/>
-      <c r="B931" s="1"/>
+      <c r="B931" s="2"/>
       <c r="C931" s="1"/>
       <c r="D931" s="1"/>
       <c r="E931" s="1"/>
@@ -54894,7 +54915,7 @@
     </row>
     <row r="932" ht="12.75" customHeight="1">
       <c r="A932" s="1"/>
-      <c r="B932" s="1"/>
+      <c r="B932" s="2"/>
       <c r="C932" s="1"/>
       <c r="D932" s="1"/>
       <c r="E932" s="1"/>
@@ -54922,7 +54943,7 @@
     </row>
     <row r="933" ht="12.75" customHeight="1">
       <c r="A933" s="1"/>
-      <c r="B933" s="1"/>
+      <c r="B933" s="2"/>
       <c r="C933" s="1"/>
       <c r="D933" s="1"/>
       <c r="E933" s="1"/>
@@ -54950,7 +54971,7 @@
     </row>
     <row r="934" ht="12.75" customHeight="1">
       <c r="A934" s="1"/>
-      <c r="B934" s="1"/>
+      <c r="B934" s="2"/>
       <c r="C934" s="1"/>
       <c r="D934" s="1"/>
       <c r="E934" s="1"/>
@@ -54978,7 +54999,7 @@
     </row>
     <row r="935" ht="12.75" customHeight="1">
       <c r="A935" s="1"/>
-      <c r="B935" s="1"/>
+      <c r="B935" s="2"/>
       <c r="C935" s="1"/>
       <c r="D935" s="1"/>
       <c r="E935" s="1"/>
@@ -55006,7 +55027,7 @@
     </row>
     <row r="936" ht="12.75" customHeight="1">
       <c r="A936" s="1"/>
-      <c r="B936" s="1"/>
+      <c r="B936" s="2"/>
       <c r="C936" s="1"/>
       <c r="D936" s="1"/>
       <c r="E936" s="1"/>
@@ -55034,7 +55055,7 @@
     </row>
     <row r="937" ht="12.75" customHeight="1">
       <c r="A937" s="1"/>
-      <c r="B937" s="1"/>
+      <c r="B937" s="2"/>
       <c r="C937" s="1"/>
       <c r="D937" s="1"/>
       <c r="E937" s="1"/>
@@ -55062,7 +55083,7 @@
     </row>
     <row r="938" ht="12.75" customHeight="1">
       <c r="A938" s="1"/>
-      <c r="B938" s="1"/>
+      <c r="B938" s="2"/>
       <c r="C938" s="1"/>
       <c r="D938" s="1"/>
       <c r="E938" s="1"/>
@@ -55090,7 +55111,7 @@
     </row>
     <row r="939" ht="12.75" customHeight="1">
       <c r="A939" s="1"/>
-      <c r="B939" s="1"/>
+      <c r="B939" s="2"/>
       <c r="C939" s="1"/>
       <c r="D939" s="1"/>
       <c r="E939" s="1"/>
@@ -55118,7 +55139,7 @@
     </row>
     <row r="940" ht="12.75" customHeight="1">
       <c r="A940" s="1"/>
-      <c r="B940" s="1"/>
+      <c r="B940" s="2"/>
       <c r="C940" s="1"/>
       <c r="D940" s="1"/>
       <c r="E940" s="1"/>
@@ -55146,7 +55167,7 @@
     </row>
     <row r="941" ht="12.75" customHeight="1">
       <c r="A941" s="1"/>
-      <c r="B941" s="1"/>
+      <c r="B941" s="2"/>
       <c r="C941" s="1"/>
       <c r="D941" s="1"/>
       <c r="E941" s="1"/>
@@ -55174,7 +55195,7 @@
     </row>
     <row r="942" ht="12.75" customHeight="1">
       <c r="A942" s="1"/>
-      <c r="B942" s="1"/>
+      <c r="B942" s="2"/>
       <c r="C942" s="1"/>
       <c r="D942" s="1"/>
       <c r="E942" s="1"/>
@@ -55202,7 +55223,7 @@
     </row>
     <row r="943" ht="12.75" customHeight="1">
       <c r="A943" s="1"/>
-      <c r="B943" s="1"/>
+      <c r="B943" s="2"/>
       <c r="C943" s="1"/>
       <c r="D943" s="1"/>
       <c r="E943" s="1"/>
@@ -55230,7 +55251,7 @@
     </row>
     <row r="944" ht="12.75" customHeight="1">
       <c r="A944" s="1"/>
-      <c r="B944" s="1"/>
+      <c r="B944" s="2"/>
       <c r="C944" s="1"/>
       <c r="D944" s="1"/>
       <c r="E944" s="1"/>
@@ -55258,7 +55279,7 @@
     </row>
     <row r="945" ht="12.75" customHeight="1">
       <c r="A945" s="1"/>
-      <c r="B945" s="1"/>
+      <c r="B945" s="2"/>
       <c r="C945" s="1"/>
       <c r="D945" s="1"/>
       <c r="E945" s="1"/>
@@ -55286,7 +55307,7 @@
     </row>
     <row r="946" ht="12.75" customHeight="1">
       <c r="A946" s="1"/>
-      <c r="B946" s="1"/>
+      <c r="B946" s="2"/>
       <c r="C946" s="1"/>
       <c r="D946" s="1"/>
       <c r="E946" s="1"/>
@@ -55314,7 +55335,7 @@
     </row>
     <row r="947" ht="12.75" customHeight="1">
       <c r="A947" s="1"/>
-      <c r="B947" s="1"/>
+      <c r="B947" s="2"/>
       <c r="C947" s="1"/>
       <c r="D947" s="1"/>
       <c r="E947" s="1"/>
@@ -55342,7 +55363,7 @@
     </row>
     <row r="948" ht="12.75" customHeight="1">
       <c r="A948" s="1"/>
-      <c r="B948" s="1"/>
+      <c r="B948" s="2"/>
       <c r="C948" s="1"/>
       <c r="D948" s="1"/>
       <c r="E948" s="1"/>
@@ -55370,7 +55391,7 @@
     </row>
     <row r="949" ht="12.75" customHeight="1">
       <c r="A949" s="1"/>
-      <c r="B949" s="1"/>
+      <c r="B949" s="2"/>
       <c r="C949" s="1"/>
       <c r="D949" s="1"/>
       <c r="E949" s="1"/>
@@ -55398,7 +55419,7 @@
     </row>
     <row r="950" ht="12.75" customHeight="1">
       <c r="A950" s="1"/>
-      <c r="B950" s="1"/>
+      <c r="B950" s="2"/>
       <c r="C950" s="1"/>
       <c r="D950" s="1"/>
       <c r="E950" s="1"/>
@@ -55426,7 +55447,7 @@
     </row>
     <row r="951" ht="12.75" customHeight="1">
       <c r="A951" s="1"/>
-      <c r="B951" s="1"/>
+      <c r="B951" s="2"/>
       <c r="C951" s="1"/>
       <c r="D951" s="1"/>
       <c r="E951" s="1"/>
@@ -55454,7 +55475,7 @@
     </row>
     <row r="952" ht="12.75" customHeight="1">
       <c r="A952" s="1"/>
-      <c r="B952" s="1"/>
+      <c r="B952" s="2"/>
       <c r="C952" s="1"/>
       <c r="D952" s="1"/>
       <c r="E952" s="1"/>
@@ -55482,7 +55503,7 @@
     </row>
     <row r="953" ht="12.75" customHeight="1">
       <c r="A953" s="1"/>
-      <c r="B953" s="1"/>
+      <c r="B953" s="2"/>
       <c r="C953" s="1"/>
       <c r="D953" s="1"/>
       <c r="E953" s="1"/>
@@ -55510,7 +55531,7 @@
     </row>
     <row r="954" ht="12.75" customHeight="1">
       <c r="A954" s="1"/>
-      <c r="B954" s="1"/>
+      <c r="B954" s="2"/>
       <c r="C954" s="1"/>
       <c r="D954" s="1"/>
       <c r="E954" s="1"/>
@@ -55538,7 +55559,7 @@
     </row>
     <row r="955" ht="12.75" customHeight="1">
       <c r="A955" s="1"/>
-      <c r="B955" s="1"/>
+      <c r="B955" s="2"/>
       <c r="C955" s="1"/>
       <c r="D955" s="1"/>
       <c r="E955" s="1"/>
@@ -55566,7 +55587,7 @@
     </row>
     <row r="956" ht="12.75" customHeight="1">
       <c r="A956" s="1"/>
-      <c r="B956" s="1"/>
+      <c r="B956" s="2"/>
       <c r="C956" s="1"/>
       <c r="D956" s="1"/>
       <c r="E956" s="1"/>
@@ -55594,7 +55615,7 @@
     </row>
     <row r="957" ht="12.75" customHeight="1">
       <c r="A957" s="1"/>
-      <c r="B957" s="1"/>
+      <c r="B957" s="2"/>
       <c r="C957" s="1"/>
       <c r="D957" s="1"/>
       <c r="E957" s="1"/>
@@ -55622,7 +55643,7 @@
     </row>
     <row r="958" ht="12.75" customHeight="1">
       <c r="A958" s="1"/>
-      <c r="B958" s="1"/>
+      <c r="B958" s="2"/>
       <c r="C958" s="1"/>
       <c r="D958" s="1"/>
       <c r="E958" s="1"/>
@@ -55650,7 +55671,7 @@
     </row>
     <row r="959" ht="12.75" customHeight="1">
       <c r="A959" s="1"/>
-      <c r="B959" s="1"/>
+      <c r="B959" s="2"/>
       <c r="C959" s="1"/>
       <c r="D959" s="1"/>
       <c r="E959" s="1"/>
@@ -55678,7 +55699,7 @@
     </row>
     <row r="960" ht="12.75" customHeight="1">
       <c r="A960" s="1"/>
-      <c r="B960" s="1"/>
+      <c r="B960" s="2"/>
       <c r="C960" s="1"/>
       <c r="D960" s="1"/>
       <c r="E960" s="1"/>
@@ -55706,7 +55727,7 @@
     </row>
     <row r="961" ht="12.75" customHeight="1">
       <c r="A961" s="1"/>
-      <c r="B961" s="1"/>
+      <c r="B961" s="2"/>
       <c r="C961" s="1"/>
       <c r="D961" s="1"/>
       <c r="E961" s="1"/>
@@ -55734,7 +55755,7 @@
     </row>
     <row r="962" ht="12.75" customHeight="1">
       <c r="A962" s="1"/>
-      <c r="B962" s="1"/>
+      <c r="B962" s="2"/>
       <c r="C962" s="1"/>
       <c r="D962" s="1"/>
       <c r="E962" s="1"/>
@@ -55762,7 +55783,7 @@
     </row>
     <row r="963" ht="12.75" customHeight="1">
       <c r="A963" s="1"/>
-      <c r="B963" s="1"/>
+      <c r="B963" s="2"/>
       <c r="C963" s="1"/>
       <c r="D963" s="1"/>
       <c r="E963" s="1"/>
@@ -55790,7 +55811,7 @@
     </row>
     <row r="964" ht="12.75" customHeight="1">
       <c r="A964" s="1"/>
-      <c r="B964" s="1"/>
+      <c r="B964" s="2"/>
       <c r="C964" s="1"/>
       <c r="D964" s="1"/>
       <c r="E964" s="1"/>
@@ -55818,7 +55839,7 @@
     </row>
     <row r="965" ht="12.75" customHeight="1">
       <c r="A965" s="1"/>
-      <c r="B965" s="1"/>
+      <c r="B965" s="2"/>
       <c r="C965" s="1"/>
       <c r="D965" s="1"/>
       <c r="E965" s="1"/>
@@ -55846,7 +55867,7 @@
     </row>
     <row r="966" ht="12.75" customHeight="1">
       <c r="A966" s="1"/>
-      <c r="B966" s="1"/>
+      <c r="B966" s="2"/>
       <c r="C966" s="1"/>
       <c r="D966" s="1"/>
       <c r="E966" s="1"/>
@@ -55874,7 +55895,7 @@
     </row>
     <row r="967" ht="12.75" customHeight="1">
       <c r="A967" s="1"/>
-      <c r="B967" s="1"/>
+      <c r="B967" s="2"/>
       <c r="C967" s="1"/>
       <c r="D967" s="1"/>
       <c r="E967" s="1"/>
@@ -55902,7 +55923,7 @@
     </row>
     <row r="968" ht="12.75" customHeight="1">
       <c r="A968" s="1"/>
-      <c r="B968" s="1"/>
+      <c r="B968" s="2"/>
       <c r="C968" s="1"/>
       <c r="D968" s="1"/>
       <c r="E968" s="1"/>
@@ -55930,7 +55951,7 @@
     </row>
     <row r="969" ht="12.75" customHeight="1">
       <c r="A969" s="1"/>
-      <c r="B969" s="1"/>
+      <c r="B969" s="2"/>
       <c r="C969" s="1"/>
       <c r="D969" s="1"/>
       <c r="E969" s="1"/>
@@ -55958,7 +55979,7 @@
     </row>
     <row r="970" ht="12.75" customHeight="1">
       <c r="A970" s="1"/>
-      <c r="B970" s="1"/>
+      <c r="B970" s="2"/>
       <c r="C970" s="1"/>
       <c r="D970" s="1"/>
       <c r="E970" s="1"/>
@@ -55986,7 +56007,7 @@
     </row>
     <row r="971" ht="12.75" customHeight="1">
       <c r="A971" s="1"/>
-      <c r="B971" s="1"/>
+      <c r="B971" s="2"/>
       <c r="C971" s="1"/>
       <c r="D971" s="1"/>
       <c r="E971" s="1"/>
@@ -56014,7 +56035,7 @@
     </row>
     <row r="972" ht="12.75" customHeight="1">
       <c r="A972" s="1"/>
-      <c r="B972" s="1"/>
+      <c r="B972" s="2"/>
       <c r="C972" s="1"/>
       <c r="D972" s="1"/>
       <c r="E972" s="1"/>
@@ -56042,7 +56063,7 @@
     </row>
     <row r="973" ht="12.75" customHeight="1">
       <c r="A973" s="1"/>
-      <c r="B973" s="1"/>
+      <c r="B973" s="2"/>
       <c r="C973" s="1"/>
       <c r="D973" s="1"/>
       <c r="E973" s="1"/>
@@ -56070,7 +56091,7 @@
     </row>
     <row r="974" ht="12.75" customHeight="1">
       <c r="A974" s="1"/>
-      <c r="B974" s="1"/>
+      <c r="B974" s="2"/>
       <c r="C974" s="1"/>
       <c r="D974" s="1"/>
       <c r="E974" s="1"/>
@@ -56098,7 +56119,7 @@
     </row>
     <row r="975" ht="12.75" customHeight="1">
       <c r="A975" s="1"/>
-      <c r="B975" s="1"/>
+      <c r="B975" s="2"/>
       <c r="C975" s="1"/>
       <c r="D975" s="1"/>
       <c r="E975" s="1"/>
@@ -56126,7 +56147,7 @@
     </row>
     <row r="976" ht="12.75" customHeight="1">
       <c r="A976" s="1"/>
-      <c r="B976" s="1"/>
+      <c r="B976" s="2"/>
       <c r="C976" s="1"/>
       <c r="D976" s="1"/>
       <c r="E976" s="1"/>
@@ -56154,7 +56175,7 @@
     </row>
     <row r="977" ht="12.75" customHeight="1">
       <c r="A977" s="1"/>
-      <c r="B977" s="1"/>
+      <c r="B977" s="2"/>
       <c r="C977" s="1"/>
       <c r="D977" s="1"/>
       <c r="E977" s="1"/>
@@ -56182,7 +56203,7 @@
     </row>
     <row r="978" ht="12.75" customHeight="1">
       <c r="A978" s="1"/>
-      <c r="B978" s="1"/>
+      <c r="B978" s="2"/>
       <c r="C978" s="1"/>
       <c r="D978" s="1"/>
       <c r="E978" s="1"/>
@@ -56210,7 +56231,7 @@
     </row>
     <row r="979" ht="12.75" customHeight="1">
       <c r="A979" s="1"/>
-      <c r="B979" s="1"/>
+      <c r="B979" s="2"/>
       <c r="C979" s="1"/>
       <c r="D979" s="1"/>
       <c r="E979" s="1"/>
@@ -56238,7 +56259,7 @@
     </row>
     <row r="980" ht="12.75" customHeight="1">
       <c r="A980" s="1"/>
-      <c r="B980" s="1"/>
+      <c r="B980" s="2"/>
       <c r="C980" s="1"/>
       <c r="D980" s="1"/>
       <c r="E980" s="1"/>
@@ -56266,7 +56287,7 @@
     </row>
     <row r="981" ht="12.75" customHeight="1">
       <c r="A981" s="1"/>
-      <c r="B981" s="1"/>
+      <c r="B981" s="2"/>
       <c r="C981" s="1"/>
       <c r="D981" s="1"/>
       <c r="E981" s="1"/>
@@ -56294,7 +56315,7 @@
     </row>
     <row r="982" ht="12.75" customHeight="1">
       <c r="A982" s="1"/>
-      <c r="B982" s="1"/>
+      <c r="B982" s="2"/>
       <c r="C982" s="1"/>
       <c r="D982" s="1"/>
       <c r="E982" s="1"/>
@@ -56322,7 +56343,7 @@
     </row>
     <row r="983" ht="12.75" customHeight="1">
       <c r="A983" s="1"/>
-      <c r="B983" s="1"/>
+      <c r="B983" s="2"/>
       <c r="C983" s="1"/>
       <c r="D983" s="1"/>
       <c r="E983" s="1"/>
@@ -56350,7 +56371,7 @@
     </row>
     <row r="984" ht="12.75" customHeight="1">
       <c r="A984" s="1"/>
-      <c r="B984" s="1"/>
+      <c r="B984" s="2"/>
       <c r="C984" s="1"/>
       <c r="D984" s="1"/>
       <c r="E984" s="1"/>
@@ -56378,7 +56399,7 @@
     </row>
     <row r="985" ht="12.75" customHeight="1">
       <c r="A985" s="1"/>
-      <c r="B985" s="1"/>
+      <c r="B985" s="2"/>
       <c r="C985" s="1"/>
       <c r="D985" s="1"/>
       <c r="E985" s="1"/>
@@ -56406,7 +56427,7 @@
     </row>
     <row r="986" ht="12.75" customHeight="1">
       <c r="A986" s="1"/>
-      <c r="B986" s="1"/>
+      <c r="B986" s="2"/>
       <c r="C986" s="1"/>
       <c r="D986" s="1"/>
       <c r="E986" s="1"/>
@@ -56434,7 +56455,7 @@
     </row>
     <row r="987" ht="12.75" customHeight="1">
       <c r="A987" s="1"/>
-      <c r="B987" s="1"/>
+      <c r="B987" s="2"/>
       <c r="C987" s="1"/>
       <c r="D987" s="1"/>
       <c r="E987" s="1"/>
@@ -56462,7 +56483,7 @@
     </row>
     <row r="988" ht="12.75" customHeight="1">
       <c r="A988" s="1"/>
-      <c r="B988" s="1"/>
+      <c r="B988" s="2"/>
       <c r="C988" s="1"/>
       <c r="D988" s="1"/>
       <c r="E988" s="1"/>
@@ -56490,7 +56511,7 @@
     </row>
     <row r="989" ht="12.75" customHeight="1">
       <c r="A989" s="1"/>
-      <c r="B989" s="1"/>
+      <c r="B989" s="2"/>
       <c r="C989" s="1"/>
       <c r="D989" s="1"/>
       <c r="E989" s="1"/>
@@ -56518,7 +56539,7 @@
     </row>
     <row r="990" ht="12.75" customHeight="1">
       <c r="A990" s="1"/>
-      <c r="B990" s="1"/>
+      <c r="B990" s="2"/>
       <c r="C990" s="1"/>
       <c r="D990" s="1"/>
       <c r="E990" s="1"/>
@@ -56546,7 +56567,7 @@
     </row>
     <row r="991" ht="12.75" customHeight="1">
       <c r="A991" s="1"/>
-      <c r="B991" s="1"/>
+      <c r="B991" s="2"/>
       <c r="C991" s="1"/>
       <c r="D991" s="1"/>
       <c r="E991" s="1"/>
@@ -56574,7 +56595,7 @@
     </row>
     <row r="992" ht="12.75" customHeight="1">
       <c r="A992" s="1"/>
-      <c r="B992" s="1"/>
+      <c r="B992" s="2"/>
       <c r="C992" s="1"/>
       <c r="D992" s="1"/>
       <c r="E992" s="1"/>
@@ -56602,7 +56623,7 @@
     </row>
     <row r="993" ht="12.75" customHeight="1">
       <c r="A993" s="1"/>
-      <c r="B993" s="1"/>
+      <c r="B993" s="2"/>
       <c r="C993" s="1"/>
       <c r="D993" s="1"/>
       <c r="E993" s="1"/>
@@ -56630,7 +56651,7 @@
     </row>
     <row r="994" ht="12.75" customHeight="1">
       <c r="A994" s="1"/>
-      <c r="B994" s="1"/>
+      <c r="B994" s="2"/>
       <c r="C994" s="1"/>
       <c r="D994" s="1"/>
       <c r="E994" s="1"/>
@@ -56658,7 +56679,7 @@
     </row>
     <row r="995" ht="12.75" customHeight="1">
       <c r="A995" s="1"/>
-      <c r="B995" s="1"/>
+      <c r="B995" s="2"/>
       <c r="C995" s="1"/>
       <c r="D995" s="1"/>
       <c r="E995" s="1"/>
@@ -56686,7 +56707,7 @@
     </row>
     <row r="996" ht="12.75" customHeight="1">
       <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
+      <c r="B996" s="2"/>
       <c r="C996" s="1"/>
       <c r="D996" s="1"/>
       <c r="E996" s="1"/>
@@ -56714,7 +56735,7 @@
     </row>
     <row r="997" ht="12.75" customHeight="1">
       <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
+      <c r="B997" s="2"/>
       <c r="C997" s="1"/>
       <c r="D997" s="1"/>
       <c r="E997" s="1"/>
@@ -56742,7 +56763,7 @@
     </row>
     <row r="998" ht="12.75" customHeight="1">
       <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
+      <c r="B998" s="2"/>
       <c r="C998" s="1"/>
       <c r="D998" s="1"/>
       <c r="E998" s="1"/>
@@ -56770,7 +56791,7 @@
     </row>
     <row r="999" ht="12.75" customHeight="1">
       <c r="A999" s="1"/>
-      <c r="B999" s="1"/>
+      <c r="B999" s="2"/>
       <c r="C999" s="1"/>
       <c r="D999" s="1"/>
       <c r="E999" s="1"/>
@@ -56798,7 +56819,7 @@
     </row>
     <row r="1000" ht="12.75" customHeight="1">
       <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
+      <c r="B1000" s="2"/>
       <c r="C1000" s="1"/>
       <c r="D1000" s="1"/>
       <c r="E1000" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -4,7 +4,8 @@
   <workbookPr/>
   <sheets>
     <sheet state="visible" name="Locations" sheetId="1" r:id="rId5"/>
-    <sheet state="visible" name="Openings" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Quests" sheetId="2" r:id="rId6"/>
+    <sheet state="visible" name="Openings" sheetId="3" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr/>
@@ -12,27 +13,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="64">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="72">
   <si>
     <t>Location ID</t>
-  </si>
-  <si>
-    <t>Opening_ID</t>
   </si>
   <si>
     <t>Location Name</t>
   </si>
   <si>
     <t>Location Type</t>
-  </si>
-  <si>
-    <t>Opening</t>
-  </si>
-  <si>
-    <t>Opening_Location</t>
-  </si>
-  <si>
-    <t>Player_Type</t>
   </si>
   <si>
     <t>Meadowbrook</t>
@@ -50,12 +39,6 @@
     <t>Maple City</t>
   </si>
   <si>
-    <t>You wake up, full of excitement. You are still a little tired because you barely got any sleep last night, but that doesn't matter any more because today is the day that you get your first Morimon! You quickly get dressed and grab the backpack you packed last night before heading downstairs to join your parents for breakfast. Your mom has prepared a big meal but you're too excited to eat more than a few bites. "You've grown up so fast!" your mother exclaims. "Make sure you keep in touch, and be safe!" she tells you. Your father pats you on the shoulder, reminding you that you had better hurry to the Morimon center or else you'll be late. Taking his advice, you throw your backpack over your shoulder and head out of the house.</t>
-  </si>
-  <si>
-    <t>Catcher</t>
-  </si>
-  <si>
     <t>Timberline Trail</t>
   </si>
   <si>
@@ -65,16 +48,19 @@
     <t>Destination</t>
   </si>
   <si>
-    <t>You feel someone gently shaking you awake; still a bit groggy from the night before. As you awaken you hear the familiar voice of your father. "Come on [Player_Name], it's time to wake up. You don't want to be late for your first day as a Morimon catcher." Your lack of energy becomes completely replaced with a surge of excitement. That's right! Today is the day you've been dreaming of. It's the chance for you to venture out on your own as a Morimon catcher. You quickly check the time and realize your father wasn't kidding. If you don't hurry you will be late. You quickly throw on some clothes and grab the bag you packed the night before, then head out the front door.</t>
-  </si>
-  <si>
     <t>Ironvale</t>
   </si>
   <si>
     <t>Ashland Trail</t>
   </si>
   <si>
+    <t>Opening_ID</t>
+  </si>
+  <si>
     <t>Lake Ashland Cavern</t>
+  </si>
+  <si>
+    <t>Opening</t>
   </si>
   <si>
     <t>Moonshadow Trail</t>
@@ -86,19 +72,58 @@
     <t>Brightwater Bridge</t>
   </si>
   <si>
+    <t>Questline_ID</t>
+  </si>
+  <si>
+    <t>Opening_Location</t>
+  </si>
+  <si>
     <t>Tidecrest Trail</t>
+  </si>
+  <si>
+    <t>Player_Type</t>
+  </si>
+  <si>
+    <t>Questline_Name</t>
   </si>
   <si>
     <t>Fernway Trail</t>
   </si>
   <si>
+    <t>Sequence_Name</t>
+  </si>
+  <si>
+    <t>Location(s)</t>
+  </si>
+  <si>
+    <t>Modifiers</t>
+  </si>
+  <si>
     <t>Hollowpass Tunnel</t>
+  </si>
+  <si>
+    <t>Triggered</t>
+  </si>
+  <si>
+    <t>Action</t>
+  </si>
+  <si>
+    <t>Text</t>
+  </si>
+  <si>
+    <t>You wake up, full of excitement. You are still a little tired because you barely got any sleep last night, but that doesn't matter any more because today is the day that you get your first Morimon! You quickly get dressed and grab the backpack you packed last night before heading downstairs to join your parents for breakfast. Your mom has prepared a big meal but you're too excited to eat more than a few bites. "You've grown up so fast!" your mother exclaims. "Make sure you keep in touch, and be safe!" she tells you. Your father pats you on the shoulder, reminding you that you had better hurry to the Morimon center or else you'll be late. Taking his advice, you throw your backpack over your shoulder and head out of the house.</t>
   </si>
   <si>
     <t>Sunreach Trail</t>
   </si>
   <si>
+    <t>Catcher</t>
+  </si>
+  <si>
     <t>Scarletide City</t>
+  </si>
+  <si>
+    <t>You feel someone gently shaking you awake; still a bit groggy from the night before. As you awaken you hear the familiar voice of your father. "Come on [Player_Name], it's time to wake up. You don't want to be late for your first day as a Morimon catcher." Your lack of energy becomes completely replaced with a surge of excitement. That's right! Today is the day you've been dreaming of. It's the chance for you to venture out on your own as a Morimon catcher. You quickly check the time and realize your father wasn't kidding. If you don't hurry you will be late. You quickly throw on some clothes and grab the bag you packed the night before, then head out the front door.</t>
   </si>
   <si>
     <t>The Gilded Voyager</t>
@@ -250,12 +275,12 @@
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment shrinkToFit="0" wrapText="1"/>
     </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="1" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
@@ -273,6 +298,10 @@
 </file>
 
 <file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cx="http://schemas.microsoft.com/office/drawing/2014/chartex" xmlns:cx1="http://schemas.microsoft.com/office/drawing/2015/9/8/chartex" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:x3Unk="http://schemas.microsoft.com/office/drawing/2010/slicer" xmlns:sle15="http://schemas.microsoft.com/office/drawing/2012/slicer"/>
 </file>
 
@@ -493,10 +522,10 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D1" s="1"/>
       <c r="E1" s="1"/>
@@ -527,10 +556,10 @@
         <v>1.0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>7</v>
+        <v>3</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -561,10 +590,10 @@
         <v>2.0</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1"/>
@@ -595,10 +624,10 @@
         <v>3.0</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1"/>
@@ -629,10 +658,10 @@
         <v>4.0</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1"/>
@@ -663,10 +692,10 @@
         <v>5.0</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1"/>
@@ -697,10 +726,10 @@
         <v>6.0</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1"/>
@@ -731,10 +760,10 @@
         <v>7.0</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1"/>
@@ -765,10 +794,10 @@
         <v>8.0</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>20</v>
+        <v>14</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1"/>
@@ -799,10 +828,10 @@
         <v>9.0</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1"/>
@@ -833,10 +862,10 @@
         <v>10.0</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1"/>
@@ -867,10 +896,10 @@
         <v>11.0</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1"/>
@@ -901,10 +930,10 @@
         <v>12.0</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="C13" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1"/>
@@ -935,10 +964,10 @@
         <v>13.0</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1"/>
@@ -969,10 +998,10 @@
         <v>14.0</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1"/>
@@ -1003,10 +1032,10 @@
         <v>15.0</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1"/>
@@ -1037,10 +1066,10 @@
         <v>16.0</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>28</v>
+        <v>35</v>
       </c>
       <c r="C17" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1"/>
@@ -1071,10 +1100,10 @@
         <v>17.0</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>29</v>
+        <v>37</v>
       </c>
       <c r="C18" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1"/>
@@ -1105,10 +1134,10 @@
         <v>18.0</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>30</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1"/>
@@ -1139,10 +1168,10 @@
         <v>19.0</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1"/>
@@ -1173,10 +1202,10 @@
         <v>20.0</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="C21" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1"/>
@@ -1207,10 +1236,10 @@
         <v>21.0</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>33</v>
+        <v>41</v>
       </c>
       <c r="C22" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1"/>
@@ -1241,10 +1270,10 @@
         <v>22.0</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>34</v>
+        <v>42</v>
       </c>
       <c r="C23" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1"/>
@@ -1275,10 +1304,10 @@
         <v>23.0</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>35</v>
+        <v>43</v>
       </c>
       <c r="C24" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1"/>
@@ -1309,10 +1338,10 @@
         <v>24.0</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>36</v>
+        <v>44</v>
       </c>
       <c r="C25" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1"/>
@@ -1343,10 +1372,10 @@
         <v>25.0</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>37</v>
+        <v>45</v>
       </c>
       <c r="C26" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1"/>
@@ -1377,10 +1406,10 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>38</v>
+        <v>46</v>
       </c>
       <c r="C27" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1"/>
@@ -1411,10 +1440,10 @@
         <v>27.0</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>39</v>
+        <v>47</v>
       </c>
       <c r="C28" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1"/>
@@ -1445,10 +1474,10 @@
         <v>28.0</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1"/>
@@ -1479,10 +1508,10 @@
         <v>29.0</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1"/>
@@ -1513,10 +1542,10 @@
         <v>30.0</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>42</v>
+        <v>50</v>
       </c>
       <c r="C31" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1"/>
@@ -1547,10 +1576,10 @@
         <v>31.0</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>43</v>
+        <v>51</v>
       </c>
       <c r="C32" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1"/>
@@ -1581,10 +1610,10 @@
         <v>32.0</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1"/>
@@ -1615,10 +1644,10 @@
         <v>33.0</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>45</v>
+        <v>53</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1"/>
@@ -1649,10 +1678,10 @@
         <v>34.0</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>46</v>
+        <v>54</v>
       </c>
       <c r="C35" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1"/>
@@ -1683,10 +1712,10 @@
         <v>35.0</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>47</v>
+        <v>55</v>
       </c>
       <c r="C36" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -1717,10 +1746,10 @@
         <v>36.0</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>48</v>
+        <v>56</v>
       </c>
       <c r="C37" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1"/>
@@ -1751,10 +1780,10 @@
         <v>37.0</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>49</v>
+        <v>57</v>
       </c>
       <c r="C38" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1"/>
@@ -1785,10 +1814,10 @@
         <v>38.0</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>50</v>
+        <v>58</v>
       </c>
       <c r="C39" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -1819,10 +1848,10 @@
         <v>39.0</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>51</v>
+        <v>59</v>
       </c>
       <c r="C40" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1"/>
@@ -1853,10 +1882,10 @@
         <v>40.0</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="C41" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1"/>
@@ -1887,10 +1916,10 @@
         <v>41.0</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1"/>
@@ -1921,10 +1950,10 @@
         <v>42.0</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C43" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1"/>
@@ -1955,10 +1984,10 @@
         <v>43.0</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="C44" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -1989,10 +2018,10 @@
         <v>44.0</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="C45" s="1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1"/>
@@ -2023,10 +2052,10 @@
         <v>45.0</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="C46" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1"/>
@@ -2057,10 +2086,10 @@
         <v>46.0</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="C47" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1"/>
@@ -2091,10 +2120,10 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="C48" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1"/>
@@ -2125,10 +2154,10 @@
         <v>48.0</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1"/>
@@ -2159,10 +2188,10 @@
         <v>49.0</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1"/>
@@ -2193,10 +2222,10 @@
         <v>50.0</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="C51" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -2227,10 +2256,10 @@
         <v>51.0</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="C52" s="1" t="s">
-        <v>16</v>
+        <v>10</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1"/>
@@ -28811,6 +28840,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
   <sheetPr>
+    <outlinePr summaryBelow="0" summaryRight="0"/>
+  </sheetPr>
+  <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
+  <cols>
+    <col customWidth="1" min="2" max="2" width="13.38"/>
+    <col customWidth="1" min="3" max="3" width="13.88"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B1" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C1" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="F1" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G1" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H1" s="3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+  </sheetData>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+  <sheetPr>
     <pageSetUpPr/>
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="12.63" defaultRowHeight="15.0"/>
@@ -28825,16 +28896,16 @@
   <sheetData>
     <row r="1" ht="12.75" customHeight="1">
       <c r="A1" s="1" t="s">
-        <v>1</v>
+        <v>13</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="F1" s="1"/>
       <c r="G1" s="1"/>
@@ -28859,17 +28930,17 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" ht="12.75" customHeight="1">
-      <c r="A2" s="3">
+      <c r="A2" s="4">
         <v>1.0</v>
       </c>
-      <c r="B2" s="4" t="s">
-        <v>12</v>
+      <c r="B2" s="5" t="s">
+        <v>32</v>
       </c>
       <c r="C2" s="1">
         <v>1.0</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E2" s="1"/>
       <c r="F2" s="1"/>
@@ -28895,17 +28966,17 @@
       <c r="Z2" s="1"/>
     </row>
     <row r="3" ht="12.75" customHeight="1">
-      <c r="A3" s="5">
+      <c r="A3" s="3">
         <v>2.0</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>17</v>
+      <c r="B3" s="5" t="s">
+        <v>36</v>
       </c>
       <c r="C3" s="6">
         <v>1.0</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>

--- a/data.xlsx
+++ b/data.xlsx
@@ -5,7 +5,8 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Locations" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Location_1" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Openings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Quests" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Openings" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -8742,6 +8743,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="13.38" customWidth="1" style="5" min="2" max="2"/>
+    <col width="13.88" customWidth="1" style="5" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Questline_ID</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Questline_Name</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Sequence_Name</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Location(s)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Modifiers</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Triggered</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:Z220"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="12.63" defaultRowHeight="15" customHeight="1"/>
   <cols>
@@ -8837,7 +8898,7 @@
       <c r="Z2" s="2" t="n"/>
     </row>
     <row r="3" ht="12.75" customHeight="1" s="5">
-      <c r="A3" t="n">
+      <c r="A3" s="0" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="inlineStr">
